--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -8,13 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,11 +49,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,7 +89,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -468,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -568,257 +560,250 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2.4</v>
+        <v>-3</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>BUGÜN</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 20/7 , ALT -  - 30/6 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 11 - 8/4 , SHORT - 11 - 8/4 , -</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
-L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-12/%50)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>73.40000153</v>
+        <v>16.96</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 10 - 5/7 , SHORT - 10 - 5/7 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+ALT -  - 18/4 , ALT -  - 18/4 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (15g/-9/%50)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-5/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (6g/-3/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-5/%65)
+R - TP5/20G - %80 / 102 işlem - ADAY (5g/-5/%60)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>17.48999977</v>
+        <v>285.25</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 15/2 , ALT -  - 15/2 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (4g/-2/%100)
-L - TP5/10G - %77 / 43 işlem - ADAY (5g/0/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-2/%90)
-R - TP5/20G - %80 / 102 işlem - ADAY (4g/-2/%95)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>294</v>
+        <v>38.7</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 13/0 , LONG - 2 - 11/1 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 6 - 11/6 , LONG - 6 - 11/6 , -</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G, V-TP2/10G, V-TP5/10G, Y-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (12g/-11/%56)
-E - TP5/20G - %69 / 179 işlem - ADAY (4g/0/%85)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/0/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (10g/-11/%15)
-R - TP2/10G - %84 / 119 işlem - ADAY (3g/-3/%85)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-1/%90)
-V - TP2/10G - %95 / 21 işlem - ADAY (3g/-3/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (3g/-3/%88)
-Y - TP5/20G - %71 / 98 işlem - ADAY (11g/-11/%15)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (8g/-2/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (8g/-2/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-16/%15)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 72 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -827,103 +812,111 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>3.02999997</v>
+        <v>7</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 13/0 , LONG - 3 - 11/1 , -</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>M-TP5/20G, E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G, V-TP2/10G, V-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (1g/-2/%100)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (13g/-11/%60)
+E - TP5/20G - %69 / 179 işlem - ADAY (5g/-1/%95)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-1/%90)
+Q - TP5/20G - %70 / 203 işlem - ADAY (11g/-11/%10)
+R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-2/%70)
+V - TP2/10G - %95 / 21 işlem - ADAY (4g/-3/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (4g/-3/%75)
+Y - TP5/20G - %71 / 98 işlem - ADAY (12g/-11/%15)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 72 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>37.40000153</v>
+        <v>3.02</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+        <v>-1.3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 11/6 , LONG - 5 - 11/6 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 71 - 12/8 , SHORT - 71 - 14/7 , -</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
@@ -936,19 +929,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (7g/-1/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (7g/-1/%67)
-Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-16/%10)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (11g/-7/%75)
+R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%75)
+R - TP5/20G - %80 / 102 işlem - ADAY (4g/-3/%85)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -957,65 +950,66 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>7.05999994</v>
+        <v>61.4</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 10/0 , SHORT - 87 - 11/9 , LONG - 7 - 14/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 5 - 7/3 , LONG - 5 - 7/3 , LONG - 2 - 10/1</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-2/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (17g/-2/%69)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-2/%65)
-Z - TP5/20G - %75 / 71 işlem - ADAY (3g/-2/%90)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/+2/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/+2/%100)
+Q - TP2/10G - %82 / 103 işlem - ADAY (3g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-7/%40)
+R - TP5/20G - %80 / 102 işlem - ADAY (18g/-7/%25)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 77 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1024,64 +1018,66 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>80.19999695</v>
+        <v>26.6</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 32 - 4/6 , LONG - 30 - 4/6 , LONG - 30 - 4/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
         <v>55</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/0/%84)
-H - TP5/10G - %70 / 20 işlem - ADAY (2g/0/%100)
-H - TP5/20G - %85 / 20 işlem - ADAY (2g/0/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/+1/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (4g/+1/%100)
+I - TP5/20G - %82 / 67 işlem - ADAY (4g/+1/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/+1/%100)
+R - TP5/20G - %80 / 102 işlem - ADAY (15g/-10/%20)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1090,65 +1086,63 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>11.35999966</v>
+        <v>3.14</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+        <v>-2.8</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 70 - 12/9 , SHORT - 70 - 13/8 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 21/7 , ALT -  - 32/8 , -</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (9g/-6/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (10g/-5/%75)
-R - TP5/10G - %60 / 138 işlem - ADAY (3g/-2/%95)
-R - TP5/20G - %80 / 102 işlem - ADAY (3g/-2/%85)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-3/%92)
+L - TP5/10G - %77 / 43 işlem - ADAY (1g/-3/%93)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
@@ -1157,66 +1151,63 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>62.20000076</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
+        <v>-1.4</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 4 - 8/2 , LONG - 4 - 8/2 , LONG - 1 - 10/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 3 - 10/0 , LONG - 3 - 10/0 , LONG - 5 - 10/3</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>H-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/+2/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/+2/%100)
-Q - TP2/10G - %82 / 103 işlem - ADAY (2g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-7/%25)
-R - TP5/20G - %80 / 102 işlem - ADAY (17g/-7/%35)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (9g/-6/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%95)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 76 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -1225,24 +1216,24 @@
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>26.5</v>
+        <v>2.91</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>ELDEKİ</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -1252,168 +1243,168 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 2 - 10/1 , SHORT - 88 - 10/10 , LONG - 8 - 14/3</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/0/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (3g/0/%100)
-I - TP5/20G - %82 / 67 işlem - ADAY (3g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/0/%100)
-R - TP5/20G - %80 / 102 işlem - ADAY (14g/-11/%30)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-2/%55)
+I - TP5/20G - %82 / 67 işlem - ADAY (18g/-2/%54)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-2/%50)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>3.11999989</v>
+        <v>80.55</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 29/2 , ALT -  - 24/5 , LONG - 2 - 33/2</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 33 - 3/7 , LONG - 31 - 3/7 , LONG - 31 - 3/7</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (13g/-3/%35)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/+1/%100)
+H - TP5/10G - %70 / 20 işlem - ADAY (3g/+1/%100)
+H - TP5/20G - %85 / 20 işlem - ADAY (3g/+1/%100)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>37.5</v>
+        <v>11.52</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 9/1 , LONG - 2 - 9/1 , LONG - 4 - 9/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 30/2 , ALT -  - 24/6 , LONG - 3 - 34/1</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
         <v>51</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>H-TP2/10G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (8g/-5/%73)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/+1/%100)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (14g/-4/%40)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 76 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1422,10 +1413,10 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>2.95000005</v>
+        <v>37.2</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
@@ -1435,22 +1426,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
+        <v>-1.3</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 4 - 19/2 , LONG - 6 - 26/7 , LONG - 6 - 4/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 5 - 21/1 , LONG - 7 - 27/6 , LONG - 7 - 5/5</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1472,8 +1463,8 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (2g/0/%100)
-Z - TP5/20G - %75 / 71 işlem - ADAY (3g/+1/%100)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-1/%92)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%85)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1487,10 +1478,10 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>95.80000305</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
@@ -1500,22 +1491,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 12/1 , LONG - 137 - 19/12 , -</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 15/4 , ALT -  - 15/4 , -</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1537,9 +1528,9 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (4g/-4/%70)
-I - TP5/10G - %61 / 109 işlem - ADAY (3g/-2/%70)
-I - TP5/20G - %82 / 67 işlem - ADAY (4g/-4/%90)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (5g/-7/%55)
+I - TP5/10G - %61 / 109 işlem - ADAY (4g/-5/%70)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-7/%80)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1553,35 +1544,35 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>15.07999992</v>
+        <v>14.63</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+        <v>-1.3</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 22 - 14/10 , ALT -  - 17/4 , ALT -  - 16/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1591,26 +1582,27 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/0/%95)
-I - TP5/20G - %82 / 67 işlem - ADAY (4g/+1/%100)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/+1/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/0/%85)
+I - TP5/10G - %61 / 109 işlem - ADAY (4g/0/%80)
+I - TP5/20G - %82 / 67 işlem - ADAY (4g/0/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-8/%20)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1619,166 +1611,166 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>80</v>
+        <v>294.75</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
+        <v>-5.9</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 71/54 , ALT -  - 98/46 , ALT -  - 71/54</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>L-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/+1/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (3g/+1/%100)
-I - TP5/20G - %82 / 67 işlem - ADAY (3g/+1/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-7/%25)</t>
+          <t>L - TP5/10G - %77 / 43 işlem - ADAY (9g/-27/%38)
+Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-41/%10)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 73 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>298.5</v>
+        <v>19.61</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
+        <v>-1.7</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 23 - 16/9 , ALT -  - 19/6 , ALT -  - 18/5</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (12g/-3/%55)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-2/%95)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-1/%90)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>8.19999981</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
+        <v>-0.9</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 60 - 7/5 , SHORT - 62 - 6/6 , ALT -  - 12/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1788,24 +1780,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/0/%100)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (3g/-4/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (3g/-4/%89)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1814,34 +1807,34 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>300.25</v>
+        <v>35.68</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
 -</t>
         </is>
       </c>
@@ -1864,7 +1857,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-2/%70)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/-3/%65)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1878,39 +1871,39 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>6.17999983</v>
+        <v>8.18</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+        <v>-1.1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 16/5 , LONG - 2 - 20/2 , ALT -  - 21/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 61 - 8/5 , SHORT - 63 - 7/5 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -1923,17 +1916,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-4/%40)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%95)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -1942,39 +1935,39 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>547.5</v>
+        <v>297</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
 -</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
@@ -1987,17 +1980,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (1g/+2/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-2/%65)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -2006,39 +1999,39 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>234.80000305</v>
+        <v>6.21</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
+        <v>-0.9</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 65 - 11/5 , SHORT - 142 - 26/7 , LONG - 6 - 10/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+-</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0</v>
@@ -2056,7 +2049,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-3/%60)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2066,238 +2059,235 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>165.1000061</v>
+        <v>232.69999695</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
+        <v>-1.4</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 11 - 15/15 , LONG - 10 - 18/13 , UST -  - 0/10</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 66 - 12/4 , SHORT - 143 - 28/5 , LONG - 7 - 11/1</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>L-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-U - TP5/20G - %74 / 74 işlem - ADAY (2g/0/%100)
-V - TP2/10G - %95 / 21 işlem - ADAY (2g/0/%100)
-V - TP5/10G - %75 / 20 işlem - ADAY (3g/+2/%100)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-4/%45)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>72.65000153</v>
+        <v>162.8</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 2 - 2/13 , UST -  - 4/18 , UST -  - 4/15</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 6 - 16/5 , LONG - 3 - 20/1 , ALT -  - 22/4</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (14g/-7/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-4/%25)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>701</v>
+        <v>543</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+        <v>-2.3</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 18 - 4/6 , LONG - 31 - 5/7 , LONG - 9 - 6/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 3 - 5/11 , UST -  - 1/16 , SHORT - 2 - 3/12</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Y-TP5/10G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/10G - %61 / 71 işlem - ADAY (8g/+2/%100)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (15g/-9/%40)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>154.19999695</v>
+        <v>685</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-UST -  - 3/12 , UST -  - 2/12 , SHORT - 10 - 3/7</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>1</v>
@@ -2310,17 +2300,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (15g/0/%100)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-10/%50)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
@@ -2329,193 +2319,196 @@
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>108.30000305</v>
+        <v>3.5</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-UST -  - 3/23 , UST -  - 4/29 , UST -  - 12/22</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 19 - 5/5 , LONG - 32 - 6/6 , LONG - 10 - 7/5</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>Y-TP5/10G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-2/%90)</t>
+          <t>Y - TP5/10G - %61 / 71 işlem - ADAY (9g/+1/%100)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 18 - 8/8 , SHORT - 12 - 7/9 , LONG - 4 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 6 - 9/19 , LONG - 7 - 8/20 , UST -  - 8/16</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>K-TP5/20G, Q-TP5/20G</t>
+          <t>X-TP5/20G, Y-TP2/10G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %90 / 51 işlem - ONAY (13g/0/%67)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/+3/%100)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (2g/+3/%100)
+Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
+X - TP5/10G - %82 / 44 işlem - ADAY (2g/+3/%100)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/+3/%100)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 75 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi, Y: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 33 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>217.30000305</v>
+        <v>2.86</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
+        <v>-2.3</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 19 - 14/7 , LONG - 5 - 15/2 , LONG - 31 - 5/5</t>
+          <t>BIS -2, PHL +2, CNDL -1, XU030 0, TOPLAM -1, ALMA
+LONG - 12 - 18/13 , LONG - 11 - 21/11 , SHORT - 1 - 2/7</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+          <t>L-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (2g/-2/%92)
-U - TP5/20G - %74 / 74 işlem - ADAY (10g/-1/%95)
-Z - TP5/20G - %75 / 71 işlem - ADAY (10g/-1/%70)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/-2/%100)
+U - TP5/20G - %74 / 74 işlem - ADAY (3g/-2/%85)
+V - TP2/10G - %95 / 21 işlem - ADAY (3g/-2/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (4g/0/%75)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -2524,170 +2517,167 @@
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>2.03999996</v>
+        <v>71</v>
       </c>
       <c r="O31" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
+        <v>-1.8</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 10/19 , LONG - 6 - 9/19 , UST -  - 7/16</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+UST -  - 1/10 , UST -  - 1/10 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/+2/%100)
-X - TP5/10G - %82 / 44 işlem - ADAY (1g/+2/%100)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/+2/%100)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-1/%50)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>2.81999993</v>
+        <v>106.3</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
+        <v>-0.1</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 45 - 1/14 , LONG - 80 - 5/14 , SHORT - 3 - 0/15</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 1 - 0/9 , SHORT - 1 - 0/9 , SHORT - 3 - 1/9</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (3g/0/%100)
-Z - TP5/20G - %75 / 71 işlem - ADAY (3g/0/%100)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (1g/0/%95)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>225.5</v>
+        <v>20.9</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
+        <v>-4.4</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 1 - 2/20 , SHORT - 1 - 1/25 , UST -  - 8/18</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>1</v>
@@ -2700,159 +2690,160 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (15g/-10/%50)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-6/%82)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>3.5</v>
+        <v>47.82</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 42 - 11/13 , LONG - 42 - 11/13 , SHORT - 2 - 1/9</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 20 - 14/7 , LONG - 6 - 15/2 , LONG - 32 - 5/5</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (0g/0/%100)
-U - TP2/10G - %75 / 97 işlem - ADAY (2g/-1/%85)
-U - TP5/20G - %74 / 74 işlem - ADAY (10g/-1/%95)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-2/%92)
+U - TP5/20G - %74 / 74 işlem - ADAY (11g/-1/%85)
+Z - TP5/20G - %75 / 71 işlem - ADAY (11g/-1/%55)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>117.30000305</v>
+        <v>2.04</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 3/7 , LONG - 9 - 14/10 , LONG - 7 - 15/10</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 19 - 8/8 , SHORT - 17 - 9/7 , LONG - 5 - 5/5</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>K-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (3g/+2/%100)</t>
+          <t>K - TP5/20G - %90 / 51 işlem - ONAY (14g/0/%63)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/+3/%100)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 75 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>19.73999977</v>
+        <v>217.4</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
@@ -2862,22 +2853,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 18 - 20/11 , LONG - 19 - 4/8 , LONG - 18 - 1/8</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 15 - 23/9 , LONG - 20 - 5/7 , LONG - 19 - 2/7</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2899,7 +2890,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (2g/+1/%100)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (3g/0/%100)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2913,10 +2904,10 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>91.25</v>
+        <v>90.7</v>
       </c>
       <c r="O37" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
@@ -2926,22 +2917,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 30 - 5/7 , LONG - 38 - 5/6 , LONG - 75 - 10/10</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 31 - 4/7 , LONG - 39 - 5/7 , LONG - 76 - 9/11</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2963,7 +2954,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (17g/+2/%100)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (18g/+2/%100)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2977,35 +2968,35 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>134.19999695</v>
+        <v>134.6</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 2 - 31/3 , ALT -  - 88/39 , ALT -  - 63/47</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 46 - 1/14 , LONG - 81 - 5/14 , SHORT - 4 - 0/15</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -3022,84 +3013,83 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>L-TP5/10G, Q-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %77 / 43 işlem - ADAY (8g/-22/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-38/%15)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (4g/0/%100)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%100)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 73 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>20.84000015</v>
+        <v>225.4</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
+        <v>-2.3</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 47/33 , LONG - 6 - 24/9 , LONG - 3 - 7/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 9 - 5/5 , LONG - 9 - 5/5 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, R-TP5/10G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/-16/%10)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-18/%0)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/+1/%100)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-2/%80)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-2/%70)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 92 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
@@ -3108,35 +3098,35 @@
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>3.91000009</v>
+        <v>52.4</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-UST -  - 8/16 , LONG - 44 - 4/23 , UST -  - 2/11</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 11 - 5/5 , SHORT - 11 - 5/5 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -3146,66 +3136,65 @@
         <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (0g/0/%100)
-U - TP5/20G - %74 / 74 işlem - ADAY (2g/+2/%100)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>61.40000153</v>
+        <v>21.74</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 10 - 4/6 , SHORT - 10 - 4/6 , SHORT - 10 - 4/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 6 - 3/6 , LONG - 10 - 14/10 , LONG - 8 - 15/10</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -3218,93 +3207,94 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (11g/-2/%85)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/+2/%100)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>21.87999916</v>
+        <v>19.71</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
+        <v>-2.8</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 6 - 5/5 , SHORT - 12 - 5/5 , SHORT - 10 - 4/8</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 1 - 2/10 , LONG - 25 - 11/12 , SHORT - 1 - 1/9</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>22.31999969</v>
+        <v>291.25</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
@@ -3314,22 +3304,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
+        <v>-1.9</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 10 - 8/2 , SHORT - 11 - 9/4 , SHORT - 11 - 9/4</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 11 - 9/1 , SHORT - 12 - 10/3 , SHORT - 12 - 10/3</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -3351,10 +3341,10 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (2g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (2g/0/%100)
-R - TP2/10G - %84 / 119 işlem - ADAY (2g/0/%100)
-R - TP5/10G - %60 / 138 işlem - ADAY (2g/0/%100)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (3g/-2/%95)
+Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-2/%90)
+R - TP2/10G - %84 / 119 işlem - ADAY (3g/-2/%90)
+R - TP5/10G - %60 / 138 işlem - ADAY (3g/-2/%95)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3368,231 +3358,236 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>1.02999997</v>
+        <v>1.01</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
+        <v>-1.8</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 6 - 6/4 , LONG - 23 - 17/4 , ALT -  - 18/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 43 - 13/11 , SHORT - 3 - 4/6 , SHORT - 3 - 3/7</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (3g/-2/%80)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (1g/-2/%95)
+U - TP2/10G - %75 / 97 işlem - ADAY (3g/-3/%60)
+U - TP5/20G - %74 / 74 işlem - ADAY (11g/-2/%85)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>72.30000305</v>
+        <v>115.2</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 9 - 3/9 , LONG - 5 - 4/6 , LONG - 4 - 6/4</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+ALT -  - 49/35 , LONG - 7 - 25/7 , LONG - 4 - 8/2</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/+1/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-17/%10)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-20/%0)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-1/%90)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 92 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>103.69999695</v>
+        <v>3.83</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 4 - 9/1 , LONG - 4 - 10/1 , LONG - 4 - 10/1</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+UST -  - 7/16 , LONG - 45 - 5/22 , UST -  - 1/10</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (14g/+1/%100)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (1g/0/%100)
+U - TP5/20G - %74 / 74 işlem - ADAY (3g/+1/%100)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>11.39000034</v>
+        <v>61.1</v>
       </c>
       <c r="O47" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
+        <v>-1.8</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 14 - 7/21 , LONG - 8 - 5/5 , SHORT - 10 - 6/4</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 7 - 7/3 , SHORT - 13 - 7/3 , SHORT - 11 - 6/6</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -3605,2949 +3600,358 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/+1/%100)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-5/%60)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>140</v>
+        <v>21.92</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
+        <v>-4.3</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 16 - 10/1 , SHORT - 22 - 9/1 , SHORT - 14 - 10/1</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AKSA</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 11/0 , ALT -  - 11/1 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (15g/0/%75)</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="O50" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TRMET</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 15 - 10/19 , SHORT - 15 - 10/6 , SHORT - 11 - 8/3</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%90)</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="O51" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 7 - 7/3 , LONG - 24 - 19/3 , ALT -  - 20/3</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (4g/-4/%70)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="O52" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+LONG - 10 - 4/8 , LONG - 6 - 5/5 , LONG - 5 - 6/4</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (2g/-3/%75)
-S - TP5/20G - %82 / 22 işlem - ADAY (2g/-3/%88)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="G53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N49" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="O49" s="8" t="n">
-        <v>46276</v>
+      <c r="N53" s="7" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="O53" s="8" t="n">
+        <v>46279</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="48" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Hisse</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Düne_Göre_%</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Yarın_Alım</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Puan</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Onaylı_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Aday_Sistem_Sayısı</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Toplam_Öneren_Sistem</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Kodları</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Sistem_Detayı</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Neden</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Engel_Risk</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Son_Fiyat</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Fiyat_Tarihi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>KONTR</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>K-TP5/20G, M-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (14g/-15/%50)
-M - TP5/20G - %90 / 50 işlem - ONAY (14g/-15/%70)</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>3.29999995</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASTOR</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 18/5 , ALT -  - 18/5 , -</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, L-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-5/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (4g/-3/%91)
-R - TP5/20G - %81 / 99 işlem - ADAY (3g/-5/%65)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 52 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>285.25</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-SHORT - 9 - 3/9 , SHORT - 9 - 2/9 , -</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (14g/-7/%57)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>17.86000061</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 11/2 , LONG - 1 - 9/3 , -</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, I-TP5/10G, R-TP2/10G, R-TP5/10G, V-TP2/10G, V-TP5/10G, V-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %90 / 50 işlem - ONAY (11g/-9/%75)
-I - TP5/10G - %61 / 108 işlem - ADAY (3g/+2/%100)
-R - TP2/10G - %84 / 119 işlem - ADAY (2g/0/%95)
-R - TP5/10G - %61 / 137 işlem - ADAY (4g/+1/%100)
-V - TP2/10G - %95 / 21 işlem - ADAY (2g/0/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (2g/0/%89)
-V - TP5/20G - %95 / 20 işlem - ADAY (15g/-13/%0)
-Y - TP5/20G - %73 / 96 işlem - ADAY (10g/-9/%30)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>3.0999999</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MIATK</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>K-TP2/10G, K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>K - TP2/10G - %96 / 49 işlem - ONAY (0g/0/%100)
-K - TP5/10G - %85 / 40 işlem - ONAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 17 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>38.08000183</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 10/1 , LONG - 1 - 10/1 , LONG - 3 - 10/3</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (7g/-5/%73)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>2.95000005</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MGROS</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 4 - 17/4 , LONG - 1 - 21/1 , ALT -  - 23/5</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>E-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %88 / 67 işlem - ONAY (8g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 33 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>542</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/1 , SHORT - 86 - 12/9 , LONG - 6 - 15/2</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (16g/-3/%18)
-I - TP5/20G - %84 / 50 işlem - ADAY (16g/-3/%67)
-Q - TP5/20G - %68 / 69 işlem - ADAY (16g/-3/%55)
-Z - TP5/20G - %75 / 71 işlem - ADAY (2g/-3/%90)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 69 - 12/8 , SHORT - 69 - 14/7 , -</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (8g/-6/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (9g/-6/%75)
-L - TP5/10G - %79 / 42 işlem - ADAY (9g/-6/%56)
-R - TP5/10G - %61 / 137 işlem - ADAY (2g/-2/%90)
-R - TP5/20G - %81 / 99 işlem - ADAY (2g/-2/%85)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 45 hisse / 58 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>62.09999847</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
-LONG - 1 - 33/2 , ALT -  - 86/37 , ALT -  - 61/46</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (7g/-21/%75)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>21.21999931</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 31 - 4/6 , LONG - 29 - 4/6 , LONG - 29 - 4/6</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (1g/-1/%95)
-H - TP5/10G - %70 / 20 işlem - ADAY (1g/-1/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (1g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>11.28999996</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 32/4 , ALT -  - 26/7 , ALT -  - 35/0</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %81 / 99 işlem - ADAY (12g/-5/%50)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 60 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>36.79999924</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CVKMD</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 11/0 , LONG - 136 - 19/12 , -</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (3g/-4/%75)
-I - TP5/10G - %61 / 108 işlem - ADAY (2g/-1/%95)
-I - TP5/20G - %84 / 50 işlem - ADAY (2g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>15.19999981</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 3 - 9/1 , ALT -  - 11/0 , ALT -  - 11/1</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>I-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>I - TP5/10G - %61 / 108 işlem - ADAY (3g/+1/%100)
-Q - TP2/10G - %82 / 103 işlem - ADAY (1g/-1/%95)
-Q - TP5/20G - %68 / 69 işlem - ADAY (1g/-1/%100)
-R - TP5/10G - %61 / 137 işlem - ADAY (9g/-4/%0)
-R - TP5/20G - %81 / 99 işlem - ADAY (16g/-8/%25)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 57 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>26.29999924</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>I-TP5/10G, I-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>I - TP5/10G - %61 / 108 işlem - ADAY (2g/0/%100)
-I - TP5/20G - %84 / 50 işlem - ADAY (2g/0/%100)
-R - TP5/20G - %81 / 99 işlem - ADAY (13g/-11/%25)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 44 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>3.0999999</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 10 - 16/14 , LONG - 7 - 25/8 , UST -  - 1/10</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>U-TP5/20G, V-TP2/10G, V-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (1g/0/%95)
-V - TP2/10G - %95 / 21 işlem - ADAY (1g/0/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (2g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 34 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>72.30000305</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>6.1500001</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 3 - 20/1 , LONG - 5 - 27/6 , LONG - 5 - 4/6</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %88 / 42 işlem - ONAY (1g/-1/%93)
-Z - TP5/10G - %60 / 40 işlem - ADAY (1g/-1/%93)
-Z - TP5/20G - %75 / 71 işlem - ADAY (2g/0/%95)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>94.90000153</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 21 - 14/10 , ALT -  - 18/4 , ALT -  - 16/3</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %61 / 137 işlem - ADAY (3g/+1/%100)
-Y - TP5/20G - %73 / 96 işlem - ADAY (19g/-7/%5)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 70 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>79.94999695</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BRYAT</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 5 - 6/4 , ALT -  - 27/8 , LONG - 30 - 17/8</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %61 / 137 işlem - ADAY (4g/+3/%100)
-Y - TP5/20G - %73 / 96 işlem - ADAY (4g/+3/%100)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 70 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>1703</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>GRSEL</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>I-TP5/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>I - TP5/10G - %61 / 108 işlem - ADAY (2g/+1/%100)
-I - TP5/20G - %84 / 50 işlem - ADAY (2g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 34 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>298.5</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PGSUS</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 17 - 5/5 , LONG - 30 - 5/7 , LONG - 8 - 7/5</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G, Y-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (18g/+1/%100)
-Q - TP5/20G - %68 / 69 işlem - ADAY (18g/+1/%100)
-Y - TP5/10G - %61 / 71 işlem - ADAY (7g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>153.30000305</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TKFEN</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 17 - 11/5 , SHORT - 15 - 12/5 , LONG - 3 - 8/2</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>K-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (12g/-3/%62)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>211.3999939</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 5 - 4/8 , SHORT - 30 - 16/14 , -</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %90 / 50 işlem - ONAY (9g/-2/%80)
-R - TP5/20G - %81 / 99 işlem - ADAY (9g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 49 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>18.79999924</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BRSAN</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 4/19 , UST -  - 4/19 , UST -  - 5/16</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>X-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>X - TP5/20G - %93 / 42 işlem - ONAY (13g/-6/%57)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 34 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>704.5</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 3/12 , UST -  - 2/12 , SHORT - 9 - 3/7</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (14g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>107.80000305</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>HALKB</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-UST -  - 3/24 , UST -  - 4/29 , UST -  - 13/23</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (2g/-1/%91)</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>50.04999924</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>IZENR</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 4 - 11/6 , LONG - 4 - 11/6 , -</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (6g/0/%82)
-L - TP5/10G - %79 / 42 işlem - ADAY (6g/0/%78)</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>7.11999989</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>KCHOL</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 44 - 1/14 , LONG - 79 - 5/14 , SHORT - 2 - 0/15</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (2g/0/%80)
-Z - TP5/20G - %75 / 71 işlem - ADAY (2g/0/%95)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>224.30000305</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 18 - 14/7 , LONG - 4 - 15/2 , LONG - 30 - 4/6</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %88 / 42 işlem - ONAY (1g/-2/%93)
-U - TP5/20G - %74 / 74 işlem - ADAY (9g/0/%90)
-Z - TP5/10G - %60 / 40 işlem - ADAY (9g/0/%22)
-Z - TP5/20G - %75 / 71 işlem - ADAY (9g/0/%60)</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="n">
-        <v>2.04999995</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AEFES</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 4 - 4/6 , LONG - 8 - 15/10 , LONG - 6 - 16/9</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (2g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>19.57999992</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ENKAI</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 17 - 22/10 , LONG - 18 - 5/7 , LONG - 17 - 2/7</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (1g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>OYAKC</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 5 - 6/5 , SHORT - 11 - 5/5 , SHORT - 9 - 4/7</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (11g/-4/%80)</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="n">
-        <v>22.15999985</v>
-      </c>
-      <c r="O34" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SOKM</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 43 - 5/22 , LONG - 43 - 5/22 , UST -  - 1/11</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="n">
-        <v>60.59999847</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>GSRAY</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 9 - 9/2 , SHORT - 10 - 10/3 , SHORT - 10 - 10/3</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/-1/%100)
-Q - TP5/20G - %68 / 69 işlem - ADAY (1g/-1/%100)
-R - TP2/10G - %84 / 119 işlem - ADAY (1g/-1/%95)
-R - TP5/10G - %61 / 137 işlem - ADAY (1g/-1/%95)</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 64 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="n">
-        <v>1.01999998</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 8 - 5/7 , LONG - 4 - 6/4 , LONG - 3 - 8/3</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1/%43)</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="n">
-        <v>101.59999847</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>GARAN</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 29 - 5/7 , LONG - 37 - 6/6 , LONG - 74 - 10/10</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (16g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="n">
-        <v>133.3999939</v>
-      </c>
-      <c r="O38" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (1g/0/%100)
-S - TP5/20G - %82 / 22 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="n">
-        <v>37.24000168</v>
-      </c>
-      <c r="O39" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ENJSA</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 41 - 11/13 , SHORT - 1 - 1/8 , SHORT - 1 - 1/8</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (1g/-1/%85)
-U - TP5/20G - %74 / 74 işlem - ADAY (9g/-1/%90)</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="n">
-        <v>117</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 9 - 5/5 , SHORT - 9 - 5/5 , SHORT - 9 - 5/5</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (10g/-3/%95)</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N41" s="7" t="n">
-        <v>21.63999939</v>
-      </c>
-      <c r="O41" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ECILC</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 5 - 7/3 , LONG - 22 - 18/3 , ALT -  - 20/2</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP5/20G - %73 / 96 işlem - ADAY (2g/-3/%85)</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="n">
-        <v>71.59999847</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BTCIM</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 47/33 , LONG - 5 - 24/8 , LONG - 2 - 7/3</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %61 / 137 işlem - ADAY (3g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="n">
-        <v>3.92000008</v>
-      </c>
-      <c r="O43" s="8" t="n">
-        <v>46275</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:O43"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6573,72 +3977,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Strateji</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Ana_Aile</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Profil</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Islem</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Basari_Pct</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Ort_Getiri_Pct</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Ort_Bekleme_Gun</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Portfoy_Getiri_Pct</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Benzersiz_Hisse</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Benzersiz_Giris_Gunu</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Formul</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Parametreler</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Gecti_85_40</t>
         </is>
@@ -6668,16 +4072,16 @@
       <c r="E2" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="11" t="n">
         <v>87.67123287671232</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="11" t="n">
         <v>1.091845009198165</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="11" t="n">
         <v>3.643835616438356</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="11" t="n">
         <v>24.40911840921945</v>
       </c>
       <c r="J2" s="5" t="n">
@@ -6724,16 +4128,16 @@
       <c r="E3" s="5" t="n">
         <v>179</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="11" t="n">
         <v>69.27374301675978</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="11" t="n">
         <v>1.692906525012615</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="11" t="n">
         <v>10.8268156424581</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="11" t="n">
         <v>-10.07451841902579</v>
       </c>
       <c r="J3" s="5" t="n">
@@ -6780,16 +4184,16 @@
       <c r="E4" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="11" t="n">
         <v>92.15686274509804</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="11" t="n">
         <v>1.535365337628641</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="11" t="n">
         <v>3.588235294117647</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="11" t="n">
         <v>40.64175143303033</v>
       </c>
       <c r="J4" s="5" t="n">
@@ -6839,13 +4243,13 @@
       <c r="F5" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="11" t="n">
         <v>3.338603886774568</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="11" t="n">
         <v>5.9</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="11" t="n">
         <v>30.92879569495881</v>
       </c>
       <c r="J5" s="5" t="n">
@@ -6895,13 +4299,13 @@
       <c r="F6" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="11" t="n">
         <v>4.208405838146707</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="11" t="n">
         <v>7.7</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="11" t="n">
         <v>44.08348773053212</v>
       </c>
       <c r="J6" s="5" t="n">
@@ -6948,16 +4352,16 @@
       <c r="E7" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>85.9375</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>0.4383224057379628</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="11" t="n">
         <v>4.15625</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="11" t="n">
         <v>8.845387974022433</v>
       </c>
       <c r="J7" s="5" t="n">
@@ -7004,16 +4408,16 @@
       <c r="E8" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>60.55045871559633</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="11" t="n">
         <v>1.543551578295935</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="11" t="n">
         <v>6.495412844036697</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="11" t="n">
         <v>29.12146269092428</v>
       </c>
       <c r="J8" s="5" t="n">
@@ -7060,16 +4464,16 @@
       <c r="E9" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <v>82.08955223880596</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="11" t="n">
         <v>2.45818280260672</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="11" t="n">
         <v>10.02985074626866</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="11" t="n">
         <v>18.35020892327415</v>
       </c>
       <c r="J9" s="5" t="n">
@@ -7116,16 +4520,16 @@
       <c r="E10" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>95.91836734693878</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="11" t="n">
         <v>1.838447929308523</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="11" t="n">
         <v>1.591836734693878</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="11" t="n">
         <v>64.06688536247781</v>
       </c>
       <c r="J10" s="5" t="n">
@@ -7175,13 +4579,13 @@
       <c r="F11" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <v>3.586870312855289</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="11" t="n">
         <v>115.6983709467846</v>
       </c>
       <c r="J11" s="5" t="n">
@@ -7228,16 +4632,16 @@
       <c r="E12" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>90.19607843137256</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>3.573764506811416</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="11" t="n">
         <v>6.235294117647059</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="11" t="n">
         <v>152.8572199280838</v>
       </c>
       <c r="J12" s="5" t="n">
@@ -7290,10 +4694,10 @@
       <c r="G13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="11" t="n">
         <v>1.865384615384615</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="11" t="n">
         <v>123.0120060251001</v>
       </c>
       <c r="J13" s="5" t="n">
@@ -7340,16 +4744,16 @@
       <c r="E14" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="11" t="n">
         <v>76.74418604651163</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="11" t="n">
         <v>3.153776633785343</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="11" t="n">
         <v>4.162790697674419</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="11" t="n">
         <v>148.3657178501799</v>
       </c>
       <c r="J14" s="5" t="n">
@@ -7396,16 +4800,16 @@
       <c r="E15" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="11" t="n">
         <v>90.90909090909091</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="11" t="n">
         <v>3.896170479805682</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="11" t="n">
         <v>5.818181818181818</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="11" t="n">
         <v>134.8453792690374</v>
       </c>
       <c r="J15" s="5" t="n">
@@ -7452,16 +4856,16 @@
       <c r="E16" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="11" t="n">
         <v>98.33333333333333</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="11" t="n">
         <v>1.86266250815524</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="11" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="11" t="n">
         <v>39.36576444231839</v>
       </c>
       <c r="J16" s="5" t="n">
@@ -7511,13 +4915,13 @@
       <c r="F17" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="11" t="n">
         <v>2.119612978858227</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="11" t="n">
         <v>5.533333333333333</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="11" t="n">
         <v>-9.569928550174378</v>
       </c>
       <c r="J17" s="5" t="n">
@@ -7564,16 +4968,16 @@
       <c r="E18" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="11" t="n">
         <v>89.09090909090909</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="11" t="n">
         <v>3.577493268682341</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="11" t="n">
         <v>7.236363636363636</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="11" t="n">
         <v>16.19253686944791</v>
       </c>
       <c r="J18" s="5" t="n">
@@ -7620,16 +5024,16 @@
       <c r="E19" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="11" t="n">
         <v>96.55172413793103</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="11" t="n">
         <v>1.759420035738506</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="H19" s="11" t="n">
         <v>2.206896551724138</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="11" t="n">
         <v>87.78857601793675</v>
       </c>
       <c r="J19" s="5" t="n">
@@ -7676,16 +5080,16 @@
       <c r="E20" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="11" t="n">
         <v>78.78787878787878</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="11" t="n">
         <v>2.847412976091975</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="11" t="n">
         <v>4.181818181818182</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="11" t="n">
         <v>71.51714451317355</v>
       </c>
       <c r="J20" s="5" t="n">
@@ -7732,16 +5136,16 @@
       <c r="E21" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="11" t="n">
         <v>88.88888888888889</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="11" t="n">
         <v>3.410953131837676</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="11" t="n">
         <v>5.666666666666667</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="11" t="n">
         <v>105.704688458288</v>
       </c>
       <c r="J21" s="5" t="n">
@@ -7788,16 +5192,16 @@
       <c r="E22" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="11" t="n">
         <v>81.55339805825243</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="11" t="n">
         <v>0.9040056201490013</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" s="11" t="n">
         <v>4.766990291262136</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="11" t="n">
         <v>13.51481346674499</v>
       </c>
       <c r="J22" s="5" t="n">
@@ -7844,16 +5248,16 @@
       <c r="E23" s="5" t="n">
         <v>203</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F23" s="11" t="n">
         <v>69.95073891625616</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="11" t="n">
         <v>1.328564835412801</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="H23" s="11" t="n">
         <v>10.51724137931035</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="I23" s="11" t="n">
         <v>10.31065008382135</v>
       </c>
       <c r="J23" s="5" t="n">
@@ -7900,16 +5304,16 @@
       <c r="E24" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="11" t="n">
         <v>84.03361344537815</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="11" t="n">
         <v>0.8723884204925718</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="H24" s="11" t="n">
         <v>3.857142857142857</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" s="11" t="n">
         <v>21.413730878954</v>
       </c>
       <c r="J24" s="5" t="n">
@@ -7956,16 +5360,16 @@
       <c r="E25" s="5" t="n">
         <v>138</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="11" t="n">
         <v>60.14492753623188</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="11" t="n">
         <v>1.524903733436686</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="H25" s="11" t="n">
         <v>6.528985507246377</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="I25" s="11" t="n">
         <v>-1.165874385992138</v>
       </c>
       <c r="J25" s="5" t="n">
@@ -8012,16 +5416,16 @@
       <c r="E26" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>80.3921568627451</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="11" t="n">
         <v>2.437078703629713</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="H26" s="11" t="n">
         <v>9.549019607843137</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" s="11" t="n">
         <v>80.77588286830797</v>
       </c>
       <c r="J26" s="5" t="n">
@@ -8071,13 +5475,13 @@
       <c r="F27" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="11" t="n">
         <v>1.460171634530557</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="H27" s="11" t="n">
         <v>2.4</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="I27" s="11" t="n">
         <v>38.38169394790141</v>
       </c>
       <c r="J27" s="5" t="n">
@@ -8124,16 +5528,16 @@
       <c r="E28" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="11" t="n">
         <v>78.26086956521739</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="11" t="n">
         <v>3.282469851681598</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="H28" s="11" t="n">
         <v>4.869565217391305</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="I28" s="11" t="n">
         <v>59.66864125825173</v>
       </c>
       <c r="J28" s="5" t="n">
@@ -8180,16 +5584,16 @@
       <c r="E29" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="11" t="n">
         <v>81.81818181818181</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="11" t="n">
         <v>1.599054318607395</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="H29" s="11" t="n">
         <v>7.045454545454546</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="I29" s="11" t="n">
         <v>1.097127327046299</v>
       </c>
       <c r="J29" s="5" t="n">
@@ -8236,16 +5640,16 @@
       <c r="E30" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="11" t="n">
         <v>86.27450980392157</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="G30" s="11" t="n">
         <v>0.876653028687471</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="H30" s="11" t="n">
         <v>3.549019607843137</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="I30" s="11" t="n">
         <v>11.72108628423414</v>
       </c>
       <c r="J30" s="5" t="n">
@@ -8295,13 +5699,13 @@
       <c r="F31" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="11" t="n">
         <v>1.561522779858157</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="H31" s="11" t="n">
         <v>6.164285714285715</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="I31" s="11" t="n">
         <v>11.39100532375073</v>
       </c>
       <c r="J31" s="5" t="n">
@@ -8348,16 +5752,16 @@
       <c r="E32" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="11" t="n">
         <v>77.34375</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="11" t="n">
         <v>1.367327019729346</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="H32" s="11" t="n">
         <v>9.0859375</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="I32" s="11" t="n">
         <v>0.5762422699556957</v>
       </c>
       <c r="J32" s="5" t="n">
@@ -8404,16 +5808,16 @@
       <c r="E33" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="11" t="n">
         <v>75.25773195876289</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="G33" s="11" t="n">
         <v>0.4213810555920299</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="H33" s="11" t="n">
         <v>4.484536082474227</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="I33" s="11" t="n">
         <v>42.75730243099525</v>
       </c>
       <c r="J33" s="5" t="n">
@@ -8460,16 +5864,16 @@
       <c r="E34" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="11" t="n">
         <v>74.32432432432432</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="11" t="n">
         <v>1.750488557981346</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H34" s="11" t="n">
         <v>10.97297297297297</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="I34" s="11" t="n">
         <v>50.75453283804112</v>
       </c>
       <c r="J34" s="5" t="n">
@@ -8516,16 +5920,16 @@
       <c r="E35" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="11" t="n">
         <v>95.23809523809524</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="11" t="n">
         <v>1.413361333617355</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="H35" s="11" t="n">
         <v>2.809523809523809</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="I35" s="11" t="n">
         <v>37.30548787582775</v>
       </c>
       <c r="J35" s="5" t="n">
@@ -8575,13 +5979,13 @@
       <c r="F36" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G36" s="11" t="n">
         <v>2.442847651787989</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="H36" s="11" t="n">
         <v>5.15</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I36" s="11" t="n">
         <v>38.28659541177836</v>
       </c>
       <c r="J36" s="5" t="n">
@@ -8631,13 +6035,13 @@
       <c r="F37" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G37" s="11" t="n">
         <v>3.330815662507273</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="H37" s="11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="I37" s="11" t="n">
         <v>27.01916763269523</v>
       </c>
       <c r="J37" s="5" t="n">
@@ -8684,16 +6088,16 @@
       <c r="E38" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="11" t="n">
         <v>97.82608695652173</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="11" t="n">
         <v>1.924611088950938</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="H38" s="11" t="n">
         <v>1.695652173913043</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I38" s="11" t="n">
         <v>82.04682460124249</v>
       </c>
       <c r="J38" s="5" t="n">
@@ -8740,16 +6144,16 @@
       <c r="E39" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="11" t="n">
         <v>81.81818181818181</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="11" t="n">
         <v>2.943899674461814</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H39" s="11" t="n">
         <v>4.068181818181818</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I39" s="11" t="n">
         <v>54.3255919731962</v>
       </c>
       <c r="J39" s="5" t="n">
@@ -8796,16 +6200,16 @@
       <c r="E40" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="11" t="n">
         <v>93.02325581395348</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="11" t="n">
         <v>3.603444578558364</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="H40" s="11" t="n">
         <v>5.13953488372093</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="I40" s="11" t="n">
         <v>112.1618675988657</v>
       </c>
       <c r="J40" s="5" t="n">
@@ -8852,16 +6256,16 @@
       <c r="E41" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="11" t="n">
         <v>85.8974358974359</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G41" s="11" t="n">
         <v>0.7885766637045726</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="H41" s="11" t="n">
         <v>3.653846153846154</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I41" s="11" t="n">
         <v>25.22705608291336</v>
       </c>
       <c r="J41" s="5" t="n">
@@ -8908,16 +6312,16 @@
       <c r="E42" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F42" s="11" t="n">
         <v>60.56338028169014</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="11" t="n">
         <v>0.8093717118089521</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="H42" s="11" t="n">
         <v>6.676056338028169</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="I42" s="11" t="n">
         <v>34.72039972996088</v>
       </c>
       <c r="J42" s="5" t="n">
@@ -8964,16 +6368,16 @@
       <c r="E43" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F43" s="11" t="n">
         <v>71.42857142857143</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G43" s="11" t="n">
         <v>1.309494133631699</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="H43" s="11" t="n">
         <v>10.23469387755102</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="I43" s="11" t="n">
         <v>44.14991894463613</v>
       </c>
       <c r="J43" s="5" t="n">
@@ -9020,16 +6424,16 @@
       <c r="E44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F44" s="11" t="n">
         <v>88.37209302325581</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G44" s="11" t="n">
         <v>1.031530880120439</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="H44" s="11" t="n">
         <v>3.441860465116279</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="I44" s="11" t="n">
         <v>11.9994303250593</v>
       </c>
       <c r="J44" s="5" t="n">
@@ -9076,16 +6480,16 @@
       <c r="E45" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F45" s="11" t="n">
         <v>74.64788732394366</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="G45" s="11" t="n">
         <v>2.457478789688865</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="H45" s="11" t="n">
         <v>10.64788732394366</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="I45" s="11" t="n">
         <v>20.29378703244169</v>
       </c>
       <c r="J45" s="5" t="n">

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-3</v>
+        <v>-4.8</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 11 - 8/4 , SHORT - 11 - 8/4 , -</t>
+SHORT - 11 - 10/2 , SHORT - 11 - 10/3 , -</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-12/%50)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-13/%50)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>16.96</v>
+        <v>16.65</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46279</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 18/4 , ALT -  - 18/4 , -</t>
+ALT -  - 18/5 , ALT -  - 18/5 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -665,10 +665,10 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-5/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (6g/-3/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-5/%65)
-R - TP5/20G - %80 / 102 işlem - ADAY (5g/-5/%60)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-6/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (6g/-4/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-5/%50)
+R - TP5/20G - %80 / 102 işlem - ADAY (5g/-6/%60)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>285.25</v>
+        <v>284</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46279</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>38.7</v>
+        <v>38.74</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46279</v>
@@ -755,11 +755,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -773,8 +773,8 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 6 - 11/6 , LONG - 6 - 11/6 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 1 - 12/0 , LONG - 3 - 10/2 , -</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
@@ -784,35 +784,41 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+          <t>M-TP5/20G, E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G, V-TP2/10G, V-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (8g/-2/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (8g/-2/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-16/%15)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (13g/-11/%60)
+E - TP5/20G - %69 / 179 işlem - ADAY (5g/0/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (11g/-10/%20)
+R - TP2/10G - %84 / 119 işlem - ADAY (4g/-2/%85)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-1/%80)
+V - TP2/10G - %95 / 21 işlem - ADAY (4g/-2/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (4g/-2/%75)
+Y - TP5/20G - %71 / 98 işlem - ADAY (12g/-11/%15)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 72 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>7</v>
+        <v>3.04</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46279</v>
@@ -821,11 +827,11 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.3</v>
+        <v>-6</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -839,52 +845,46 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 13/0 , LONG - 3 - 11/1 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 71 - 17/4 , SHORT - 71 - 19/3 , -</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M-TP5/20G, E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G, V-TP2/10G, V-TP5/10G, Y-TP5/20G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (13g/-11/%60)
-E - TP5/20G - %69 / 179 işlem - ADAY (5g/-1/%95)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-1/%90)
-Q - TP5/20G - %70 / 203 işlem - ADAY (11g/-11/%10)
-R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-2/%70)
-V - TP2/10G - %95 / 21 işlem - ADAY (4g/-3/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (4g/-3/%75)
-Y - TP5/20G - %71 / 98 işlem - ADAY (12g/-11/%15)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (11g/-11/%75)
+R - TP5/10G - %60 / 138 işlem - ADAY (4g/-8/%35)
+R - TP5/20G - %80 / 102 işlem - ADAY (4g/-8/%60)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 72 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>3.02</v>
+        <v>58.45</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46279</v>
@@ -893,11 +893,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-1.3</v>
+        <v>0.3</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -912,93 +912,27 @@
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 71 - 12/8 , SHORT - 71 - 14/7 , -</t>
+LONG - 5 - 7/3 , LONG - 5 - 7/3 , LONG - 2 - 10/1</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
         <v>55</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (11g/-7/%75)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%75)
-R - TP5/20G - %80 / 102 işlem - ADAY (4g/-3/%85)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 5 - 7/3 , LONG - 5 - 7/3 , LONG - 2 - 10/1</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/+2/%100)
 I - TP5/10G - %61 / 109 işlem - ADAY (5g/+2/%100)
@@ -1007,18 +941,83 @@
 R - TP5/20G - %80 / 102 işlem - ADAY (18g/-7/%25)</t>
         </is>
       </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EUPWR</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 20/6 , ALT -  - 30/7 , -</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-1/%92)
+L - TP5/10G - %77 / 43 işlem - ADAY (1g/-1/%93)</t>
+        </is>
+      </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>26.6</v>
+        <v>72.3</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46279</v>
@@ -1027,11 +1026,11 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1045,39 +1044,36 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 3 - 10/0 , LONG - 3 - 10/0 , LONG - 5 - 10/3</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>H-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/+1/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/+1/%100)
-I - TP5/20G - %82 / 67 işlem - ADAY (4g/+1/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/+1/%100)
-R - TP5/20G - %80 / 102 işlem - ADAY (15g/-10/%20)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (9g/-6/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%95)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 76 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1086,7 +1082,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46279</v>
@@ -1095,30 +1091,30 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-2.8</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>İZLEME</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 21/7 , ALT -  - 32/8 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 19 - 2/7 , LONG - 32 - 3/9 , LONG - 10 - 4/8</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>1</v>
@@ -1131,27 +1127,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-3/%92)
-L - TP5/10G - %77 / 43 işlem - ADAY (1g/-3/%93)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (0g/0/%100)
+Z - TP5/20G - %75 / 71 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok</t>
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>71.34999999999999</v>
+        <v>157.3</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46279</v>
@@ -1160,11 +1156,11 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.4</v>
+        <v>0.4</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1177,94 +1173,29 @@
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 3 - 10/0 , LONG - 3 - 10/0 , LONG - 5 - 10/3</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (9g/-6/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%95)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 76 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
 LONG - 2 - 10/1 , SHORT - 88 - 10/10 , LONG - 8 - 14/3</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F11" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-2/%55)
 I - TP5/20G - %82 / 67 işlem - ADAY (18g/-2/%54)
@@ -1272,75 +1203,139 @@
 Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N12" s="7" t="n">
-        <v>80.55</v>
-      </c>
-      <c r="O12" s="8" t="n">
+      <c r="N11" s="7" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="O11" s="8" t="n">
         <v>46279</v>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>TSKB</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B12" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
 LONG - 33 - 3/7 , LONG - 31 - 3/7 , LONG - 31 - 3/7</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/+1/%100)
 H - TP5/10G - %70 / 20 işlem - ADAY (3g/+1/%100)
 H - TP5/20G - %85 / 20 işlem - ADAY (3g/+1/%100)</t>
         </is>
       </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 29/2 , ALT -  - 24/5 , LONG - 3 - 33/2</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (14g/-3/%40)</t>
+        </is>
+      </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1349,7 +1344,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>11.52</v>
+        <v>37.44</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46279</v>
@@ -1358,11 +1353,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1377,34 +1372,35 @@
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 30/2 , ALT -  - 24/6 , LONG - 3 - 34/1</t>
+ALT -  - 24/1 , LONG - 7 - 28/6 , LONG - 7 - 5/5</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (14g/-4/%40)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-1/%92)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1413,7 +1409,7 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>37.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46279</v>
@@ -1422,11 +1418,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-1.3</v>
+        <v>-5.3</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1440,36 +1436,37 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 5 - 21/1 , LONG - 7 - 27/6 , LONG - 7 - 5/5</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 17/6 , ALT -  - 17/6 , -</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-1/%92)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%85)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (5g/-9/%55)
+I - TP5/10G - %61 / 109 işlem - ADAY (4g/-7/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-9/%80)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1478,7 +1475,7 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>94.59999999999999</v>
+        <v>14.28</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46279</v>
@@ -1487,11 +1484,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3</v>
+        <v>-1.1</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1505,94 +1502,28 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 15/4 , ALT -  - 15/4 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (5g/-7/%55)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/-5/%70)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-7/%80)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GRSEL</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/0/%85)
 I - TP5/10G - %61 / 109 işlem - ADAY (4g/0/%80)
@@ -1600,9 +1531,74 @@
 Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-8/%20)</t>
         </is>
       </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>295.25</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 75/59 , ALT -  - 103/50 , ALT -  - 75/59</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %77 / 43 işlem - ADAY (9g/-29/%38)
+Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-43/%10)</t>
+        </is>
+      </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 73 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1611,7 +1607,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>294.75</v>
+        <v>19.09</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46279</v>
@@ -1620,11 +1616,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-5.9</v>
+        <v>-1.9</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1638,45 +1634,46 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 71/54 , ALT -  - 98/46 , ALT -  - 71/54</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 23 - 16/9 , ALT -  - 19/6 , ALT -  - 18/5</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>L-TP5/10G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %77 / 43 işlem - ADAY (9g/-27/%38)
-Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-41/%10)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-2/%85)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-1/%90)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 73 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>19.61</v>
+        <v>78.5</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46279</v>
@@ -1685,11 +1682,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1703,46 +1700,45 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 23 - 16/9 , ALT -  - 19/6 , ALT -  - 18/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-2/%95)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-1/%90)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (3g/-6/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (3g/-6/%89)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>78.65000000000001</v>
+        <v>35.1</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46279</v>
@@ -1751,11 +1747,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.9</v>
+        <v>-3.7</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1780,25 +1776,24 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (3g/-4/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (3g/-4/%89)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/-7/%35)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1807,7 +1802,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>35.68</v>
+        <v>7.9</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46279</v>
@@ -1816,11 +1811,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1835,7 +1830,7 @@
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+SHORT - 61 - 8/4 , SHORT - 63 - 7/5 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -1857,7 +1852,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/-3/%65)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%95)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1871,7 +1866,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>8.18</v>
+        <v>296.25</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46279</v>
@@ -1880,11 +1875,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1898,8 +1893,8 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 61 - 8/5 , SHORT - 63 - 7/5 , ALT -  - 13/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+-</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1921,7 +1916,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%95)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-2/%55)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1935,7 +1930,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>297</v>
+        <v>6.18</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46279</v>
@@ -1944,11 +1939,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1967,7 +1962,7 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
@@ -1980,17 +1975,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-2/%65)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -1999,7 +1994,7 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>6.21</v>
+        <v>232.69999695</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46279</v>
@@ -2008,11 +2003,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2026,12 +2021,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 66 - 12/4 , SHORT - 143 - 28/5 , LONG - 7 - 11/1</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0</v>
@@ -2049,7 +2044,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/+1/%100)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-4/%45)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2059,11 +2054,11 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>232.69999695</v>
+        <v>162.8</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>46279</v>
@@ -2072,11 +2067,11 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -2091,7 +2086,7 @@
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 66 - 12/4 , SHORT - 143 - 28/5 , LONG - 7 - 11/1</t>
+LONG - 6 - 16/5 , LONG - 3 - 21/1 , ALT -  - 22/4</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2113,7 +2108,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-4/%45)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%20)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2127,7 +2122,7 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>162.8</v>
+        <v>541</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46279</v>
@@ -2136,11 +2131,11 @@
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2154,44 +2149,49 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 6 - 16/5 , LONG - 3 - 20/1 , ALT -  - 22/4</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 0, TOPLAM 4, İZLE
+LONG - 12 - 15/15 , LONG - 11 - 18/13 , SHORT - 1 - 0/9</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-4/%25)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
+Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
+U - TP5/20G - %74 / 74 işlem - ADAY (3g/0/%100)
+V - TP2/10G - %95 / 21 işlem - ADAY (3g/0/%100)
+V - TP5/10G - %75 / 20 işlem - ADAY (4g/+2/%100)
+Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>543</v>
+        <v>72.7</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46279</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 3 - 5/11 , UST -  - 1/16 , SHORT - 2 - 3/12</t>
+SHORT - 3 - 5/10 , UST -  - 1/15 , SHORT - 2 - 3/12</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>46279</v>
@@ -2328,11 +2328,11 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2346,44 +2346,44 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 19 - 5/5 , LONG - 32 - 6/6 , LONG - 10 - 7/5</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
+SHORT - 1 - 1/8 , SHORT - 1 - 1/8 , SHORT - 3 - 2/7</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Y-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/10G - %61 / 71 işlem - ADAY (9g/+1/%100)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (1g/-2/%95)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>153</v>
+        <v>20.6</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>46279</v>
@@ -2392,11 +2392,11 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1.4</v>
+        <v>-2.2</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -2410,47 +2410,44 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 6 - 9/19 , LONG - 7 - 8/20 , UST -  - 8/16</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+UST -  - 1/10 , UST -  - 0/10 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X-TP5/20G, Y-TP2/10G, X-TP5/10G, Y-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (2g/+3/%100)
-Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
-X - TP5/10G - %82 / 44 işlem - ADAY (2g/+3/%100)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/+3/%100)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-2/%50)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi, Y: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 33 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>2.86</v>
+        <v>105.9</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46279</v>
@@ -2459,11 +2456,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-2.3</v>
+        <v>-5.4</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2477,47 +2474,44 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL -1, XU030 0, TOPLAM -1, ALMA
-LONG - 12 - 18/13 , LONG - 11 - 21/11 , SHORT - 1 - 2/7</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 1 - 3/19 , SHORT - 1 - 2/24 , UST -  - 7/18</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>L-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/-2/%100)
-U - TP5/20G - %74 / 74 işlem - ADAY (3g/-2/%85)
-V - TP2/10G - %95 / 21 işlem - ADAY (3g/-2/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (4g/0/%75)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-7/%82)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>71</v>
+        <v>47.32</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46279</v>
@@ -2526,11 +2520,11 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2544,44 +2538,46 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-UST -  - 1/10 , UST -  - 1/10 , SHORT - 11 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 6 - 13/4 , LONG - 6 - 13/4 , -</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-1/%50)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (8g/-4/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (8g/-4/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-18/%15)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>106.3</v>
+        <v>6.86</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>46279</v>
@@ -2590,11 +2586,11 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -2608,44 +2604,48 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 1 - 0/9 , SHORT - 1 - 0/9 , SHORT - 3 - 1/9</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 0, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (1g/0/%95)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-1/%85)
+I - TP5/10G - %61 / 109 işlem - ADAY (4g/-1/%80)
+I - TP5/20G - %82 / 67 işlem - ADAY (4g/-1/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%95)
+R - TP5/20G - %80 / 102 işlem - ADAY (15g/-12/%20)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>20.9</v>
+        <v>3.07</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46279</v>
@@ -2654,11 +2654,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2671,102 +2671,103 @@
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 1 - 2/20 , SHORT - 1 - 1/25 , UST -  - 8/18</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-6/%82)</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="n">
-        <v>47.82</v>
-      </c>
-      <c r="O34" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
 LONG - 20 - 14/7 , LONG - 6 - 15/2 , LONG - 32 - 5/5</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="6" t="n">
+      <c r="G34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I34" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-2/%92)
 U - TP5/20G - %74 / 74 işlem - ADAY (11g/-1/%85)
 Z - TP5/20G - %75 / 71 işlem - ADAY (11g/-1/%55)</t>
         </is>
       </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 19 - 8/8 , SHORT - 17 - 9/7 , LONG - 5 - 5/5</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>K-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %90 / 51 işlem - ONAY (14g/-1/%63)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/+3/%100)</t>
+        </is>
+      </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 75 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -2775,7 +2776,7 @@
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>2.04</v>
+        <v>216.6</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46279</v>
@@ -2784,63 +2785,62 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 15 - 25/7 , LONG - 20 - 7/5 , LONG - 19 - 4/6</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 19 - 8/8 , SHORT - 17 - 9/7 , LONG - 5 - 5/5</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="H36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>K-TP5/20G, Q-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %90 / 51 işlem - ONAY (14g/0/%63)
-Q - TP5/20G - %70 / 203 işlem - ADAY (6g/+3/%100)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (3g/-1/%90)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 75 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>217.4</v>
+        <v>89.05</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46279</v>
@@ -2849,11 +2849,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -2867,8 +2867,8 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 15 - 23/9 , LONG - 20 - 5/7 , LONG - 19 - 2/7</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
+LONG - 31 - 5/7 , LONG - 39 - 6/6 , LONG - 76 - 10/10</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (3g/0/%100)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (18g/+1/%100)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>90.7</v>
+        <v>133.8</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46279</v>
@@ -2913,11 +2913,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2931,8 +2931,8 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 31 - 4/7 , LONG - 39 - 5/7 , LONG - 76 - 9/11</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 46 - 1/14 , LONG - 81 - 5/14 , SHORT - 4 - 0/15</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2942,33 +2942,34 @@
         <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (18g/+2/%100)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (4g/0/%100)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%100)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>134.6</v>
+        <v>225.3</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46279</v>
@@ -2977,11 +2978,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2995,45 +2996,45 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 46 - 1/14 , LONG - 81 - 5/14 , SHORT - 4 - 0/15</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 9 - 6/4 , LONG - 9 - 6/4 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (4g/0/%100)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%100)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>225.4</v>
+        <v>52.25</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46279</v>
@@ -3042,11 +3043,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-2.3</v>
+        <v>-0.5</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3061,35 +3062,34 @@
       <c r="E40" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 9 - 5/5 , LONG - 9 - 5/5 , SHORT - 11 - 5/5</t>
+SHORT - 11 - 5/5 , SHORT - 11 - 5/5 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-2/%80)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-2/%70)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>52.4</v>
+        <v>21.78</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>46279</v>
@@ -3107,11 +3107,11 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 11 - 5/5 , SHORT - 11 - 5/5 , SHORT - 11 - 5/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 6 - 3/6 , LONG - 10 - 14/10 , LONG - 8 - 15/10</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -3143,26 +3143,26 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/+2/%100)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>21.74</v>
+        <v>19.69</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46279</v>
@@ -3171,11 +3171,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-0.2</v>
+        <v>-4.5</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3190,34 +3190,35 @@
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 6 - 3/6 , LONG - 10 - 14/10 , LONG - 8 - 15/10</t>
+SHORT - 1 - 4/8 , LONG - 25 - 13/11 , SHORT - 1 - 3/7</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
         <v>11</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/+2/%100)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-5/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
@@ -3226,7 +3227,7 @@
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>19.71</v>
+        <v>286.25</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46279</v>
@@ -3235,11 +3236,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-2.8</v>
+        <v>-1</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3254,35 +3255,37 @@
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 1 - 2/10 , LONG - 25 - 11/12 , SHORT - 1 - 1/9</t>
+SHORT - 11 - 9/1 , SHORT - 12 - 10/3 , SHORT - 12 - 10/3</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>11</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (3g/-1/%95)
+Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-1/%95)
+R - TP2/10G - %84 / 119 işlem - ADAY (3g/-1/%90)
+R - TP5/10G - %60 / 138 işlem - ADAY (3g/-1/%100)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3291,7 +3294,7 @@
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>291.25</v>
+        <v>1.02</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46279</v>
@@ -3300,11 +3303,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3319,7 +3322,7 @@
       <c r="E44" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 11 - 9/1 , SHORT - 12 - 10/3 , SHORT - 12 - 10/3</t>
+LONG - 43 - 14/10 , SHORT - 3 - 4/6 , SHORT - 3 - 4/6</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -3329,27 +3332,26 @@
         <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (3g/-2/%95)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-2/%90)
-R - TP2/10G - %84 / 119 işlem - ADAY (3g/-2/%90)
-R - TP5/10G - %60 / 138 işlem - ADAY (3g/-2/%95)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (1g/-2/%65)
+U - TP2/10G - %75 / 97 işlem - ADAY (3g/-3/%70)
+U - TP5/20G - %74 / 74 işlem - ADAY (11g/-3/%85)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -3358,7 +3360,7 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>1.01</v>
+        <v>114.5</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46279</v>
@@ -3367,11 +3369,11 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-1.8</v>
+        <v>-4.3</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3385,8 +3387,8 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 43 - 13/11 , SHORT - 3 - 4/6 , SHORT - 3 - 3/7</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+ALT -  - 52/38 , LONG - 7 - 28/6 , LONG - 4 - 10/0</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -3403,19 +3405,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (1g/-2/%95)
-U - TP2/10G - %75 / 97 işlem - ADAY (3g/-3/%60)
-U - TP5/20G - %74 / 74 işlem - ADAY (11g/-2/%85)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-19/%10)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-22/%0)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-3/%65)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 92 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -3424,7 +3426,7 @@
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>115.2</v>
+        <v>3.74</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46279</v>
@@ -3433,11 +3435,11 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3451,37 +3453,36 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-ALT -  - 49/35 , LONG - 7 - 25/7 , LONG - 4 - 8/2</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
+UST -  - 6/15 , LONG - 45 - 6/21 , SHORT - 1 - 0/9</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, R-TP5/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-17/%10)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-20/%0)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-1/%90)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (1g/-2/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (3g/0/%90)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 92 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -3490,7 +3491,7 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>3.83</v>
+        <v>60.25</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46279</v>
@@ -3499,11 +3500,11 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-0.5</v>
+        <v>-2.2</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3517,8 +3518,8 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-UST -  - 7/16 , LONG - 45 - 5/22 , UST -  - 1/10</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 7 - 7/3 , SHORT - 13 - 7/3 , SHORT - 11 - 6/6</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
@@ -3528,25 +3529,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (1g/0/%100)
-U - TP5/20G - %74 / 74 işlem - ADAY (3g/+1/%100)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-6/%60)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>61.1</v>
+        <v>21.82</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46279</v>
@@ -3564,11 +3564,11 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-1.8</v>
+        <v>-5.5</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3582,8 +3582,8 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 7 - 7/3 , SHORT - 13 - 7/3 , SHORT - 11 - 6/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+ALT -  - 11/0 , SHORT - 22 - 10/0 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3600,26 +3600,26 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-5/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-6/%75)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>21.92</v>
+        <v>372</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46279</v>
@@ -3628,11 +3628,11 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-4.3</v>
+        <v>-2.6</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 16 - 10/1 , SHORT - 22 - 9/1 , SHORT - 14 - 10/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 12/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3664,17 +3664,17 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-2/%75)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>376.75</v>
+        <v>11.09</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46279</v>
@@ -3692,11 +3692,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 11/0 , ALT -  - 11/1 , ALT -  - 11/1</t>
+SHORT - 15 - 10/19 , SHORT - 15 - 10/6 , SHORT - 11 - 8/3</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (15g/0/%75)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%95)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>11.22</v>
+        <v>137.2</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46279</v>
@@ -3756,11 +3756,11 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-2.3</v>
+        <v>-3.1</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 15 - 10/19 , SHORT - 15 - 10/6 , SHORT - 11 - 8/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 7 - 8/2 , LONG - 24 - 20/1 , ALT -  - 22/4</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -3792,26 +3792,26 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%90)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (4g/-5/%60)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>136.8</v>
+        <v>70.05</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46279</v>
@@ -3820,11 +3820,11 @@
     <row r="52" ht="32" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 7 - 7/3 , LONG - 24 - 19/3 , ALT -  - 20/3</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+LONG - 10 - 4/7 , LONG - 6 - 5/5 , LONG - 5 - 7/3</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (4g/-4/%70)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/0/%80)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
@@ -3875,78 +3875,14 @@
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>70.90000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>46279</v>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-LONG - 10 - 4/8 , LONG - 6 - 5/5 , LONG - 5 - 6/4</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="O53" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O53"/>
+  <autoFilter ref="A1:O52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-4.8</v>
+        <v>-5</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 11 - 10/2 , SHORT - 11 - 10/3 , -</t>
+SHORT - 11 - 11/2 , SHORT - 11 - 10/2 , -</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>16.65</v>
+        <v>16.62000084</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46279</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-3.4</v>
+        <v>-3.9</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 18/5 , ALT -  - 18/5 , -</t>
+ALT -  - 19/5 , ALT -  - 19/5 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -667,7 +667,7 @@
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-6/%91)
 L - TP5/10G - %77 / 43 işlem - ADAY (6g/-4/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-5/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-6/%45)
 R - TP5/20G - %80 / 102 işlem - ADAY (5g/-6/%60)</t>
         </is>
       </c>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>284</v>
+        <v>282.5</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46279</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (2g/+2/%100)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>38.74</v>
+        <v>38.52000046</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46279</v>
@@ -755,11 +755,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -773,52 +773,47 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 1 - 12/0 , LONG - 3 - 10/2 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 2 - 10/1 , SHORT - 88 - 10/10 , LONG - 8 - 13/3</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
         <v>56</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G, V-TP2/10G, V-TP5/10G, Y-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (13g/-11/%60)
-E - TP5/20G - %69 / 179 işlem - ADAY (5g/0/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (11g/-10/%20)
-R - TP2/10G - %84 / 119 işlem - ADAY (4g/-2/%85)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-1/%80)
-V - TP2/10G - %95 / 21 işlem - ADAY (4g/-2/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (4g/-2/%75)
-Y - TP5/20G - %71 / 98 işlem - ADAY (12g/-11/%15)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-2/%55)
+I - TP5/20G - %82 / 67 işlem - ADAY (18g/-2/%54)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-2/%50)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 72 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>3.04</v>
+        <v>80.65000153</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46279</v>
@@ -831,7 +826,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -884,7 +879,7 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>58.45</v>
+        <v>58.5</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46279</v>
@@ -897,7 +892,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -952,7 +947,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>26.58</v>
+        <v>26.60000038</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46279</v>
@@ -965,7 +960,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1.9</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -980,7 +975,7 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 20/6 , ALT -  - 30/7 , -</t>
+ALT -  - 20/7 , ALT -  - 31/7 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -1002,8 +997,8 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-1/%92)
-L - TP5/10G - %77 / 43 işlem - ADAY (1g/-1/%93)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-2/%92)
+L - TP5/10G - %77 / 43 işlem - ADAY (1g/-2/%93)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1017,7 +1012,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>72.3</v>
+        <v>72</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46279</v>
@@ -1030,7 +1025,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-1.4</v>
+        <v>-2</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1045,7 +1040,7 @@
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 3 - 10/0 , LONG - 3 - 10/0 , LONG - 5 - 10/3</t>
+ALT -  - 11/0 , ALT -  - 11/0 , LONG - 5 - 11/2</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1082,7 +1077,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>2.91</v>
+        <v>2.8900001</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46279</v>
@@ -1091,187 +1086,184 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 19 - 2/7 , LONG - 32 - 3/9 , LONG - 10 - 4/8</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (0g/0/%100)
-Z - TP5/20G - %75 / 71 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>157.3</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 2 - 10/1 , SHORT - 88 - 10/10 , LONG - 8 - 14/3</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-2/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (18g/-2/%54)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-2/%50)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
 LONG - 33 - 3/7 , LONG - 31 - 3/7 , LONG - 31 - 3/7</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/+1/%100)
 H - TP5/10G - %70 / 20 işlem - ADAY (3g/+1/%100)
 H - TP5/20G - %85 / 20 işlem - ADAY (3g/+1/%100)</t>
         </is>
       </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>11.48999977</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 29/1 , ALT -  - 23/5 , LONG - 3 - 33/2</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (14g/-3/%40)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>37.52000046</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 24/1 , LONG - 7 - 28/6 , LONG - 7 - 5/5</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-1/%92)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
+        </is>
+      </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1280,7 +1272,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>11.46</v>
+        <v>94.34999847</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46279</v>
@@ -1289,11 +1281,11 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0.2</v>
+        <v>-6</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1307,35 +1299,37 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 29/2 , ALT -  - 24/5 , LONG - 3 - 33/2</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 18/7 , ALT -  - 18/7 , -</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (14g/-3/%40)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (5g/-10/%55)
+I - TP5/10G - %61 / 109 işlem - ADAY (4g/-8/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-10/%80)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1344,7 +1338,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>37.44</v>
+        <v>14.18000031</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46279</v>
@@ -1353,11 +1347,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1370,160 +1364,29 @@
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 24/1 , LONG - 7 - 28/6 , LONG - 7 - 5/5</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-1/%92)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CVKMD</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 17/6 , ALT -  - 17/6 , -</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (5g/-9/%55)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/-7/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-9/%80)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>14.28</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>GRSEL</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
 -</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F14" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/0/%85)
 I - TP5/10G - %61 / 109 işlem - ADAY (4g/0/%80)
@@ -1531,18 +1394,149 @@
 Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-8/%20)</t>
         </is>
       </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>295</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 75/59 , ALT -  - 103/50 , ALT -  - 75/59</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %77 / 43 işlem - ADAY (9g/-29/%38)
+Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-43/%10)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 73 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>19.10000038</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 23 - 17/8 , ALT -  - 20/6 , ALT -  - 19/5</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-3/%75)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-2/%90)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-2/%80)</t>
+        </is>
+      </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>295.25</v>
+        <v>78.09999847</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46279</v>
@@ -1551,11 +1545,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-8.4</v>
+        <v>-2.4</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1569,12 +1563,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 75/59 , ALT -  - 103/50 , ALT -  - 75/59</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0</v>
@@ -1587,18 +1581,18 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>L-TP5/10G, Q-TP5/20G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %77 / 43 işlem - ADAY (9g/-29/%38)
-Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-43/%10)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (3g/-6/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (3g/-6/%89)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 73 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1607,7 +1601,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>19.09</v>
+        <v>35.13999939</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46279</v>
@@ -1616,11 +1610,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-1.9</v>
+        <v>-4.9</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1634,46 +1628,44 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 23 - 16/9 , ALT -  - 19/6 , ALT -  - 18/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-2/%85)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-1/%90)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/-8/%25)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>78.5</v>
+        <v>7.80000019</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46279</v>
@@ -1682,11 +1674,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-2.5</v>
+        <v>-1.6</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1701,7 +1693,7 @@
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+SHORT - 61 - 8/4 , SHORT - 63 - 8/4 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1711,25 +1703,24 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (3g/-6/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (3g/-6/%89)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%100)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1738,7 +1729,7 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>35.1</v>
+        <v>295.5</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46279</v>
@@ -1747,11 +1738,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-3.7</v>
+        <v>0.2</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1765,7 +1756,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
 -</t>
         </is>
       </c>
@@ -1788,7 +1779,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/-7/%35)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-2/%60)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1802,7 +1793,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>7.9</v>
+        <v>6.19000006</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46279</v>
@@ -1811,11 +1802,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1829,12 +1820,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 61 - 8/4 , SHORT - 63 - 7/5 , ALT -  - 13/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+-</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
@@ -1847,17 +1838,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%95)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -1866,7 +1857,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>296.25</v>
+        <v>231.8999939</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46279</v>
@@ -1875,11 +1866,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1893,12 +1884,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 66 - 12/4 , SHORT - 143 - 28/6 , LONG - 7 - 11/2</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -1911,26 +1902,26 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-2/%55)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-4/%55)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>6.18</v>
+        <v>163.19999695</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46279</v>
@@ -1939,11 +1930,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.6</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1957,12 +1948,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 6 - 17/4 , LONG - 3 - 21/1 , ALT -  - 23/5</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
@@ -1980,7 +1971,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/+1/%100)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1990,11 +1981,11 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>232.69999695</v>
+        <v>538.5</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46279</v>
@@ -2003,11 +1994,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-1.4</v>
+        <v>0.1</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2020,157 +2011,29 @@
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 66 - 12/4 , SHORT - 143 - 28/5 , LONG - 7 - 11/1</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-4/%45)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>162.8</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MGROS</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 6 - 16/5 , LONG - 3 - 21/1 , ALT -  - 22/4</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%20)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>541</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL +2, CNDL 0, XU030 0, TOPLAM 4, İZLE
 LONG - 12 - 15/15 , LONG - 11 - 18/13 , SHORT - 1 - 0/9</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F24" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H24" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
 Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
@@ -2180,18 +2043,146 @@
 Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>72.69999695</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BRSAN</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 3 - 5/10 , UST -  - 1/15 , SHORT - 2 - 3/12</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (15g/-9/%40)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>682.5</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KONTR</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>M-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-11/%50)</t>
+        </is>
+      </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>72.7</v>
+        <v>3.48000002</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46279</v>
@@ -2200,11 +2191,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.7</v>
+        <v>-1.6</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2218,12 +2209,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 3 - 5/10 , UST -  - 1/15 , SHORT - 2 - 3/12</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
+SHORT - 1 - 1/8 , SHORT - 1 - 1/8 , SHORT - 3 - 2/7</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2236,17 +2227,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (15g/-9/%40)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (1g/-2/%95)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2255,7 +2246,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>682</v>
+        <v>20.57999992</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>46279</v>
@@ -2264,11 +2255,11 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -2282,12 +2273,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+UST -  - 1/10 , UST -  - 0/10 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>1</v>
@@ -2300,26 +2291,26 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-10/%50)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-2/%50)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>3.5</v>
+        <v>105.90000153</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>46279</v>
@@ -2328,11 +2319,11 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.5</v>
+        <v>-5.8</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2346,12 +2337,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
-SHORT - 1 - 1/8 , SHORT - 1 - 1/8 , SHORT - 3 - 2/7</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 1 - 4/19 , SHORT - 1 - 3/24 , UST -  - 7/17</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>1</v>
@@ -2364,17 +2355,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (1g/-2/%95)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-7/%82)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
@@ -2383,7 +2374,7 @@
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>20.6</v>
+        <v>47.08000183</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>46279</v>
@@ -2392,11 +2383,11 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-2.2</v>
+        <v>0.7</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -2410,44 +2401,46 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-UST -  - 1/10 , UST -  - 0/10 , SHORT - 11 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 1 - 12/1 , LONG - 3 - 10/2 , -</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-2/%50)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (13g/-10/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (11g/-10/%20)
+Y - TP5/20G - %71 / 98 işlem - ADAY (12g/-10/%15)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>105.9</v>
+        <v>3.04999995</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46279</v>
@@ -2456,11 +2449,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-5.4</v>
+        <v>-3.7</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2474,35 +2467,37 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 1 - 3/19 , SHORT - 1 - 2/24 , UST -  - 7/18</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 0, TOPLAM 4, İZLE
+LONG - 6 - 14/3 , LONG - 6 - 14/3 , -</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-7/%82)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (8g/-5/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (8g/-5/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-19/%15)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -2511,7 +2506,7 @@
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>47.32</v>
+        <v>6.80000019</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46279</v>
@@ -2520,11 +2515,11 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2.8</v>
+        <v>-1.6</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2537,95 +2532,29 @@
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 6 - 13/4 , LONG - 6 - 13/4 , -</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (8g/-4/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (8g/-4/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-18/%15)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL -1, XU030 0, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F32" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H32" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I32" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-1/%85)
 I - TP5/10G - %61 / 109 işlem - ADAY (4g/-1/%80)
@@ -2634,75 +2563,140 @@
 R - TP5/20G - %80 / 102 işlem - ADAY (15g/-12/%20)</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N33" s="7" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O33" s="8" t="n">
+      <c r="N32" s="7" t="n">
+        <v>3.06999993</v>
+      </c>
+      <c r="O32" s="8" t="n">
         <v>46279</v>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>TUKAS</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
 LONG - 20 - 14/7 , LONG - 6 - 15/2 , LONG - 32 - 5/5</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F33" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6" t="n">
+      <c r="G33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-2/%92)
 U - TP5/20G - %74 / 74 işlem - ADAY (11g/-1/%85)
 Z - TP5/20G - %75 / 71 işlem - ADAY (11g/-1/%55)</t>
         </is>
       </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>2.03999996</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 19 - 8/8 , SHORT - 17 - 9/7 , LONG - 5 - 5/5</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>K-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %90 / 51 işlem - ONAY (14g/-1/%63)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/+3/%100)</t>
+        </is>
+      </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 75 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -2711,7 +2705,7 @@
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>2.04</v>
+        <v>216.30000305</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46279</v>
@@ -2720,11 +2714,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-0.3</v>
+        <v>-2.1</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2738,45 +2732,44 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 19 - 8/8 , SHORT - 17 - 9/7 , LONG - 5 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 15 - 25/8 , LONG - 20 - 6/6 , LONG - 19 - 4/6</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>K-TP5/20G, Q-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %90 / 51 işlem - ONAY (14g/-1/%63)
-Q - TP5/20G - %70 / 203 işlem - ADAY (6g/+3/%100)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (3g/-1/%90)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 75 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>216.6</v>
+        <v>89.30000305</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46279</v>
@@ -2785,11 +2778,11 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2803,8 +2796,8 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 15 - 25/7 , LONG - 20 - 7/5 , LONG - 19 - 4/6</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
+LONG - 31 - 5/7 , LONG - 39 - 6/6 , LONG - 76 - 10/10</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -2826,7 +2819,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (3g/-1/%90)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (18g/+1/%100)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2840,7 +2833,7 @@
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>89.05</v>
+        <v>133.8999939</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46279</v>
@@ -2849,11 +2842,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -2867,8 +2860,8 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
-LONG - 31 - 5/7 , LONG - 39 - 6/6 , LONG - 76 - 10/10</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 46 - 1/14 , LONG - 81 - 5/14 , SHORT - 4 - 0/15</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2878,33 +2871,34 @@
         <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (18g/+1/%100)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (4g/0/%100)
+Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%100)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>133.8</v>
+        <v>225.5</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46279</v>
@@ -2913,11 +2907,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-0.1</v>
+        <v>-2.6</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2931,45 +2925,45 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 46 - 1/14 , LONG - 81 - 5/14 , SHORT - 4 - 0/15</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 9 - 6/4 , LONG - 9 - 6/4 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (4g/0/%100)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%100)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>225.3</v>
+        <v>52.25</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46279</v>
@@ -2978,11 +2972,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-2.6</v>
+        <v>-0.6</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2997,35 +2991,34 @@
       <c r="E39" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 9 - 6/4 , LONG - 9 - 6/4 , SHORT - 11 - 5/5</t>
+SHORT - 11 - 5/5 , SHORT - 11 - 5/5 , SHORT - 11 - 5/5</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
@@ -3034,7 +3027,7 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>52.25</v>
+        <v>21.73999977</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46279</v>
@@ -3043,11 +3036,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3061,12 +3054,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 11 - 5/5 , SHORT - 11 - 5/5 , SHORT - 11 - 5/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 6 - 3/6 , LONG - 10 - 14/10 , LONG - 8 - 15/10</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -3079,26 +3072,26 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/+2/%100)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>21.78</v>
+        <v>19.70000076</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>46279</v>
@@ -3107,11 +3100,11 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-0.3</v>
+        <v>-5.2</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3126,34 +3119,35 @@
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 6 - 3/6 , LONG - 10 - 14/10 , LONG - 8 - 15/10</t>
+SHORT - 1 - 4/7 , LONG - 25 - 14/10 , SHORT - 1 - 3/6</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
         <v>11</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/+2/%100)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-5/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -3162,7 +3156,7 @@
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>19.69</v>
+        <v>284.25</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46279</v>
@@ -3171,11 +3165,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-4.5</v>
+        <v>-1.9</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3190,35 +3184,37 @@
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 1 - 4/8 , LONG - 25 - 13/11 , SHORT - 1 - 3/7</t>
+SHORT - 11 - 10/1 , SHORT - 12 - 11/2 , SHORT - 12 - 11/2</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
         <v>11</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-5/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (3g/-2/%95)
+Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-2/%90)
+R - TP2/10G - %84 / 119 işlem - ADAY (3g/-2/%90)
+R - TP5/10G - %60 / 138 işlem - ADAY (3g/-2/%95)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
@@ -3227,7 +3223,7 @@
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>286.25</v>
+        <v>1.00999999</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46279</v>
@@ -3236,11 +3232,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-1</v>
+        <v>-2.6</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3255,7 +3251,7 @@
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 11 - 9/1 , SHORT - 12 - 10/3 , SHORT - 12 - 10/3</t>
+LONG - 43 - 14/10 , SHORT - 3 - 4/6 , SHORT - 3 - 4/6</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -3265,27 +3261,26 @@
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (3g/-1/%95)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-1/%95)
-R - TP2/10G - %84 / 119 işlem - ADAY (3g/-1/%90)
-R - TP5/10G - %60 / 138 işlem - ADAY (3g/-1/%100)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (1g/-3/%60)
+U - TP2/10G - %75 / 97 işlem - ADAY (3g/-4/%70)
+U - TP5/20G - %74 / 74 işlem - ADAY (11g/-3/%80)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3294,7 +3289,7 @@
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>1.02</v>
+        <v>114.30000305</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46279</v>
@@ -3303,11 +3298,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-2.4</v>
+        <v>-4.9</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3321,8 +3316,8 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 43 - 14/10 , SHORT - 3 - 4/6 , SHORT - 3 - 4/6</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+ALT -  - 53/39 , LONG - 7 - 28/5 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -3339,19 +3334,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (1g/-2/%65)
-U - TP2/10G - %75 / 97 işlem - ADAY (3g/-3/%70)
-U - TP5/20G - %74 / 74 işlem - ADAY (11g/-3/%85)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-20/%10)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-22/%0)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-4/%60)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 92 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -3360,7 +3355,7 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>114.5</v>
+        <v>3.72000003</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46279</v>
@@ -3369,11 +3364,11 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-4.3</v>
+        <v>-1.6</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3387,37 +3382,36 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-ALT -  - 52/38 , LONG - 7 - 28/6 , LONG - 4 - 10/0</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+UST -  - 6/15 , LONG - 45 - 6/22 , SHORT - 1 - 0/9</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, R-TP5/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-19/%10)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-22/%0)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-3/%65)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (1g/-2/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (3g/0/%100)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 92 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -3426,7 +3420,7 @@
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>3.74</v>
+        <v>60.40000153</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46279</v>
@@ -3435,11 +3429,11 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3453,8 +3447,8 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
-UST -  - 6/15 , LONG - 45 - 6/21 , SHORT - 1 - 0/9</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 7 - 7/3 , SHORT - 13 - 7/3 , SHORT - 11 - 7/6</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
@@ -3464,25 +3458,24 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (1g/-2/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (3g/0/%90)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-6/%60)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -3491,7 +3484,7 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>60.25</v>
+        <v>21.78000069</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46279</v>
@@ -3500,11 +3493,11 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-2.2</v>
+        <v>-5.4</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3518,8 +3511,8 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 7 - 7/3 , SHORT - 13 - 7/3 , SHORT - 11 - 6/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+ALT -  - 11/0 , SHORT - 22 - 10/0 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
@@ -3536,26 +3529,26 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-6/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-5/%75)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>21.82</v>
+        <v>372.5</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46279</v>
@@ -3564,11 +3557,11 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-5.5</v>
+        <v>-2.6</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3582,12 +3575,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 11/0 , SHORT - 22 - 10/0 , ALT -  - 11/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 12/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -3600,17 +3593,17 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-6/%75)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-2/%75)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
@@ -3619,7 +3612,7 @@
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>372</v>
+        <v>11.09000015</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46279</v>
@@ -3628,11 +3621,11 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3647,7 +3640,7 @@
       <c r="E49" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 12/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
+SHORT - 15 - 10/18 , SHORT - 15 - 10/6 , SHORT - 11 - 8/2</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3669,7 +3662,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-2/%75)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%80)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -3683,7 +3676,7 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>11.09</v>
+        <v>136.5</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46279</v>
@@ -3692,11 +3685,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-2</v>
+        <v>-3.9</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3710,12 +3703,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 15 - 10/19 , SHORT - 15 - 10/6 , SHORT - 11 - 8/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 13/1 , LONG - 24 - 21/1 , ALT -  - 23/5</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -3728,26 +3721,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%95)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (4g/-6/%50)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>137.2</v>
+        <v>69.44999695</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46279</v>
@@ -3756,11 +3749,11 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-3.1</v>
+        <v>-1.3</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3774,12 +3767,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 7 - 8/2 , LONG - 24 - 20/1 , ALT -  - 22/4</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+LONG - 10 - 4/7 , LONG - 6 - 5/5 , LONG - 5 - 7/3</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -3792,17 +3785,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (4g/-5/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/0/%80)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
@@ -3811,78 +3804,14 @@
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>70.05</v>
+        <v>102.40000153</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46279</v>
       </c>
     </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-LONG - 10 - 4/7 , LONG - 6 - 5/5 , LONG - 5 - 7/3</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/0/%80)</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N52" s="7" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="O52" s="8" t="n">
-        <v>46279</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O52"/>
+  <autoFilter ref="A1:O51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,6 +462,3428 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Son_Fiyat</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Fiyat_Tarihi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KONTR</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>M-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/?/%?)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>3.48000002</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 12 - 9/3 , SHORT - 12 - 8/4 , -</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-12/%50)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 23/9 , ALT -  - 23/9 , -</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-10/%86)
+L - TP5/10G - %77 / 43 işlem - ADAY (7g/-8/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-10/%60)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>272</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MIATK</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-4/%90)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+LONG - 34 - 5/5 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-1/%69)
+H - TP5/10G - %70 / 20 işlem - ADAY (4g/-1/%100)
+H - TP5/20G - %85 / 20 işlem - ADAY (4g/-1/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EUPWR</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 18/5 , ALT -  - 29/6 , -</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-2/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/-2/%83)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 31/3 , ALT -  - 25/7 , LONG - 4 - 34/1</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-5/%40)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 6 - 7/4 , LONG - 6 - 7/4 , LONG - 3 - 9/1</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+2/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/+2/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)
+R - TP5/20G - %80 / 102 işlem - ADAY (19g/-6/%16)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 15/4 , SHORT - 89 - 15/6 , ALT -  - 19/1</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-7/%5)
+I - TP5/20G - %82 / 67 işlem - ADAY (19g/-7/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-7/%10)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-6/%70)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CVKMD</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 11/1 , ALT -  - 16/5 , -</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-9/%40)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-7/%55)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-9/%80)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 72 - 16/5 , SHORT - 72 - 18/4 , -</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-11/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-8/%35)
+R - TP5/20G - %80 / 102 işlem - ADAY (5g/-8/%60)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 25/2 , LONG - 8 - 29/5 , LONG - 8 - 6/4</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-3/%78)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-2/%80)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GRSEL</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/+1/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/+1/%100)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/+1/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-7/%35)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>299</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 24 - 17/8 , ALT -  - 20/6 , ALT -  - 19/5</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-4/%80)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-3/%100)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-3/%45)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+-</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>S-TP5/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-5/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (4g/-5/%89)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DAPGM</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-9/%20)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 5 - 12/1 , SHORT - 86 - 24/9 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-2/%90)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 11 - 6/6 , LONG - 7 - 7/3 , LONG - 6 - 9/2</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-2/%70)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 62 - 9/3 , SHORT - 64 - 9/3 , ALT -  - 15/4</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-3/%75)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>291</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-3/%45)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 36/1 , ALT -  - 106/52 , ALT -  - 77/60</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-44/%10)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+SHORT - 67 - 13/4 , SHORT - 144 - 28/5 , LONG - 8 - 11/1</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-5/%35)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TABGD</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/?/%?)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>231.8999939</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 15/2 , ALT -  - 23/1 , ALT -  - 25/6</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-8/%50)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FENER</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 36/1 , ALT -  - 14/3 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-5/%70)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KUYAS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+LONG - 13 - 19/12 , LONG - 13 - 19/12 , SHORT - 2 - 4/6</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-3/%100)
+Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%75)
+V - TP2/10G - %95 / 21 işlem - ADAY (4g/-3/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (5g/-1/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BRSAN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 10/6 , SHORT - 1 - 4/11 , SHORT - 3 - 8/8</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-13/%40)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>651.5</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 1 - 0/9 , SHORT - 1 - 0/9 , SHORT - 12 - 6/4</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-2/%50)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EKGYO</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 2 - 4/6 , SHORT - 2 - 4/6 , SHORT - 4 - 5/5</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-4/%85)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HALKB</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 5/18 , SHORT - 2 - 4/23 , UST -  - 5/16</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-8/%73)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 2 - 12/1 , LONG - 4 - 10/3 , -</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-11/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-10/%25)
+Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-11/%5)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TUKAS</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+LONG - 21 - 13/7 , LONG - 7 - 14/3 , LONG - 33 - 4/5</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-2/%78)
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-1/%80)
+Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-1/%50)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 7 - 14/3 , LONG - 7 - 14/3 , -</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-6/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-6/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-20/%15)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SASA</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 7 - 3/24 , LONG - 8 - 2/25 , UST -  - 12/21</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/+3/%100)
+X - TP5/10G - %82 / 44 işlem - ADAY (1g/+3/%100)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PSGYO</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-3/%90)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-3/%75)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-3/%90)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-3/%70)
+R - TP5/20G - %80 / 102 işlem - ADAY (16g/-13/%20)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>KCHOL</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+SHORT - 17 - 3/13 , LONG - 82 - 7/12 , SHORT - 5 - 2/13</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-2/%85)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-2/%80)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ENKAI</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 18 - 27/6 , LONG - 21 - 9/3 , LONG - 20 - 7/4</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-4/%75)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GARAN</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 32 - 7/5 , LONG - 40 - 8/4 , LONG - 77 - 12/8</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-1/%13)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 4/8 , LONG - 26 - 13/11 , SHORT - 2 - 3/7</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>286</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GSRAY</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 12 - 10/1 , SHORT - 13 - 11/2 , SHORT - 13 - 11/2</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-2/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-2/%75)
+R - TP2/10G - %84 / 119 işlem - ADAY (4g/-2/%85)
+R - TP5/10G - %60 / 138 işlem - ADAY (4g/-2/%75)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ENJSA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 44 - 15/10 , SHORT - 4 - 5/5 , SHORT - 4 - 5/5</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-3/%60)
+U - TP2/10G - %75 / 97 işlem - ADAY (4g/-4/%40)
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-4/%80)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SOKM</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+UST -  - 4/13 , LONG - 46 - 8/20 , SHORT - 2 - 2/7</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-3/%65)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-1/%95)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 12 - 6/4 , SHORT - 12 - 6/4 , SHORT - 12 - 6/4</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 6/4 , LONG - 11 - 17/8 , LONG - 9 - 18/8</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/0/%80)</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="O45" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TRALT</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 5/5 , LONG - 10 - 8/3 , SHORT - 12 - 8/2</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 7 - 33/2 , LONG - 1 - 17/0 , LONG - 6 - 11/2</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/0/%100)
+T - TP5/20G - %77 / 128 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 8 - 8/2 , SHORT - 14 - 9/2 , SHORT - 12 - 8/4</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ASELS</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/0 , SHORT - 23 - 10/1 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-6/%50)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>370</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AKSA</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-1/%60)</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="O50" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TRMET</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 16 - 12/17 , SHORT - 16 - 11/5 , SHORT - 12 - 9/1</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-3/%70)</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="O51" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 54/39 , LONG - 8 - 28/5 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-21/%15)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-5/%35)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O52" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O52"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3816,7 +7240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.6</v>
+        <v>-2.6</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -580,7 +580,8 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -602,7 +603,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/?/%?)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/-13/%50)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -616,10 +617,10 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>3.48000002</v>
+        <v>3.3900001</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -629,7 +630,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -644,7 +645,7 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 12 - 9/3 , SHORT - 12 - 8/4 , -</t>
+SHORT - 12 - 10/2 , SHORT - 12 - 10/3 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -666,7 +667,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-12/%50)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-13/%50)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -680,7 +681,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>16.86</v>
+        <v>16.66</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46280</v>
@@ -693,7 +694,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-3.7</v>
+        <v>-2.6</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -708,7 +709,7 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 23/9 , ALT -  - 23/9 , -</t>
+ALT -  - 22/8 , ALT -  - 22/8 , -</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -730,10 +731,10 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-10/%86)
-L - TP5/10G - %77 / 43 işlem - ADAY (7g/-8/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-10/%60)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-9/%86)
+L - TP5/10G - %77 / 43 işlem - ADAY (7g/-7/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-8/%40)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-9/%60)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -747,7 +748,7 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>272</v>
+        <v>275.25</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46280</v>
@@ -760,7 +761,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-4.7</v>
+        <v>-5.6</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -811,7 +812,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>36.72</v>
+        <v>36.38</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46280</v>
@@ -824,7 +825,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -838,8 +839,8 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-LONG - 34 - 5/5 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 34 - 6/4 , LONG - 32 - 6/4 , LONG - 32 - 6/4</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -861,9 +862,9 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-1/%69)
-H - TP5/10G - %70 / 20 işlem - ADAY (4g/-1/%100)
-H - TP5/20G - %85 / 20 işlem - ADAY (4g/-1/%100)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-2/%69)
+H - TP5/10G - %70 / 20 işlem - ADAY (4g/-2/%100)
+H - TP5/20G - %85 / 20 işlem - ADAY (4g/-2/%100)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -877,7 +878,7 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>11.23</v>
+        <v>11.19</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46280</v>
@@ -886,11 +887,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.3</v>
+        <v>-2.8</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -904,45 +905,46 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 18/5 , ALT -  - 29/6 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 72 - 18/3 , SHORT - 72 - 20/1 , -</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-2/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (2g/-2/%83)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-14/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-10/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (5g/-10/%60)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>71.75</v>
+        <v>56.85</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46280</v>
@@ -951,11 +953,11 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-1.8</v>
+        <v>1.3</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -969,44 +971,45 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 31/3 , ALT -  - 25/7 , LONG - 4 - 34/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 17/4 , ALT -  - 28/5 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
         <v>54</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-5/%40)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-1/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/-1/%83)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>36.86</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46280</v>
@@ -1015,11 +1018,11 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.2</v>
+        <v>-3.4</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1033,8 +1036,8 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 6 - 7/4 , LONG - 6 - 7/4 , LONG - 3 - 9/1</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 33/5 , ALT -  - 28/9 , ALT -  - 37/1</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1044,17 +1047,81 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-6/%40)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+LONG - 6 - 7/4 , LONG - 6 - 7/4 , LONG - 3 - 9/1</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+2/%100)
 I - TP5/10G - %61 / 109 işlem - ADAY (6g/+2/%100)
@@ -1062,85 +1129,18 @@
 R - TP5/20G - %80 / 102 işlem - ADAY (19g/-6/%16)</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N9" s="7" t="n">
-        <v>26.66</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 15/4 , SHORT - 89 - 15/6 , ALT -  - 19/1</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-7/%5)
-I - TP5/20G - %82 / 67 işlem - ADAY (19g/-7/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-7/%10)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-6/%70)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N10" s="7" t="n">
-        <v>76.65000000000001</v>
+        <v>26.64</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46280</v>
@@ -1149,11 +1149,11 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.3</v>
+        <v>-3.5</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1167,46 +1167,47 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 11/1 , ALT -  - 16/5 , -</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 13/3 , SHORT - 89 - 14/7 , LONG - 9 - 17/0</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-9/%40)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-7/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-9/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)
+I - TP5/20G - %82 / 67 işlem - ADAY (19g/-5/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>14.36</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46280</v>
@@ -1215,11 +1216,11 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1233,8 +1234,8 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 72 - 16/5 , SHORT - 72 - 18/4 , -</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 12/1 , ALT -  - 17/6 , -</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1251,28 +1252,28 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-11/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-8/%35)
-R - TP5/20G - %80 / 102 işlem - ADAY (5g/-8/%60)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-7/%55)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>58.35</v>
+        <v>14.27</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46280</v>
@@ -1285,7 +1286,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1300,7 +1301,7 @@
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 25/2 , LONG - 8 - 29/5 , LONG - 8 - 6/4</t>
+ALT -  - 26/3 , LONG - 8 - 29/4 , LONG - 8 - 7/3</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1337,7 +1338,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46280</v>
@@ -1390,7 +1391,7 @@
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/+1/%100)
 I - TP5/10G - %61 / 109 işlem - ADAY (5g/+1/%100)
 I - TP5/20G - %82 / 67 işlem - ADAY (5g/+1/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-7/%35)</t>
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-7/%40)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1404,7 +1405,7 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>299</v>
+        <v>299.25</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46280</v>
@@ -1417,7 +1418,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-0.8</v>
+        <v>-2</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1431,8 +1432,8 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 24 - 17/8 , ALT -  - 20/6 , ALT -  - 19/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 24 - 18/7 , ALT -  - 22/8 , ALT -  - 20/7</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1454,9 +1455,9 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-4/%80)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-3/%100)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-3/%45)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-5/%65)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-4/%90)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-4/%40)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1470,7 +1471,7 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>77.45</v>
+        <v>76.5</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46280</v>
@@ -1479,11 +1480,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1498,11 +1499,11 @@
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
+SHORT - 67 - 13/3 , SHORT - 144 - 29/5 , LONG - 8 - 12/0</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0</v>
@@ -1515,27 +1516,27 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-5/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (4g/-5/%89)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-5/%30)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>35.2</v>
+        <v>161.2</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46280</v>
@@ -1544,11 +1545,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1562,8 +1563,8 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 13/0 , SHORT - 86 - 25/8 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1585,7 +1586,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-9/%20)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%80)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1599,7 +1600,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>7.73</v>
+        <v>22.8</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46280</v>
@@ -1608,11 +1609,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1626,8 +1627,8 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 5 - 12/1 , SHORT - 86 - 24/9 , ALT -  - 15/2</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1649,7 +1650,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-2/%90)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1663,7 +1664,7 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>23</v>
+        <v>99.7</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46280</v>
@@ -1672,11 +1673,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1690,8 +1691,8 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 11 - 6/6 , LONG - 7 - 7/3 , LONG - 6 - 9/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 62 - 9/3 , SHORT - 64 - 9/3 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1713,7 +1714,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-2/%70)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-3/%75)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1727,7 +1728,7 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>100.4</v>
+        <v>291.25</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46280</v>
@@ -1736,11 +1737,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-1.5</v>
+        <v>-0.8</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1754,8 +1755,8 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 62 - 9/3 , SHORT - 64 - 9/3 , ALT -  - 15/4</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+-</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1777,7 +1778,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-3/%75)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-3/%45)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1791,7 +1792,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>291</v>
+        <v>6.14</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46280</v>
@@ -1800,11 +1801,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-0.8</v>
+        <v>-2.7</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1818,12 +1819,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 37/1 , ALT -  - 107/53 , ALT -  - 78/61</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
@@ -1836,17 +1837,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-3/%45)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-44/%10)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -1855,7 +1856,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>6.14</v>
+        <v>18.58</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46280</v>
@@ -1864,11 +1865,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-2.3</v>
+        <v>-1.2</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1882,8 +1883,8 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 36/1 , ALT -  - 106/52 , ALT -  - 77/60</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1905,7 +1906,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-44/%10)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-1/%95)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1919,7 +1920,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>18.66</v>
+        <v>229.1000061</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46280</v>
@@ -1928,11 +1929,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1946,12 +1947,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-SHORT - 67 - 13/4 , SHORT - 144 - 28/5 , LONG - 8 - 11/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 15/2 , ALT -  - 23/1 , ALT -  - 25/6</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
@@ -1964,26 +1965,26 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-5/%35)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-8/%50)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>162.2</v>
+        <v>68.2</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46280</v>
@@ -1992,11 +1993,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2010,56 +2011,58 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/?/%?)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-8/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (4g/-8/%89)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>231.8999939</v>
+        <v>34.3</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -2074,11 +2077,11 @@
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 15/2 , ALT -  - 23/1 , ALT -  - 25/6</t>
+ALT -  - 36/0 , ALT -  - 13/3 , ALT -  - 13/3</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0</v>
@@ -2091,17 +2094,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-8/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-4/%70)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2110,7 +2113,7 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>67.90000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46280</v>
@@ -2119,11 +2122,11 @@
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-3.8</v>
+        <v>-2.6</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2137,44 +2140,49 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 36/1 , ALT -  - 14/3 , ALT -  - 14/3</t>
+          <t>BIS -1, PHL +2, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+LONG - 13 - 18/13 , LONG - 13 - 18/13 , SHORT - 2 - 3/6</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-5/%70)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-3/%100)
+Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-2/%90)
+V - TP2/10G - %95 / 21 işlem - ADAY (4g/-2/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (5g/0/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>2.78</v>
+        <v>70.8</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46280</v>
@@ -2183,11 +2191,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.4</v>
+        <v>-4</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2201,49 +2209,44 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
-LONG - 13 - 19/12 , LONG - 13 - 19/12 , SHORT - 2 - 4/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 10/7 , SHORT - 1 - 3/12 , SHORT - 3 - 7/8</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-3/%100)
-Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%75)
-V - TP2/10G - %95 / 21 işlem - ADAY (4g/-3/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (5g/-1/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-13/%40)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>70.25</v>
+        <v>655</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>46280</v>
@@ -2252,11 +2255,11 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-4.5</v>
+        <v>-0.8</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -2270,12 +2273,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 10/6 , SHORT - 1 - 4/11 , SHORT - 3 - 8/8</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 1 - 1/9 , SHORT - 1 - 1/9 , SHORT - 12 - 6/4</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>1</v>
@@ -2288,26 +2291,26 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-13/%40)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-3/%50)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>651.5</v>
+        <v>105.1</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>46280</v>
@@ -2316,11 +2319,11 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.4</v>
+        <v>-3.8</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2335,11 +2338,11 @@
       <c r="E29" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 0/9 , SHORT - 1 - 0/9 , SHORT - 12 - 6/4</t>
+SHORT - 2 - 6/4 , SHORT - 2 - 6/4 , SHORT - 4 - 7/4</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>1</v>
@@ -2352,17 +2355,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-2/%50)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-5/%85)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
@@ -2371,7 +2374,7 @@
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>105.5</v>
+        <v>19.8</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>46280</v>
@@ -2380,7 +2383,7 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -2398,12 +2401,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 4/6 , SHORT - 2 - 4/6 , SHORT - 4 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 7/16 , SHORT - 2 - 6/22 , UST -  - 4/15</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
@@ -2416,17 +2419,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-4/%85)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-10/%73)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -2435,7 +2438,7 @@
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>20.02</v>
+        <v>45.82</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46280</v>
@@ -2444,11 +2447,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.6</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2462,8 +2465,8 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 2 - 5/18 , SHORT - 2 - 4/23 , UST -  - 5/16</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 13/0 , LONG - 4 - 11/2 , -</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
@@ -2473,24 +2476,26 @@
         <v>1</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-8/%73)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-11/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-11/%20)
+Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-11/%5)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -2499,7 +2504,7 @@
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>46.66</v>
+        <v>3</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46280</v>
@@ -2508,11 +2513,11 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2526,12 +2531,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 2 - 12/1 , LONG - 4 - 10/3 , -</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+LONG - 21 - 14/7 , LONG - 7 - 15/2 , LONG - 33 - 5/5</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>1</v>
@@ -2544,85 +2549,85 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-11/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-10/%25)
-Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-11/%5)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 21 - 13/7 , LONG - 7 - 14/3 , LONG - 33 - 4/5</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-2/%78)
 U - TP5/20G - %74 / 74 işlem - ADAY (12g/-1/%80)
 Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-1/%50)</t>
         </is>
       </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 7 - 15/2 , LONG - 7 - 15/2 , -</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-7/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-7/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-21/%15)</t>
+        </is>
+      </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -2631,7 +2636,7 @@
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>2.04</v>
+        <v>6.61</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46280</v>
@@ -2640,11 +2645,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-1.3</v>
+        <v>1.4</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2659,11 +2664,11 @@
       <c r="E34" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 7 - 14/3 , LONG - 7 - 14/3 , -</t>
+LONG - 7 - 4/23 , LONG - 8 - 3/24 , UST -  - 11/20</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>1</v>
@@ -2676,19 +2681,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-6/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (9g/-6/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-20/%15)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/+2/%100)
+X - TP5/10G - %82 / 44 işlem - ADAY (1g/+2/%100)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/+2/%100)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -2697,7 +2702,7 @@
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>6.71</v>
+        <v>2.98</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46280</v>
@@ -2706,11 +2711,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>2.7</v>
+        <v>-4.2</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2724,46 +2729,48 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 7 - 3/24 , LONG - 8 - 2/25 , UST -  - 12/21</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/+3/%100)
-X - TP5/10G - %82 / 44 işlem - ADAY (1g/+3/%100)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/+3/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-5/%75)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-5/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-5/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-5/%60)
+R - TP5/20G - %80 / 102 işlem - ADAY (16g/-16/%20)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46280</v>
@@ -2772,11 +2779,11 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-1.3</v>
+        <v>-3.1</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2790,48 +2797,45 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+SHORT - 17 - 4/11 , LONG - 82 - 9/11 , SHORT - 5 - 4/12</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-3/%90)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-3/%75)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-3/%90)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-3/%70)
-R - TP5/20G - %80 / 102 işlem - ADAY (16g/-13/%20)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-3/%85)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-3/%80)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>3.03</v>
+        <v>218.4</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46280</v>
@@ -2840,11 +2844,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-2</v>
+        <v>-3.1</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -2858,36 +2862,35 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-SHORT - 17 - 3/13 , LONG - 82 - 7/12 , SHORT - 5 - 2/13</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 18 - 28/5 , LONG - 21 - 9/3 , LONG - 20 - 7/3</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-2/%85)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-2/%80)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-4/%70)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -2896,7 +2899,7 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>220.9</v>
+        <v>86.55</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46280</v>
@@ -2905,11 +2908,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2923,8 +2926,8 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 18 - 27/6 , LONG - 21 - 9/3 , LONG - 20 - 7/4</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 32 - 8/4 , LONG - 40 - 9/4 , LONG - 77 - 13/8</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2946,7 +2949,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-4/%75)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-1/%13)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2960,7 +2963,7 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>86.75</v>
+        <v>130.3</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46280</v>
@@ -2969,11 +2972,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-2.2</v>
+        <v>0.9</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2987,35 +2990,36 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 32 - 7/5 , LONG - 40 - 8/4 , LONG - 77 - 12/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 4/8 , LONG - 26 - 13/11 , SHORT - 2 - 3/7</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-1/%13)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
@@ -3024,7 +3028,7 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>131</v>
+        <v>286.75</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46280</v>
@@ -3033,11 +3037,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3052,370 +3056,370 @@
       <c r="E40" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 2 - 4/8 , LONG - 26 - 13/11 , SHORT - 2 - 3/7</t>
+ALT -  - 11/0 , SHORT - 13 - 12/1 , SHORT - 13 - 12/1</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I40" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-3/%70)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-3/%80)
+R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
+R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%80)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ENJSA</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 44 - 17/8 , SHORT - 4 - 7/3 , SHORT - 4 - 7/3</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-5/%50)
+U - TP2/10G - %75 / 97 işlem - ADAY (4g/-6/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-6/%70)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SOKM</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+UST -  - 3/12 , SHORT - 2 - 5/18 , SHORT - 2 - 3/7</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="I42" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-4/%60)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%85)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 12 - 7/4 , SHORT - 12 - 6/4 , SHORT - 12 - 6/4</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 6/4 , LONG - 11 - 17/8 , LONG - 9 - 17/8</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/0/%80)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TRALT</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 5/5 , LONG - 10 - 8/3 , SHORT - 12 - 8/3</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="n">
-        <v>286</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>GSRAY</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 12 - 10/1 , SHORT - 13 - 11/2 , SHORT - 13 - 11/2</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-2/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-2/%75)
-R - TP2/10G - %84 / 119 işlem - ADAY (4g/-2/%85)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N41" s="7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O41" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ENJSA</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 44 - 15/10 , SHORT - 4 - 5/5 , SHORT - 4 - 5/5</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-3/%60)
-U - TP2/10G - %75 / 97 işlem - ADAY (4g/-4/%40)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-4/%80)</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SOKM</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 4/13 , LONG - 46 - 8/20 , SHORT - 2 - 2/7</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-3/%65)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-1/%95)</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="O43" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 12 - 6/4 , SHORT - 12 - 6/4 , SHORT - 12 - 6/4</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="n">
-        <v>21.44</v>
-      </c>
-      <c r="O44" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AEFES</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 6/4 , LONG - 11 - 17/8 , LONG - 9 - 18/8</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/0/%80)</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>19.17</v>
+        <v>51.3</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46280</v>
@@ -3424,11 +3428,11 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-2.2</v>
+        <v>-1.7</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3443,35 +3447,34 @@
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 5/5 , LONG - 10 - 8/3 , SHORT - 12 - 8/2</t>
+LONG - 8 - 9/2 , SHORT - 14 - 9/1 , SHORT - 12 - 8/4</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -3480,7 +3483,7 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>51.1</v>
+        <v>21.42</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46280</v>
@@ -3489,11 +3492,11 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3507,36 +3510,35 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 7 - 33/2 , LONG - 1 - 17/0 , LONG - 6 - 11/2</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/0/%100)
-T - TP5/20G - %77 / 128 işlem - ADAY (1g/0/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-11/%10)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -3545,7 +3547,7 @@
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>2.84</v>
+        <v>7.53</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46280</v>
@@ -3554,11 +3556,11 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3572,12 +3574,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 8 - 8/2 , SHORT - 14 - 9/2 , SHORT - 12 - 8/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 16 - 12/17 , SHORT - 16 - 11/5 , SHORT - 12 - 10/1</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -3590,26 +3592,26 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-3/%70)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>21.48</v>
+        <v>134.3</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46280</v>
@@ -3618,11 +3620,11 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-0.7</v>
+        <v>-1.8</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3636,44 +3638,45 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , SHORT - 23 - 10/1 , ALT -  - 11/1</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 36/0 , ALT -  - 19/2 , ALT -  - 13/0</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-6/%50)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-2/%95)
+T - TP5/20G - %77 / 128 işlem - ADAY (1g/-2/%95)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>370</v>
+        <v>2.79</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46280</v>
@@ -3682,11 +3685,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3700,12 +3703,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 12/1</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+LONG - 1 - 10/0 , SHORT - 23 - 9/1 , LONG - 1 - 10/0</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -3718,26 +3721,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-1/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-5/%50)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>11.14</v>
+        <v>374</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46280</v>
@@ -3746,11 +3749,11 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3764,44 +3767,45 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 16 - 12/17 , SHORT - 16 - 11/5 , SHORT - 12 - 9/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 55/40 , LONG - 8 - 29/5 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-3/%70)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-21/%15)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%30)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>134.3</v>
+        <v>3.64</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46280</v>
@@ -3810,11 +3814,11 @@
     <row r="52" ht="32" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3828,36 +3832,35 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 54/39 , LONG - 8 - 28/5 , ALT -  - 11/0</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-21/%15)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-5/%35)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-2/%60)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
@@ -3866,7 +3869,7 @@
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>3.67</v>
+        <v>11.05</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>46280</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>16.66</v>
+        <v>16.69</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46280</v>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-2.6</v>
+        <v>-3.5</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 22/8 , ALT -  - 22/8 , -</t>
+ALT -  - 23/9 , ALT -  - 23/9 , -</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -731,10 +731,10 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-9/%86)
-L - TP5/10G - %77 / 43 işlem - ADAY (7g/-7/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-8/%40)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-9/%60)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-10/%86)
+L - TP5/10G - %77 / 43 işlem - ADAY (7g/-8/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-10/%60)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>275.25</v>
+        <v>272.5</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46280</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-5.6</v>
+        <v>-10</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-4/%90)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-9/%90)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>36.38</v>
+        <v>34.68</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46280</v>
@@ -821,11 +821,11 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-2.6</v>
+        <v>-5.2</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -839,12 +839,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 34 - 6/4 , LONG - 32 - 6/4 , LONG - 32 - 6/4</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+ALT -  - 17/4 , ALT -  - 14/3 , -</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -857,223 +857,225 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-15/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-15/%10)
+Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-15/%5)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EUPWR</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 21/7 , ALT -  - 32/8 , -</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-4/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/-4/%83)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 18/0 , ALT -  - 18/0 , -</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-9/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-9/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-23/%15)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 34 - 6/4 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-2/%69)
 H - TP5/10G - %70 / 20 işlem - ADAY (4g/-2/%100)
 H - TP5/20G - %85 / 20 işlem - ADAY (4g/-2/%100)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N6" s="7" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 72 - 18/3 , SHORT - 72 - 20/1 , -</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-14/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-10/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (5g/-10/%60)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>56.85</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EUPWR</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 17/4 , ALT -  - 28/5 , -</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-1/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (2g/-1/%83)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 33/5 , ALT -  - 28/9 , ALT -  - 37/1</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-6/%40)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
       <c r="N9" s="7" t="n">
-        <v>36.26</v>
+        <v>11.23</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46280</v>
@@ -1082,11 +1084,11 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.2</v>
+        <v>-5</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1100,38 +1102,37 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-LONG - 6 - 7/4 , LONG - 6 - 7/4 , LONG - 3 - 9/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 72 - 20/1 , ALT -  - 23/0 , -</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+2/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/+2/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)
-R - TP5/20G - %80 / 102 işlem - ADAY (19g/-6/%16)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-16/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-12/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (5g/-12/%60)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
@@ -1140,7 +1141,7 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>26.64</v>
+        <v>55.6</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46280</v>
@@ -1149,11 +1150,11 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-3.5</v>
+        <v>-3.8</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1167,47 +1168,44 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 13/3 , SHORT - 89 - 14/7 , LONG - 9 - 17/0</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 38/2</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)
-I - TP5/20G - %82 / 67 işlem - ADAY (19g/-5/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-7/%35)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>77.84999999999999</v>
+        <v>36.08</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46280</v>
@@ -1216,11 +1214,11 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1234,37 +1232,38 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 12/1 , ALT -  - 17/6 , -</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+LONG - 6 - 5/5 , LONG - 6 - 5/5 , LONG - 3 - 8/2</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-7/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+4/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/+4/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-5/%25)
+R - TP5/20G - %80 / 102 işlem - ADAY (19g/-5/%16)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1273,7 +1272,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>14.27</v>
+        <v>27</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46280</v>
@@ -1282,11 +1281,11 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-1.6</v>
+        <v>-4</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1300,36 +1299,38 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 26/3 , LONG - 8 - 29/4 , LONG - 8 - 7/3</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 14/3 , SHORT - 89 - 14/7 , ALT -  - 18/0</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-3/%78)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-2/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-6/%5)
+I - TP5/20G - %82 / 67 işlem - ADAY (19g/-6/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-6/%10)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1338,7 +1339,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>92.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46280</v>
@@ -1347,1098 +1348,1106 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
+          <t>CVKMD</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 12/0 , ALT -  - 18/6 , -</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PSGYO</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-7/%55)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-7/%55)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-7/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-7/%45)
+R - TP5/20G - %80 / 102 işlem - ADAY (16g/-18/%20)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 28/4 , LONG - 8 - 31/3 , LONG - 8 - 8/2</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-4/%70)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 31/7 , ALT -  - 27/12 , ALT -  - 25/11</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-9/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-8/%80)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-8/%15)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>GRSEL</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B18" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/0/%95)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/0/%90)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/0/%90)
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-8/%20)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>293.75</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 67 - 14/3 , SHORT - 144 - 30/4 , LONG - 8 - 13/0</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-6/%30)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 14/1 , SHORT - 86 - 27/6 , ALT -  - 18/4</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 62 - 11/2 , SHORT - 64 - 10/2 , ALT -  - 16/5</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-4/%70)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>287.75</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-4/%30)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 35/0 , ALT -  - 104/51 , ALT -  - 75/58</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-43/%10)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TABGD</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F14" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/+1/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/+1/%100)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/+1/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-7/%40)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="F25" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-1/%95)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N14" s="7" t="n">
-        <v>299.25</v>
-      </c>
-      <c r="O14" s="8" t="n">
+      <c r="N25" s="7" t="n">
+        <v>229.1000061</v>
+      </c>
+      <c r="O25" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 24 - 18/7 , ALT -  - 22/8 , ALT -  - 20/7</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-5/%65)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-4/%90)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-4/%40)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="O15" s="8" t="n">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 16/3 , ALT -  - 25/2 , ALT -  - 26/7</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-9/%50)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="O26" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 67 - 13/3 , SHORT - 144 - 29/5 , LONG - 8 - 12/0</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-5/%30)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>161.2</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SARKY</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 13/0 , SHORT - 86 - 25/8 , ALT -  - 16/3</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%80)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 62 - 9/3 , SHORT - 64 - 9/3 , ALT -  - 15/4</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-3/%75)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>291.25</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-3/%45)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 37/1 , ALT -  - 107/53 , ALT -  - 78/61</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-44/%10)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TABGD</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-1/%95)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>229.1000061</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ECILC</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 15/2 , ALT -  - 23/1 , ALT -  - 25/6</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-8/%50)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F27" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-8/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (4g/-8/%89)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-9/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (4g/-9/%89)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N24" s="7" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O24" s="8" t="n">
+      <c r="N27" s="7" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O27" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 38/2 , LONG - 8 - 32/2 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-23/%15)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-8/%15)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>FENER</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="B29" s="3" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 36/0 , ALT -  - 13/3 , ALT -  - 13/3</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
+ALT -  - 38/2 , ALT -  - 15/4 , ALT -  - 15/4</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-6/%65)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N25" s="7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O25" s="8" t="n">
+      <c r="N29" s="7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O29" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KUYAS</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="B30" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL +2, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 13 - 18/13 , LONG - 13 - 18/13 , SHORT - 2 - 3/6</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+LONG - 13 - 19/12 , LONG - 13 - 19/12 , SHORT - 2 - 4/6</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G30" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H30" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I30" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-3/%100)
 Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-2/%90)
-V - TP2/10G - %95 / 21 işlem - ADAY (4g/-2/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (5g/0/%50)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%80)
+V - TP2/10G - %95 / 21 işlem - ADAY (4g/-3/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (5g/-1/%50)
 Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N26" s="7" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BRSAN</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 10/7 , SHORT - 1 - 3/12 , SHORT - 3 - 7/8</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>X-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-13/%40)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>655</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 1/9 , SHORT - 1 - 1/9 , SHORT - 12 - 6/4</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-3/%50)</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>105.1</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>EKGYO</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 6/4 , SHORT - 2 - 6/4 , SHORT - 4 - 7/4</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-5/%85)</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>HALKB</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 2 - 7/16 , SHORT - 2 - 6/22 , UST -  - 4/15</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-10/%73)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N30" s="7" t="n">
-        <v>45.82</v>
+        <v>70.5</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46280</v>
@@ -2447,11 +2456,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-1.6</v>
+        <v>-4.7</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2465,46 +2474,44 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 13/0 , LONG - 4 - 11/2 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 10/6 , SHORT - 1 - 4/11 , SHORT - 3 - 8/8</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-11/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-11/%20)
-Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-11/%5)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-14/%40)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>3</v>
+        <v>650.5</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46280</v>
@@ -2513,11 +2520,11 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2531,37 +2538,35 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 21 - 14/7 , LONG - 7 - 15/2 , LONG - 33 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 1 - 2/8 , SHORT - 1 - 2/8 , SHORT - 12 - 7/3</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-2/%78)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-1/%80)
-Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-1/%50)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-4/%50)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
@@ -2570,7 +2575,7 @@
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>2.04</v>
+        <v>103.8</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>46280</v>
@@ -2579,11 +2584,11 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -2598,36 +2603,34 @@
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 7 - 15/2 , LONG - 7 - 15/2 , -</t>
+SHORT - 2 - 5/5 , SHORT - 2 - 5/5 , SHORT - 4 - 6/4</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-7/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (9g/-7/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-21/%15)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-5/%85)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -2636,7 +2639,7 @@
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>6.61</v>
+        <v>19.93</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46280</v>
@@ -2645,11 +2648,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1.4</v>
+        <v>-2.2</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2663,37 +2666,35 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 7 - 4/23 , LONG - 8 - 3/24 , UST -  - 11/20</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 6/17 , SHORT - 2 - 5/22 , UST -  - 4/15</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/+2/%100)
-X - TP5/10G - %82 / 44 işlem - ADAY (1g/+2/%100)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/+2/%100)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-9/%73)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -2702,7 +2703,7 @@
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>2.98</v>
+        <v>46.04</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46280</v>
@@ -2711,11 +2712,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-4.2</v>
+        <v>-2.5</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2729,39 +2730,37 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 21 - 16/5 , LONG - 7 - 17/0 , LONG - 33 - 7/3</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-5/%75)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-5/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-5/%85)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-5/%60)
-R - TP5/20G - %80 / 102 işlem - ADAY (16g/-16/%20)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)
+Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-3/%50)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -2770,7 +2769,7 @@
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>2.94</v>
+        <v>1.99</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46280</v>
@@ -2779,11 +2778,11 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-3.1</v>
+        <v>-3.7</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2797,109 +2796,111 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-SHORT - 17 - 4/11 , LONG - 82 - 9/11 , SHORT - 5 - 4/12</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 9/19 , LONG - 8 - 8/20 , UST -  - 7/16</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/-4/%93)
+X - TP5/10G - %82 / 44 işlem - ADAY (1g/-4/%81)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-4/%70)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>KCHOL</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+SHORT - 17 - 4/12 , LONG - 82 - 8/11 , SHORT - 5 - 3/12</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="I37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-3/%85)
 Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-3/%80)</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N36" s="7" t="n">
-        <v>218.4</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ENKAI</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 18 - 28/5 , LONG - 21 - 9/3 , LONG - 20 - 7/3</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N37" s="7" t="n">
-        <v>86.55</v>
+        <v>218.9</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46280</v>
@@ -2908,11 +2909,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-2.7</v>
+        <v>-3.6</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2926,8 +2927,8 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 32 - 8/4 , LONG - 40 - 9/4 , LONG - 77 - 13/8</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 18 - 29/5 , LONG - 21 - 10/3 , LONG - 20 - 8/3</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2949,7 +2950,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-1/%13)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-5/%70)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2963,7 +2964,7 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>130.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46280</v>
@@ -2972,11 +2973,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.9</v>
+        <v>-3.9</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2990,142 +2991,139 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 2 - 4/8 , LONG - 26 - 13/11 , SHORT - 2 - 3/7</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 32 - 9/3 , LONG - 40 - 10/2 , LONG - 77 - 14/6</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-3/%13)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+SHORT - 2 - 4/8 , LONG - 26 - 14/11 , SHORT - 2 - 3/7</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N39" s="7" t="n">
-        <v>286.75</v>
-      </c>
-      <c r="O39" s="8" t="n">
+      <c r="N40" s="7" t="n">
+        <v>285.25</v>
+      </c>
+      <c r="O40" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>GSRAY</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 ALT -  - 11/0 , SHORT - 13 - 12/1 , SHORT - 13 - 12/1</t>
         </is>
       </c>
-      <c r="F40" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-3/%70)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-3/%80)
-R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%80)</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ENJSA</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 44 - 17/8 , SHORT - 4 - 7/3 , SHORT - 4 - 7/3</t>
-        </is>
-      </c>
       <c r="F41" s="6" t="n">
         <v>14</v>
       </c>
@@ -3133,26 +3131,27 @@
         <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-5/%50)
-U - TP2/10G - %75 / 97 işlem - ADAY (4g/-6/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-6/%70)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-2/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-2/%75)
+R - TP2/10G - %84 / 119 işlem - ADAY (4g/-2/%85)
+R - TP5/10G - %60 / 138 işlem - ADAY (4g/-2/%75)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -3161,7 +3160,7 @@
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>111.2</v>
+        <v>1.01</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46280</v>
@@ -3170,11 +3169,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-2.8</v>
+        <v>-1.7</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3188,36 +3187,37 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 3/12 , SHORT - 2 - 5/18 , SHORT - 2 - 3/7</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 44 - 16/9 , SHORT - 4 - 6/4 , SHORT - 4 - 6/4</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-4/%60)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%85)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-4/%55)
+U - TP2/10G - %75 / 97 işlem - ADAY (4g/-5/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-5/%80)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>58.7</v>
+        <v>112.3</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46280</v>
@@ -3235,11 +3235,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-1.6</v>
+        <v>-3.8</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 12 - 7/4 , SHORT - 12 - 6/4 , SHORT - 12 - 6/4</t>
+UST -  - 2/11 , SHORT - 2 - 6/17 , SHORT - 2 - 4/6</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -3264,24 +3264,25 @@
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-5/%55)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-4/%70)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3290,7 +3291,7 @@
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>21.4</v>
+        <v>58.1</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46280</v>
@@ -3299,11 +3300,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3317,12 +3318,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 6/4 , LONG - 11 - 17/8 , LONG - 9 - 17/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 12 - 7/3 , SHORT - 12 - 7/3 , SHORT - 12 - 7/3</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -3335,26 +3336,26 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/0/%80)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-5/%60)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>19.28</v>
+        <v>21.24</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46280</v>
@@ -3363,11 +3364,11 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-1.8</v>
+        <v>-3</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3381,36 +3382,35 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 5/5 , LONG - 10 - 8/3 , SHORT - 12 - 8/3</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 6/4 , LONG - 11 - 17/8 , LONG - 9 - 18/7</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
         <v>11</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-1/%80)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>51.3</v>
+        <v>19.11</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46280</v>
@@ -3428,11 +3428,11 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-1.7</v>
+        <v>-3.5</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3447,34 +3447,35 @@
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 8 - 9/2 , SHORT - 14 - 9/1 , SHORT - 12 - 8/4</t>
+SHORT - 4 - 6/4 , LONG - 10 - 9/1 , SHORT - 12 - 9/1</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-6/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-6/%60)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -3483,7 +3484,7 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>21.42</v>
+        <v>50.4</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46280</v>
@@ -3492,191 +3493,191 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
+          <t>ASELS</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+LONG - 1 - 9/1 , SHORT - 23 - 8/2 , LONG - 1 - 10/1</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-5/%55)
+Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 82 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 14 - 11/1 , SHORT - 14 - 10/0 , SHORT - 12 - 10/3</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>DAPGM</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B49" s="3" t="n">
         <v>-3.5</v>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
 -</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F49" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-11/%10)</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N47" s="7" t="n">
+      <c r="N49" s="7" t="n">
         <v>7.53</v>
-      </c>
-      <c r="O47" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>TRMET</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 16 - 12/17 , SHORT - 16 - 11/5 , SHORT - 12 - 10/1</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-3/%70)</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="n">
-        <v>134.3</v>
-      </c>
-      <c r="O48" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>HEKTS</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 36/0 , ALT -  - 19/2 , ALT -  - 13/0</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-2/%95)
-T - TP5/20G - %77 / 128 işlem - ADAY (1g/-2/%95)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="n">
-        <v>2.79</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46280</v>
@@ -3685,11 +3686,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.4</v>
+        <v>-1</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3703,12 +3704,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
-LONG - 1 - 10/0 , SHORT - 23 - 9/1 , LONG - 1 - 10/0</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 13/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -3721,26 +3722,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-5/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-3/%60)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>374</v>
+        <v>10.98</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46280</v>
@@ -3749,11 +3750,11 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3767,45 +3768,44 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 55/40 , LONG - 8 - 29/5 , ALT -  - 12/1</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 16 - 13/16 , SHORT - 16 - 12/4 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-21/%15)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%30)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-4/%60)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>3.64</v>
+        <v>132.6</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46280</v>
@@ -3814,11 +3814,11 @@
     <row r="52" ht="32" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-0.4</v>
+        <v>-4.6</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3833,34 +3833,35 @@
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
+ALT -  - 40/3 , ALT -  - 23/5 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-2/%60)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-5/%70)
+T - TP5/20G - %77 / 128 işlem - ADAY (1g/-5/%80)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
@@ -3869,7 +3870,7 @@
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>11.05</v>
+        <v>2.71</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>46280</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -478,7 +478,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -562,126 +562,130 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CVKMD</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 12/0 , ALT -  - 17/6 , -</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
+X - TP2/10G - %98 / 46 işlem - ONAY (0g/0/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>14.19999981</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>KONTR</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B3" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>M-TP5/20G</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/-13/%50)</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/-14/%50)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N2" s="7" t="n">
-        <v>3.3900001</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 12 - 10/2 , SHORT - 12 - 10/3 , -</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-13/%50)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N3" s="7" t="n">
-        <v>16.69</v>
+        <v>3.3499999</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46280</v>
@@ -690,46 +694,110 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 12 - 11/2 , SHORT - 12 - 10/2 , -</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-13/%50)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>16.62000084</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>ASTOR</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B5" s="3" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 ALT -  - 23/9 , ALT -  - 23/9 , -</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-10/%86)
 L - TP5/10G - %77 / 43 işlem - ADAY (7g/-8/%60)
@@ -737,112 +805,48 @@
 R - TP5/20G - %80 / 102 işlem - ADAY (6g/-10/%60)</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>272.5</v>
-      </c>
-      <c r="O4" s="8" t="n">
+      <c r="N5" s="7" t="n">
+        <v>272.25</v>
+      </c>
+      <c r="O5" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>MIATK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B6" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-9/%90)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 17/4 , ALT -  - 14/3 , -</t>
-        </is>
-      </c>
       <c r="F6" s="6" t="n">
         <v>58</v>
       </c>
@@ -850,26 +854,24 @@
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-15/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-15/%10)
-Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-15/%5)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-9/%90)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -878,7 +880,7 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>2.89</v>
+        <v>34.68000031</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46280</v>
@@ -887,11 +889,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-2.4</v>
+        <v>-7.2</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -905,36 +907,37 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 21/7 , ALT -  - 32/8 , -</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+ALT -  - 20/6 , ALT -  - 16/5 , -</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-4/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (2g/-4/%83)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-17/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-17/%10)
+Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-17/%5)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -943,7 +946,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>70.3</v>
+        <v>2.82999992</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46280</v>
@@ -952,11 +955,11 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-5</v>
+        <v>-2.9</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -970,37 +973,36 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 18/0 , ALT -  - 18/0 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 21/8 , ALT -  - 33/9 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-9/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (9g/-9/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-23/%15)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-5/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/-5/%83)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1009,7 +1011,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>6.46</v>
+        <v>69.90000153</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46280</v>
@@ -1018,11 +1020,11 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-2.3</v>
+        <v>-2.9</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1036,12 +1038,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 34 - 6/4 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 7 - 15/2 , LONG - 7 - 15/2 , -</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1054,19 +1056,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-2/%69)
-H - TP5/10G - %70 / 20 işlem - ADAY (4g/-2/%100)
-H - TP5/20G - %85 / 20 işlem - ADAY (4g/-2/%100)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-7/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-7/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-21/%15)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1075,7 +1077,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>11.23</v>
+        <v>6.5999999</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46280</v>
@@ -1084,11 +1086,11 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-5</v>
+        <v>-2.3</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1102,8 +1104,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 72 - 20/1 , ALT -  - 23/0 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 34 - 5/5 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1120,19 +1122,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-16/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-12/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (5g/-12/%60)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-1/%69)
+H - TP5/10G - %70 / 20 işlem - ADAY (4g/-1/%100)
+H - TP5/20G - %85 / 20 işlem - ADAY (4g/-1/%100)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
@@ -1141,7 +1143,7 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>55.6</v>
+        <v>11.22999954</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46280</v>
@@ -1150,11 +1152,11 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-3.8</v>
+        <v>-5.7</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1168,35 +1170,37 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 38/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 72 - 21/1 , ALT -  - 24/1 , -</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-7/%35)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-16/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-13/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (5g/-13/%60)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -1205,7 +1209,7 @@
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>36.08</v>
+        <v>55.15000153</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46280</v>
@@ -1214,11 +1218,11 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.5</v>
+        <v>-4.2</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1232,8 +1236,8 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 6 - 5/5 , LONG - 6 - 5/5 , LONG - 3 - 8/2</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 38/2</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1243,27 +1247,24 @@
         <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+4/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/+4/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-5/%25)
-R - TP5/20G - %80 / 102 işlem - ADAY (19g/-5/%16)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-7/%35)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1272,7 +1273,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>27</v>
+        <v>35.93999863</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46280</v>
@@ -1281,11 +1282,11 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-4</v>
+        <v>0.7</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1299,12 +1300,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 14/3 , SHORT - 89 - 14/7 , ALT -  - 18/0</t>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+LONG - 6 - 6/4 , LONG - 6 - 6/4 , LONG - 3 - 9/1</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>0</v>
@@ -1317,29 +1318,29 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-6/%5)
-I - TP5/20G - %82 / 67 işlem - ADAY (19g/-6/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-6/%10)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+3/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/+3/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)
+R - TP5/20G - %80 / 102 işlem - ADAY (19g/-6/%16)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>77.40000000000001</v>
+        <v>26.78000069</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46280</v>
@@ -1348,11 +1349,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-0.4</v>
+        <v>-3.3</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1366,46 +1367,47 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 12/0 , ALT -  - 18/6 , -</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 13/2 , SHORT - 89 - 13/7 , LONG - 9 - 17/0</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)
+I - TP5/20G - %82 / 67 işlem - ADAY (19g/-5/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>14.13</v>
+        <v>78</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46280</v>
@@ -1455,10 +1457,10 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-7/%55)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-7/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-7/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-7/%45)
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-8/%55)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-8/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-8/%35)
 R - TP5/20G - %80 / 102 işlem - ADAY (16g/-18/%20)</t>
         </is>
       </c>
@@ -1473,7 +1475,7 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>2.87</v>
+        <v>2.86999989</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46280</v>
@@ -1486,7 +1488,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1501,7 +1503,7 @@
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 28/4 , LONG - 8 - 31/3 , LONG - 8 - 8/2</t>
+ALT -  - 28/5 , LONG - 8 - 32/3 , LONG - 8 - 9/2</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1538,7 +1540,7 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>91.45</v>
+        <v>91.19999695</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46280</v>
@@ -1547,11 +1549,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-5.9</v>
+        <v>-0.7</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1566,7 +1568,7 @@
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 31/7 , ALT -  - 27/12 , ALT -  - 25/11</t>
+-</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1576,26 +1578,27 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-9/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-8/%80)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-8/%15)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-1/%95)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-1/%90)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-9/%20)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1604,7 +1607,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>73.5</v>
+        <v>293</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46280</v>
@@ -1613,11 +1616,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.4</v>
+        <v>-4.7</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1630,656 +1633,654 @@
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 30/6 , ALT -  - 25/11 , ALT -  - 24/10</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-7/%55)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-6/%85)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%25)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>74.44999695</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 67 - 14/3 , SHORT - 144 - 30/4 , LONG - 8 - 13/0</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-6/%25)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>160.30000305</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DAPGM</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-10/%10)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>7.5999999</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , SHORT - 86 - 27/6 , ALT -  - 18/5</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-5/%75)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>22.36000061</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>99.40000153</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 62 - 11/1 , SHORT - 64 - 11/2 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-5/%65)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>285.25</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-4/%25)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>6.05999994</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 34/1 , ALT -  - 102/50 , ALT -  - 74/57</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-43/%10)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TABGD</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-3/%85)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>225</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 17/4 , ALT -  - 25/3 , ALT -  - 27/8</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-10/%50)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>67.05000305</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/0/%95)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/0/%90)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/0/%90)
-Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-8/%20)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>293.75</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 67 - 14/3 , SHORT - 144 - 30/4 , LONG - 8 - 13/0</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-6/%30)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SARKY</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 14/1 , SHORT - 86 - 27/6 , ALT -  - 18/4</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>99.65000000000001</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 62 - 11/2 , SHORT - 64 - 10/2 , ALT -  - 16/5</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>287.75</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-4/%30)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 35/0 , ALT -  - 104/51 , ALT -  - 75/58</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-43/%10)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>18.89</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TABGD</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-1/%95)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>229.1000061</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ECILC</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 16/3 , ALT -  - 25/2 , ALT -  - 26/7</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-9/%50)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-9/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (4g/-9/%89)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BTCIM</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 38/2 , LONG - 8 - 32/2 , ALT -  - 14/3</t>
-        </is>
-      </c>
       <c r="F28" s="6" t="n">
         <v>39</v>
       </c>
@@ -2294,18 +2295,18 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-23/%15)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-8/%15)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-10/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (4g/-10/%89)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
@@ -2314,7 +2315,7 @@
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>3.55</v>
+        <v>33.54000092</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>46280</v>
@@ -2323,11 +2324,11 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.8</v>
+        <v>-5.9</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2342,34 +2343,35 @@
       <c r="E29" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 38/2 , ALT -  - 15/4 , ALT -  - 15/4</t>
+ALT -  - 40/3 , LONG - 8 - 34/1 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-6/%65)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-24/%15)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-10/%15)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
@@ -2378,7 +2380,7 @@
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>46280</v>
@@ -2387,11 +2389,11 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-3</v>
+        <v>-5.9</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -2405,49 +2407,44 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-LONG - 13 - 19/12 , LONG - 13 - 19/12 , SHORT - 2 - 4/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 40/3 , ALT -  - 16/5 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-3/%100)
-Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%80)
-V - TP2/10G - %95 / 21 işlem - ADAY (4g/-3/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (5g/-1/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-7/%50)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>70.5</v>
+        <v>2.72000003</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46280</v>
@@ -2456,11 +2453,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-4.7</v>
+        <v>-4.2</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2474,44 +2471,49 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 10/6 , SHORT - 1 - 4/11 , SHORT - 3 - 8/8</t>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+LONG - 13 - 20/11 , LONG - 13 - 20/11 , SHORT - 2 - 5/5</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-14/%40)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-4/%100)
+Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-4/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-4/%70)
+V - TP2/10G - %95 / 21 işlem - ADAY (4g/-4/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (5g/-2/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-4/%70)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>650.5</v>
+        <v>69.65000153</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46280</v>
@@ -2520,11 +2522,11 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2</v>
+        <v>-5.1</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2538,12 +2540,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 2/8 , SHORT - 1 - 2/8 , SHORT - 12 - 7/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 11/5 , SHORT - 1 - 5/11 , SHORT - 3 - 9/7</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>1</v>
@@ -2556,26 +2558,26 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-4/%50)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-14/%40)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>103.8</v>
+        <v>647.5</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>46280</v>
@@ -2584,258 +2586,256 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 1 - 2/8 , SHORT - 1 - 2/8 , SHORT - 12 - 8/3</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-4/%50)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>103.59999847</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>EKGYO</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="B34" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 SHORT - 2 - 5/5 , SHORT - 2 - 5/5 , SHORT - 4 - 6/4</t>
         </is>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="G33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="G34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>H-TP2/10G</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-5/%85)</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N33" s="7" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="O33" s="8" t="n">
+      <c r="N34" s="7" t="n">
+        <v>19.79999924</v>
+      </c>
+      <c r="O34" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>HALKB</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="B35" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 SHORT - 2 - 6/17 , SHORT - 2 - 5/22 , UST -  - 4/15</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F35" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="G35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>K-TP5/10G</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-9/%73)</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N34" s="7" t="n">
-        <v>46.04</v>
-      </c>
-      <c r="O34" s="8" t="n">
+      <c r="N35" s="7" t="n">
+        <v>46.08000183</v>
+      </c>
+      <c r="O35" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>TUKAS</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="B36" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
 LONG - 21 - 16/5 , LONG - 7 - 17/0 , LONG - 33 - 7/3</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F36" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="6" t="n">
+      <c r="G36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I36" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
 U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)
 Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-3/%50)</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N35" s="7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SASA</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 9/19 , LONG - 8 - 8/20 , UST -  - 7/16</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="6" t="n">
+      <c r="N36" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/-4/%93)
-X - TP5/10G - %82 / 44 işlem - ADAY (1g/-4/%81)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="n">
-        <v>2.83</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46280</v>
@@ -2844,127 +2844,129 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
+          <t>SASA</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 11/18 , LONG - 8 - 10/18 , UST -  - 5/14</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/-5/%93)
+X - TP5/10G - %82 / 44 işlem - ADAY (1g/-5/%81)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>2.79999995</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>KCHOL</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="B38" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
 SHORT - 17 - 4/12 , LONG - 82 - 8/11 , SHORT - 5 - 3/12</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F38" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="G37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="6" t="n">
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I38" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-3/%85)
 Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-3/%80)</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N37" s="7" t="n">
-        <v>218.9</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ENKAI</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 18 - 29/5 , LONG - 21 - 10/3 , LONG - 20 - 8/3</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-5/%70)</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N38" s="7" t="n">
-        <v>86.09999999999999</v>
+        <v>218.80000305</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46280</v>
@@ -2973,7 +2975,7 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -2991,8 +2993,8 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 32 - 9/3 , LONG - 40 - 10/2 , LONG - 77 - 14/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 18 - 29/5 , LONG - 21 - 10/2 , LONG - 20 - 8/2</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -3014,7 +3016,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-3/%13)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-5/%70)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -3028,7 +3030,7 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>128.7</v>
+        <v>85.80000305</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46280</v>
@@ -3037,11 +3039,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.4</v>
+        <v>-4.6</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3055,243 +3057,242 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-SHORT - 2 - 4/8 , LONG - 26 - 14/11 , SHORT - 2 - 3/7</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 32 - 10/3 , LONG - 40 - 11/2 , LONG - 77 - 15/6</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-3/%13)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>127.80000305</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+SHORT - 2 - 5/7 , LONG - 26 - 14/10 , SHORT - 2 - 3/6</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N40" s="7" t="n">
-        <v>285.25</v>
-      </c>
-      <c r="O40" s="8" t="n">
+      <c r="N41" s="7" t="n">
+        <v>284.25</v>
+      </c>
+      <c r="O41" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>GSRAY</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="B42" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 ALT -  - 11/0 , SHORT - 13 - 12/1 , SHORT - 13 - 12/1</t>
         </is>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F42" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="6" t="n">
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-2/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-2/%75)
-R - TP2/10G - %84 / 119 işlem - ADAY (4g/-2/%85)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-3/%70)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-3/%80)
+R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
+R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%80)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N41" s="7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O41" s="8" t="n">
+      <c r="N42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="8" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>ENJSA</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="B43" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 LONG - 44 - 16/9 , SHORT - 4 - 6/4 , SHORT - 4 - 6/4</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F43" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6" t="n">
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I43" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-4/%55)
 U - TP2/10G - %75 / 97 işlem - ADAY (4g/-5/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-5/%80)</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-4/%80)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N42" s="7" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SOKM</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 2/11 , SHORT - 2 - 6/17 , SHORT - 2 - 4/6</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-5/%55)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N43" s="7" t="n">
-        <v>58.1</v>
+        <v>112.80000305</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46280</v>
@@ -3300,126 +3301,127 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
+          <t>SOKM</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+UST -  - 2/12 , SHORT - 2 - 5/17 , SHORT - 2 - 4/6</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-5/%60)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%70)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>58.29999924</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>DOHOL</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="B45" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 SHORT - 12 - 7/3 , SHORT - 12 - 7/3 , SHORT - 12 - 7/3</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F45" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>U-TP5/20G</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-5/%60)</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N44" s="7" t="n">
-        <v>21.24</v>
-      </c>
-      <c r="O44" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AEFES</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 6/4 , LONG - 11 - 17/8 , LONG - 9 - 18/7</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-1/%80)</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
       <c r="N45" s="7" t="n">
-        <v>19.11</v>
+        <v>21.34000015</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46280</v>
@@ -3428,128 +3430,127 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 7/3 , LONG - 11 - 18/7 , LONG - 9 - 19/7</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-1/%80)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>18.97999954</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>TRALT</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="B47" s="3" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 SHORT - 4 - 6/4 , LONG - 10 - 9/1 , SHORT - 12 - 9/1</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F47" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="6" t="n">
+      <c r="G47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-6/%75)
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-6/%60)</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N46" s="7" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="O46" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ASELS</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
-LONG - 1 - 9/1 , SHORT - 23 - 8/2 , LONG - 1 - 10/1</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-5/%55)
-Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
       <c r="N47" s="7" t="n">
-        <v>375.75</v>
+        <v>50.45000076</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46280</v>
@@ -3562,7 +3563,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-3.3</v>
+        <v>-3.8</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3577,7 +3578,7 @@
       <c r="E48" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 14 - 11/1 , SHORT - 14 - 10/0 , SHORT - 12 - 10/3</t>
+SHORT - 14 - 12/1 , ALT -  - 11/1 , SHORT - 12 - 11/2</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3613,7 +3614,7 @@
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>21.06</v>
+        <v>20.95999908</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46280</v>
@@ -3622,11 +3623,11 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3640,12 +3641,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
--</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 14/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3658,17 +3659,17 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-11/%10)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-3/%60)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -3677,7 +3678,7 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>7.53</v>
+        <v>10.92000008</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46280</v>
@@ -3686,11 +3687,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-1</v>
+        <v>-3.2</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3704,8 +3705,8 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 13/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 16 - 14/16 , SHORT - 16 - 13/4 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3727,7 +3728,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-3/%60)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-4/%60)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -3741,7 +3742,7 @@
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>10.98</v>
+        <v>132.1000061</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46280</v>
@@ -3750,11 +3751,11 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-2.9</v>
+        <v>-6</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3768,44 +3769,45 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 16 - 13/16 , SHORT - 16 - 12/4 , ALT -  - 11/0</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 42/5 , ALT -  - 25/6 , ALT -  - 18/5</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-4/%60)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-6/%70)
+T - TP5/20G - %77 / 128 işlem - ADAY (1g/-6/%80)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>132.6</v>
+        <v>2.67000008</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46280</v>
@@ -3814,11 +3816,11 @@
     <row r="52" ht="32" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-4.6</v>
+        <v>1.2</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3832,36 +3834,35 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 40/3 , ALT -  - 23/5 , ALT -  - 16/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 9/1 , SHORT - 23 - 8/2 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-5/%70)
-T - TP5/20G - %77 / 128 işlem - ADAY (1g/-5/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-4/%60)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
@@ -3870,7 +3871,7 @@
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>2.71</v>
+        <v>377</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>46280</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -562,11 +562,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1</v>
+        <v>-3.7</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -580,48 +580,43 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 12/0 , ALT -  - 17/6 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
-X - TP2/10G - %98 / 46 işlem - ONAY (0g/0/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (18g/?/%?)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>14.19999981</v>
+        <v>3.3499999</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46280</v>
@@ -630,11 +625,11 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-3.7</v>
+        <v>-6.5</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -647,1495 +642,1499 @@
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 17/4 , ALT -  - 24/12 , -</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (7g/-16/%40)
+X - TP2/10G - %98 / 46 işlem - ONAY (1g/-7/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-14/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-16/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (1g/-7/%88)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL +2, CNDL 0, XU030 +1, TOPLAM 4, İZLE
+SHORT - 17 - 22/0 , ALT -  - 17/4 , -</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-19/%40)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 32/17 , ALT -  - 32/17 , -</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (7g/-16/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (8g/-14/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-16/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (7g/-16/%40)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EUPWR</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 31/16 , ALT -  - 44/13 , -</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-14/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (3g/-14/%85)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 35 - 10/0 , LONG - 33 - 10/0 , LONG - 33 - 10/0</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-6/%67)
+H - TP5/10G - %70 / 20 işlem - ADAY (5g/-6/%88)
+H - TP5/20G - %85 / 20 işlem - ADAY (5g/-6/%100)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MIATK</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-18/%82)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 21/3 , ALT -  - 21/3 , -</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (10g/-14/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-27/%10)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 24/10 , ALT -  - 19/8 , -</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (15g/-20/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-20/%15)
+Y - TP5/20G - %71 / 98 işlem - ADAY (14g/-20/%5)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 23/0 , ALT -  - 26/3 , -</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-20/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-17/%15)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-17/%55)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 37/2 , ALT -  - 37/2 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-8/%60)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PSGYO</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-17/%40)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-17/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-17/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-17/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (17g/-26/%15)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 41/11 , ALT -  - 35/15 , ALT -  - 45/7</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-12/%20)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GRSEL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>M-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/-14/%50)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="F15" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-6/%65)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-6/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-6/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-13/%0)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N3" s="7" t="n">
-        <v>3.3499999</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 12 - 11/2 , SHORT - 12 - 10/2 , -</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-13/%50)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>16.62000084</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ASTOR</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 23/9 , ALT -  - 23/9 , -</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="N15" s="7" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 36/11 , ALT -  - 31/16 , ALT -  - 29/15</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-12/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-11/%75)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-11/%0)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 17/3 , ALT -  - 16/5 , ALT -  - 16/2</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
+U - TP5/20G - %74 / 74 işlem - ADAY (15g/-13/%27)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 14/3 , SHORT - 90 - 14/7 , ALT -  - 18/0</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-5/%70)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GSRAY</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-10/%86)
-L - TP5/10G - %77 / 43 işlem - ADAY (7g/-8/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-10/%60)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>272.25</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MIATK</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="I19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (5g/-6/%40)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-6/%60)
+R - TP2/10G - %84 / 119 işlem - ADAY (5g/-6/%40)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-6/%40)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 7 - 9/1 , ALT -  - 11/1 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/0/%90)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/0/%70)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-9/%0)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 22/8 , ALT -  - 31/7 , ALT -  - 32/13</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-14/%45)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-9/%90)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="F23" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>S-TP5/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-14/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (5g/-14/%90)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N6" s="7" t="n">
-        <v>34.68000031</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 20/6 , ALT -  - 16/5 , -</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="N23" s="7" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 16/3 , SHORT - 68 - 17/1 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-17/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-17/%10)
-Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-17/%5)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>2.82999992</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EUPWR</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 21/8 , ALT -  - 33/9 , -</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-5/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (2g/-5/%83)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>69.90000153</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IZENR</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 7 - 15/2 , LONG - 7 - 15/2 , -</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-7/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (9g/-7/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-21/%15)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>6.5999999</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 34 - 5/5 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-1/%69)
-H - TP5/10G - %70 / 20 işlem - ADAY (4g/-1/%100)
-H - TP5/20G - %85 / 20 işlem - ADAY (4g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>11.22999954</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 72 - 21/1 , ALT -  - 24/1 , -</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-16/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-13/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (5g/-13/%60)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>55.15000153</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-2/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-8/%5)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DAPGM</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 38/2</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-7/%35)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>35.93999863</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
-LONG - 6 - 6/4 , LONG - 6 - 6/4 , LONG - 3 - 9/1</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+3/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/+3/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)
-R - TP5/20G - %80 / 102 işlem - ADAY (19g/-6/%16)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>26.78000069</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 13/2 , SHORT - 89 - 13/7 , LONG - 9 - 17/0</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)
-I - TP5/20G - %82 / 67 işlem - ADAY (19g/-5/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-8/%55)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-8/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-8/%35)
-R - TP5/20G - %80 / 102 işlem - ADAY (16g/-18/%20)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>2.86999989</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 28/5 , LONG - 8 - 32/3 , LONG - 8 - 9/2</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>91.19999695</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GRSEL</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-1/%95)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-1/%90)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
-Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-9/%20)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="F25" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-17/%15)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N17" s="7" t="n">
-        <v>293</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 30/6 , ALT -  - 25/11 , ALT -  - 24/10</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-7/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-6/%85)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%25)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>74.44999695</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 67 - 14/3 , SHORT - 144 - 30/4 , LONG - 8 - 13/0</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-6/%25)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>160.30000305</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DAPGM</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-10/%10)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>7.5999999</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SARKY</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , SHORT - 86 - 27/6 , ALT -  - 18/5</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-5/%75)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>22.36000061</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>99.40000153</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 62 - 11/1 , SHORT - 64 - 11/2 , ALT -  - 17/6</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-5/%65)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>285.25</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-4/%25)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>6.05999994</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 34/1 , ALT -  - 102/50 , ALT -  - 74/57</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-43/%10)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
       <c r="N25" s="7" t="n">
-        <v>19</v>
+        <v>7.01</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2149,12 +2148,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 28/5 , ALT -  - 28/5 , ALT -  - 30/11</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -2167,17 +2166,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-3/%85)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-2/%85)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
@@ -2186,20 +2185,20 @@
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>225</v>
+        <v>502.5</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2213,12 +2212,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 17/4 , ALT -  - 25/3 , ALT -  - 27/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 18/5 , SHORT - 87 - 32/3 , ALT -  - 23/9</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>0</v>
@@ -2231,39 +2230,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-10/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-9/%50)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>67.05000305</v>
+        <v>21.26</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-4.6</v>
+        <v>-3.1</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -2277,58 +2276,57 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 13/0 , ALT -  - 13/0 , ALT -  - 20/9</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-10/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (4g/-10/%89)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-8/%50)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>33.54000092</v>
+        <v>276.5</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.9</v>
+        <v>-2.5</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2342,58 +2340,57 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 40/3 , LONG - 8 - 34/1 , ALT -  - 16/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-24/%15)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-10/%15)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-6/%5)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>3.5</v>
+        <v>5.91</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-5.9</v>
+        <v>-3.6</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -2407,12 +2404,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 40/3 , ALT -  - 16/5 , ALT -  - 16/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 18/7 , ALT -  - 18/7 , ALT -  - 18/7</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0</v>
@@ -2430,7 +2427,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-7/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2440,24 +2437,24 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>2.72000003</v>
+        <v>10.53</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-4.2</v>
+        <v>-7.9</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2471,62 +2468,57 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
-LONG - 13 - 20/11 , LONG - 13 - 20/11 , SHORT - 2 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 38/2 , ALT -  - 115/59 , ALT -  - 83/66</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-4/%100)
-Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-4/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-4/%70)
-V - TP2/10G - %95 / 21 işlem - ADAY (4g/-4/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (5g/-2/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-4/%70)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-47/%0)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>69.65000153</v>
+        <v>17.5</v>
       </c>
       <c r="O31" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-5.1</v>
+        <v>-5.5</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2540,57 +2532,57 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 11/5 , SHORT - 1 - 5/11 , SHORT - 3 - 9/7</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 46/8 , ALT -  - 20/9 , ALT -  - 20/9</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-14/%40)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-12/%30)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>647.5</v>
+        <v>2.57</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -2604,44 +2596,43 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 2/8 , SHORT - 1 - 2/8 , SHORT - 12 - 8/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-4/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/?/%?)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>103.59999847</v>
+        <v>225</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46280</v>
@@ -2650,11 +2641,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-3.8</v>
+        <v>-6.7</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2668,57 +2659,58 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 5/5 , SHORT - 2 - 5/5 , SHORT - 4 - 6/4</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 52/12 , ALT -  - 33/13 , ALT -  - 26/11</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-5/%85)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/-12/%55)
+T - TP5/20G - %77 / 128 işlem - ADAY (2g/-12/%70)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>19.79999924</v>
+        <v>2.49</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-2.1</v>
+        <v>-7.7</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2732,57 +2724,58 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 2 - 6/17 , SHORT - 2 - 5/22 , UST -  - 4/15</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 74/57 , ALT -  - 38/2 , ALT -  - 22/11</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>E-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-9/%73)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-30/%5)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-17/%0)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>46.08000183</v>
+        <v>3.23</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-2</v>
+        <v>-4.9</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2796,59 +2789,57 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 21 - 16/5 , LONG - 7 - 17/0 , LONG - 33 - 7/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 5 - 16/1 , SHORT - 2 - 10/7 , SHORT - 4 - 14/3</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)
-Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-3/%50)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-18/%25)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>2</v>
+        <v>615.5</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-4.8</v>
+        <v>-10</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -2862,37 +2853,40 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 11/18 , LONG - 8 - 10/18 , UST -  - 5/14</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 16/3 , ALT -  - 57/16 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/-5/%93)
-X - TP5/10G - %82 / 44 işlem - ADAY (1g/-5/%81)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-14/%91)
+Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-14/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (5g/-14/%75)
+V - TP2/10G - %95 / 21 işlem - ADAY (5g/-14/%80)
+V - TP5/10G - %75 / 20 işlem - ADAY (6g/-12/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -2901,20 +2895,20 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>2.79999995</v>
+        <v>62.7</v>
       </c>
       <c r="O37" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-3</v>
+        <v>-3.9</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2928,36 +2922,35 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-SHORT - 17 - 4/12 , LONG - 82 - 8/11 , SHORT - 5 - 3/12</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 2 - 6/4 , SHORT - 2 - 6/4 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-3/%85)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-3/%80)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-8/%40)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
@@ -2966,20 +2959,20 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>218.80000305</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-3.9</v>
+        <v>-4.9</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2994,34 +2987,34 @@
       <c r="E39" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 18 - 29/5 , LONG - 21 - 10/2 , LONG - 20 - 8/2</t>
+ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-5/%70)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-10/%82)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
@@ -3030,20 +3023,20 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>85.80000305</v>
+        <v>18.83</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-4.6</v>
+        <v>-3.3</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3057,35 +3050,35 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 32 - 10/3 , LONG - 40 - 11/2 , LONG - 77 - 15/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 3 - 10/14 , SHORT - 3 - 9/19 , UST -  - 0/12</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-3/%13)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (6g/-12/%73)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
@@ -3094,20 +3087,20 @@
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>127.80000305</v>
+        <v>44.56</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3121,36 +3114,37 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-SHORT - 2 - 5/7 , LONG - 26 - 14/10 , SHORT - 2 - 3/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 22 - 20/2 , ALT -  - 21/3 , LONG - 34 - 10/1</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-8/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-6/%60)
+Z - TP5/20G - %75 / 71 işlem - ADAY (13g/-6/%50)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -3159,20 +3153,20 @@
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>284.25</v>
+        <v>1.93</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3186,60 +3180,59 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 11/0 , SHORT - 13 - 12/1 , SHORT - 13 - 12/1</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 15/15 , SHORT - 2 - 15/9 , SHORT - 1 - 5/5</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-3/%70)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-3/%80)
-R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%80)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (2g/-14/%92)
+X - TP5/10G - %82 / 44 işlem - ADAY (2g/-14/%79)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>1</v>
+        <v>2.52</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-1.3</v>
+        <v>-4.6</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3253,37 +3246,36 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 44 - 16/9 , SHORT - 4 - 6/4 , SHORT - 4 - 6/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 18 - 9/7 , SHORT - 6 - 10/3 , SHORT - 6 - 8/8</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-4/%55)
-U - TP2/10G - %75 / 97 işlem - ADAY (4g/-5/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-4/%80)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-7/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%60)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3292,20 +3284,20 @@
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>112.80000305</v>
+        <v>208.7</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3319,36 +3311,35 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 2/12 , SHORT - 2 - 5/17 , SHORT - 2 - 4/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 8 - 10/1 , LONG - 12 - 22/4 , LONG - 10 - 22/4</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-5/%60)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%70)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-5/%75)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -3357,20 +3348,20 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>58.29999924</v>
+        <v>18.39</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-1.8</v>
+        <v>-3.3</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3384,12 +3375,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 12 - 7/3 , SHORT - 12 - 7/3 , SHORT - 12 - 7/3</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 17 - 34/1 , LONG - 22 - 13/0 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
@@ -3402,17 +3393,17 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-8/%60)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -3421,20 +3412,20 @@
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>21.34000015</v>
+        <v>82.95</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-3.7</v>
+        <v>-4.5</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3448,47 +3439,48 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 7/3 , LONG - 11 - 18/7 , LONG - 9 - 19/7</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 3 - 9/3 , SHORT - 3 - 9/3 , SHORT - 3 - 8/3</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-1/%80)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-9/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-9/%50)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>18.97999954</v>
+        <v>271.5</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
@@ -3498,7 +3490,7 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-3.4</v>
+        <v>-4.1</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3512,12 +3504,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 6/4 , LONG - 10 - 9/1 , SHORT - 12 - 9/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/0 , ALT -  - 12/1 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>1</v>
@@ -3535,8 +3527,8 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-6/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-6/%60)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-10/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-10/%50)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3546,24 +3538,24 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>50.45000076</v>
+        <v>48.4</v>
       </c>
       <c r="O47" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-3.8</v>
+        <v>-4.3</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3577,57 +3569,59 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 14 - 12/1 , ALT -  - 11/1 , SHORT - 12 - 11/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 13 - 10/2 , SHORT - 5 - 10/0 , SHORT - 5 - 10/0</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-8/%45)
+U - TP2/10G - %75 / 97 işlem - ADAY (5g/-9/%40)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-9/%60)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>20.95999908</v>
+        <v>108</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-1.5</v>
+        <v>-3.8</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3641,35 +3635,36 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 14/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 1 - 1/8 , SHORT - 3 - 9/14 , SHORT - 3 - 8/3</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-3/%60)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (3g/-8/%50)
+U - TP5/20G - %74 / 74 işlem - ADAY (5g/-7/%75)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -3678,20 +3673,20 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>10.92000008</v>
+        <v>56.1</v>
       </c>
       <c r="O49" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-3.2</v>
+        <v>-4.2</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3705,12 +3700,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 16 - 14/16 , SHORT - 16 - 13/4 , ALT -  - 11/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 12/2 , ALT -  - 11/0 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -3723,17 +3718,17 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-4/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-8/%60)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
@@ -3742,20 +3737,20 @@
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>132.1000061</v>
+        <v>361.25</v>
       </c>
       <c r="O50" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-6</v>
+        <v>-4.6</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3769,58 +3764,57 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 42/5 , ALT -  - 25/6 , ALT -  - 18/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 12 - 12/1 , ALT -  - 13/3 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-6/%70)
-T - TP5/20G - %77 / 128 işlem - ADAY (1g/-6/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-8/%5)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>2.67000008</v>
+        <v>94.8</v>
       </c>
       <c r="O51" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>1.2</v>
+        <v>-4.3</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3834,12 +3828,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 9/1 , SHORT - 23 - 8/2 , LONG - 1 - 10/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 17 - 19/12 , SHORT - 17 - 16/1 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -3852,29 +3846,29 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-4/%60)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-9/%25)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>377</v>
+        <v>126.4</v>
       </c>
       <c r="O52" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
   </sheetData>
@@ -3889,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3989,11 +3983,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-5</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -4007,57 +4001,61 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 11 - 11/2 , SHORT - 11 - 10/2 , -</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 12/0 , ALT -  - 17/6 , -</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-13/%50)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
+X - TP2/10G - %98 / 46 işlem - ONAY (0g/0/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>16.62000084</v>
+        <v>14.19999981</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -4071,38 +4069,35 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 19/5 , ALT -  - 19/5 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-6/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (6g/-4/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-6/%45)
-R - TP5/20G - %80 / 102 işlem - ADAY (5g/-6/%60)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/-14/%50)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
@@ -4111,20 +4106,20 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>282.5</v>
+        <v>3.3499999</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -4138,12 +4133,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 12 - 11/2 , SHORT - 12 - 10/2 , -</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -4156,39 +4151,39 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (2g/+1/%100)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-13/%50)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>38.52000046</v>
+        <v>16.62000084</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.6</v>
+        <v>-3.6</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -4202,60 +4197,60 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 2 - 10/1 , SHORT - 88 - 10/10 , LONG - 8 - 13/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 23/9 , ALT -  - 23/9 , -</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-2/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (18g/-2/%54)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-2/%50)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-10/%86)
+L - TP5/10G - %77 / 43 işlem - ADAY (7g/-8/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-10/%60)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>80.65000153</v>
+        <v>272.25</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-5.9</v>
+        <v>-10</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -4269,37 +4264,35 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 71 - 17/4 , SHORT - 71 - 19/3 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (11g/-11/%75)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/-8/%35)
-R - TP5/20G - %80 / 102 işlem - ADAY (4g/-8/%60)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-9/%90)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -4308,20 +4301,20 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>58.5</v>
+        <v>34.68000031</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.4</v>
+        <v>-7.2</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -4335,39 +4328,37 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 5 - 7/3 , LONG - 5 - 7/3 , LONG - 2 - 10/1</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+ALT -  - 20/6 , ALT -  - 16/5 , -</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/+2/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/+2/%100)
-Q - TP2/10G - %82 / 103 işlem - ADAY (3g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-7/%40)
-R - TP5/20G - %80 / 102 işlem - ADAY (18g/-7/%25)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-17/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-17/%10)
+Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-17/%5)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -4376,10 +4367,10 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>26.60000038</v>
+        <v>2.82999992</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
@@ -4389,7 +4380,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-1.9</v>
+        <v>-2.9</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -4403,12 +4394,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 20/7 , ALT -  - 31/7 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 21/8 , ALT -  - 33/9 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -4426,8 +4417,8 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-2/%92)
-L - TP5/10G - %77 / 43 işlem - ADAY (1g/-2/%93)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-5/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/-5/%83)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -4437,24 +4428,24 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>72</v>
+        <v>69.90000153</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-2</v>
+        <v>-2.9</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -4468,36 +4459,37 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 11/0 , ALT -  - 11/0 , LONG - 5 - 11/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 7 - 15/2 , LONG - 7 - 15/2 , -</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>H-TP2/10G, Q-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (9g/-6/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%95)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-7/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-7/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-21/%15)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 76 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -4506,10 +4498,10 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>2.8900001</v>
+        <v>6.5999999</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
@@ -4519,7 +4511,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.1</v>
+        <v>-2.3</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -4533,12 +4525,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 33 - 3/7 , LONG - 31 - 3/7 , LONG - 31 - 3/7</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 34 - 5/5 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>1</v>
@@ -4556,9 +4548,9 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/+1/%100)
-H - TP5/10G - %70 / 20 işlem - ADAY (3g/+1/%100)
-H - TP5/20G - %85 / 20 işlem - ADAY (3g/+1/%100)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-1/%69)
+H - TP5/10G - %70 / 20 işlem - ADAY (4g/-1/%100)
+H - TP5/20G - %85 / 20 işlem - ADAY (4g/-1/%100)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -4568,24 +4560,24 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>11.48999977</v>
+        <v>11.22999954</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.1</v>
+        <v>-5.7</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -4599,57 +4591,59 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 29/1 , ALT -  - 23/5 , LONG - 3 - 33/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 72 - 21/1 , ALT -  - 24/1 , -</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (14g/-3/%40)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-16/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-13/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (5g/-13/%60)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>37.52000046</v>
+        <v>55.15000153</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-1.5</v>
+        <v>-4.2</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -4663,58 +4657,57 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 24/1 , LONG - 7 - 28/6 , LONG - 7 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 38/2</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-1/%92)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-1/%85)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-7/%35)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>94.34999847</v>
+        <v>35.93999863</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-6</v>
+        <v>0.7</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -4728,59 +4721,60 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 18/7 , ALT -  - 18/7 , -</t>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+LONG - 6 - 6/4 , LONG - 6 - 6/4 , LONG - 3 - 9/1</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (5g/-10/%55)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/-8/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-10/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+3/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/+3/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)
+R - TP5/20G - %80 / 102 işlem - ADAY (19g/-6/%16)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>14.18000031</v>
+        <v>26.78000069</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-1.2</v>
+        <v>-3.3</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -4794,12 +4788,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 13/2 , SHORT - 89 - 13/7 , LONG - 9 - 17/0</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
@@ -4812,42 +4806,42 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/0/%85)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/0/%80)
-I - TP5/20G - %82 / 67 işlem - ADAY (4g/0/%85)
-Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-8/%20)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)
+I - TP5/20G - %82 / 67 işlem - ADAY (19g/-5/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>295</v>
+        <v>78</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.5</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -4861,58 +4855,61 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 75/59 , ALT -  - 103/50 , ALT -  - 75/59</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>L-TP5/10G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %77 / 43 işlem - ADAY (9g/-29/%38)
-Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-43/%10)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-8/%55)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-8/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-8/%35)
+R - TP5/20G - %80 / 102 işlem - ADAY (16g/-18/%20)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 73 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>19.10000038</v>
+        <v>2.86999989</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2.4</v>
+        <v>-3.3</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -4926,37 +4923,36 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 23 - 17/8 , ALT -  - 20/6 , ALT -  - 19/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 28/5 , LONG - 8 - 32/3 , LONG - 8 - 9/2</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-3/%75)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-2/%90)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-2/%80)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-4/%70)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -4965,20 +4961,20 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>78.09999847</v>
+        <v>91.19999695</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-2.4</v>
+        <v>-0.7</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -4992,36 +4988,38 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (3g/-6/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (3g/-6/%89)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-1/%95)
+I - TP5/10G - %61 / 109 işlem - ADAY (5g/-1/%90)
+I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-9/%20)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -5030,20 +5028,20 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>35.13999939</v>
+        <v>293</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -5057,35 +5055,37 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 30/6 , ALT -  - 25/11 , ALT -  - 24/10</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (13g/-8/%25)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-7/%55)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-6/%85)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%25)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -5094,20 +5094,20 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>7.80000019</v>
+        <v>74.44999695</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -5121,57 +5121,58 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 61 - 8/4 , SHORT - 63 - 8/4 , ALT -  - 13/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 67 - 14/3 , SHORT - 144 - 30/4 , LONG - 8 - 13/0</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-6/%25)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>295.5</v>
+        <v>160.30000305</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -5185,7 +5186,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
 -</t>
         </is>
       </c>
@@ -5208,7 +5209,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-2/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-10/%10)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -5222,20 +5223,20 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>6.19000006</v>
+        <v>7.5999999</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-1.2</v>
+        <v>-4.5</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -5249,12 +5250,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , SHORT - 86 - 27/6 , ALT -  - 18/5</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
@@ -5267,17 +5268,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/0/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-5/%75)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -5286,20 +5287,20 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>231.8999939</v>
+        <v>22.36000061</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-1.2</v>
+        <v>-2.9</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -5313,12 +5314,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 66 - 12/4 , SHORT - 143 - 28/6 , LONG - 7 - 11/2</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -5331,39 +5332,39 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-4/%55)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>163.19999695</v>
+        <v>99.40000153</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-1.6</v>
+        <v>-3.5</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -5377,12 +5378,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 6 - 17/4 , LONG - 3 - 21/1 , ALT -  - 23/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 62 - 11/1 , SHORT - 64 - 11/2 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
@@ -5395,39 +5396,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-5/%65)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>538.5</v>
+        <v>285.25</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.1</v>
+        <v>-2.1</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -5441,62 +5442,57 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 0, TOPLAM 4, İZLE
-LONG - 12 - 15/15 , LONG - 11 - 18/13 , SHORT - 1 - 0/9</t>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
-Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
-U - TP5/20G - %74 / 74 işlem - ADAY (3g/0/%100)
-V - TP2/10G - %95 / 21 işlem - ADAY (3g/0/%100)
-V - TP5/10G - %75 / 20 işlem - ADAY (4g/+2/%100)
-Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-4/%25)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>72.69999695</v>
+        <v>6.05999994</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-2.6</v>
+        <v>-0.5</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -5510,57 +5506,57 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 3 - 5/10 , UST -  - 1/15 , SHORT - 2 - 3/12</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 34/1 , ALT -  - 102/50 , ALT -  - 74/57</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (15g/-9/%40)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-43/%10)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>682.5</v>
+        <v>19</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -5574,57 +5570,57 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-11/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-3/%85)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>3.48000002</v>
+        <v>225</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.6</v>
+        <v>-3.5</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -5638,57 +5634,57 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
-SHORT - 1 - 1/8 , SHORT - 1 - 1/8 , SHORT - 3 - 2/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 17/4 , ALT -  - 25/3 , ALT -  - 27/8</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (1g/-2/%95)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-10/%50)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>20.57999992</v>
+        <v>67.05000305</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-2.2</v>
+        <v>-4.6</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -5702,57 +5698,58 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-UST -  - 1/10 , UST -  - 0/10 , SHORT - 11 - 5/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (16g/-2/%50)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-10/%78)
+S - TP5/20G - %82 / 22 işlem - ADAY (4g/-10/%89)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>105.90000153</v>
+        <v>33.54000092</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.8</v>
+        <v>-5.9</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -5766,57 +5763,58 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 1 - 4/19 , SHORT - 1 - 3/24 , UST -  - 7/17</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 40/3 , LONG - 8 - 34/1 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>E-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-7/%82)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-24/%15)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-10/%15)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>47.08000183</v>
+        <v>3.5</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.7</v>
+        <v>-5.9</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -5830,59 +5828,57 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 1 - 12/1 , LONG - 3 - 10/2 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 40/3 , ALT -  - 16/5 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (13g/-10/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (11g/-10/%20)
-Y - TP5/20G - %71 / 98 işlem - ADAY (12g/-10/%15)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-7/%50)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>3.04999995</v>
+        <v>2.72000003</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-3.7</v>
+        <v>-4.2</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -5896,37 +5892,40 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 0, TOPLAM 4, İZLE
-LONG - 6 - 14/3 , LONG - 6 - 14/3 , -</t>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+LONG - 13 - 20/11 , LONG - 13 - 20/11 , SHORT - 2 - 5/5</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (8g/-5/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (8g/-5/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-19/%15)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-4/%100)
+Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-4/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-4/%70)
+V - TP2/10G - %95 / 21 işlem - ADAY (4g/-4/%88)
+V - TP5/10G - %75 / 20 işlem - ADAY (5g/-2/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-4/%70)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -5935,20 +5934,20 @@
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>6.80000019</v>
+        <v>69.65000153</v>
       </c>
       <c r="O31" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-1.6</v>
+        <v>-5.1</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -5962,61 +5961,57 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 0, TOPLAM 1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 11/5 , SHORT - 1 - 5/11 , SHORT - 3 - 9/7</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-1/%85)
-I - TP5/10G - %61 / 109 işlem - ADAY (4g/-1/%80)
-I - TP5/20G - %82 / 67 işlem - ADAY (4g/-1/%85)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%95)
-R - TP5/20G - %80 / 102 işlem - ADAY (15g/-12/%20)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-14/%40)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>3.06999993</v>
+        <v>647.5</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -6030,59 +6025,57 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 20 - 14/7 , LONG - 6 - 15/2 , LONG - 32 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 1 - 2/8 , SHORT - 1 - 2/8 , SHORT - 12 - 8/3</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (3g/-2/%92)
-U - TP5/20G - %74 / 74 işlem - ADAY (11g/-1/%85)
-Z - TP5/20G - %75 / 71 işlem - ADAY (11g/-1/%55)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-4/%50)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>2.03999996</v>
+        <v>103.59999847</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-0.5</v>
+        <v>-3.8</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -6096,54 +6089,53 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 19 - 8/8 , SHORT - 17 - 9/7 , LONG - 5 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 2 - 5/5 , SHORT - 2 - 5/5 , SHORT - 4 - 6/4</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>K-TP5/20G, Q-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %90 / 51 işlem - ONAY (14g/-1/%63)
-Q - TP5/20G - %70 / 203 işlem - ADAY (6g/+3/%100)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-5/%85)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 75 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>216.30000305</v>
+        <v>19.79999924</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -6161,35 +6153,35 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 15 - 25/8 , LONG - 20 - 6/6 , LONG - 19 - 4/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 6/17 , SHORT - 2 - 5/22 , UST -  - 4/15</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (3g/-1/%90)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-9/%73)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -6198,20 +6190,20 @@
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>89.30000305</v>
+        <v>46.08000183</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-0.2</v>
+        <v>-2</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -6225,57 +6217,59 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 0, TOPLAM -1, ALMA
-LONG - 31 - 5/7 , LONG - 39 - 6/6 , LONG - 76 - 10/10</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 21 - 16/5 , LONG - 7 - 17/0 , LONG - 33 - 7/3</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (18g/+1/%100)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)
+Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-3/%50)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>133.8999939</v>
+        <v>2</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>-4.8</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -6289,36 +6283,37 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 46 - 1/14 , LONG - 81 - 5/14 , SHORT - 4 - 0/15</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 11/18 , LONG - 8 - 10/18 , UST -  - 5/14</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (4g/0/%100)
-Z - TP5/20G - %75 / 71 işlem - ADAY (4g/0/%100)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/-5/%93)
+X - TP5/10G - %82 / 44 işlem - ADAY (1g/-5/%81)
+Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -6327,20 +6322,20 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>225.5</v>
+        <v>2.79999995</v>
       </c>
       <c r="O37" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -6354,36 +6349,36 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 9 - 6/4 , LONG - 9 - 6/4 , SHORT - 11 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+SHORT - 17 - 4/12 , LONG - 82 - 8/11 , SHORT - 5 - 3/12</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-3/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-3/%70)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-3/%85)
+Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-3/%80)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
@@ -6392,20 +6387,20 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>52.25</v>
+        <v>218.80000305</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-0.6</v>
+        <v>-3.9</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -6419,12 +6414,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 11 - 5/5 , SHORT - 11 - 5/5 , SHORT - 11 - 5/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 18 - 29/5 , LONG - 21 - 10/2 , LONG - 20 - 8/2</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>0</v>
@@ -6437,17 +6432,17 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-5/%70)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
@@ -6456,20 +6451,20 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>21.73999977</v>
+        <v>85.80000305</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-0.2</v>
+        <v>-4.6</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -6483,12 +6478,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 6 - 3/6 , LONG - 10 - 14/10 , LONG - 8 - 15/10</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+LONG - 32 - 10/3 , LONG - 40 - 11/2 , LONG - 77 - 15/6</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -6506,7 +6501,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/+2/%100)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-3/%13)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -6516,14 +6511,14 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>19.70000076</v>
+        <v>127.80000305</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
@@ -6533,7 +6528,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-5.2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -6547,12 +6542,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 1 - 4/7 , LONG - 25 - 14/10 , SHORT - 1 - 3/6</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+SHORT - 2 - 5/7 , LONG - 26 - 14/10 , SHORT - 2 - 3/6</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>1</v>
@@ -6570,8 +6565,8 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-5/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -6581,14 +6576,14 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
         <v>284.25</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
@@ -6598,7 +6593,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -6612,12 +6607,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 11 - 10/1 , SHORT - 12 - 11/2 , SHORT - 12 - 11/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 11/0 , SHORT - 13 - 12/1 , SHORT - 13 - 12/1</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -6635,10 +6630,10 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (3g/-2/%95)
-Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-2/%90)
-R - TP2/10G - %84 / 119 işlem - ADAY (3g/-2/%90)
-R - TP5/10G - %60 / 138 işlem - ADAY (3g/-2/%95)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-3/%70)
+Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-3/%80)
+R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
+R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%80)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -6648,14 +6643,14 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>1.00999999</v>
+        <v>1</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
@@ -6665,7 +6660,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-2.6</v>
+        <v>-1.3</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -6679,12 +6674,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 43 - 14/10 , SHORT - 3 - 4/6 , SHORT - 3 - 4/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 44 - 16/9 , SHORT - 4 - 6/4 , SHORT - 4 - 6/4</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -6702,9 +6697,9 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (1g/-3/%60)
-U - TP2/10G - %75 / 97 işlem - ADAY (3g/-4/%70)
-U - TP5/20G - %74 / 74 işlem - ADAY (11g/-3/%80)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-4/%55)
+U - TP2/10G - %75 / 97 işlem - ADAY (4g/-5/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (12g/-4/%80)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -6714,24 +6709,24 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>114.30000305</v>
+        <v>112.80000305</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-4.9</v>
+        <v>-3.5</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -6745,59 +6740,58 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-ALT -  - 53/39 , LONG - 7 - 28/5 , ALT -  - 11/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+UST -  - 2/12 , SHORT - 2 - 5/17 , SHORT - 2 - 4/6</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, R-TP5/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-20/%10)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-22/%0)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-4/%60)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-5/%60)
+U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%70)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 92 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>3.72000003</v>
+        <v>58.29999924</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -6811,58 +6805,57 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-UST -  - 6/15 , LONG - 45 - 6/22 , SHORT - 1 - 0/9</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 12 - 7/3 , SHORT - 12 - 7/3 , SHORT - 12 - 7/3</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (1g/-2/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (3g/0/%100)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>60.40000153</v>
+        <v>21.34000015</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-2.4</v>
+        <v>-3.7</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -6876,12 +6869,12 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 7 - 7/3 , SHORT - 13 - 7/3 , SHORT - 11 - 7/6</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 7/3 , LONG - 11 - 18/7 , LONG - 9 - 19/7</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -6894,17 +6887,17 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-6/%60)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-1/%80)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -6913,20 +6906,20 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>21.78000069</v>
+        <v>18.97999954</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-5.4</v>
+        <v>-3.4</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -6940,57 +6933,58 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 11/0 , SHORT - 22 - 10/0 , ALT -  - 11/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 4 - 6/4 , LONG - 10 - 9/1 , SHORT - 12 - 9/1</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-5/%75)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-6/%75)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-6/%60)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>372.5</v>
+        <v>50.45000076</v>
       </c>
       <c r="O47" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-2.6</v>
+        <v>-3.8</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -7004,12 +6998,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 12/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 14 - 12/1 , ALT -  - 11/1 , SHORT - 12 - 11/2</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -7022,39 +7016,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-2/%75)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>11.09000015</v>
+        <v>20.95999908</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -7068,8 +7062,8 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 15 - 10/18 , SHORT - 15 - 10/6 , SHORT - 11 - 8/2</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 14/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -7091,7 +7085,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%80)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-3/%60)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -7105,20 +7099,20 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>136.5</v>
+        <v>10.92000008</v>
       </c>
       <c r="O49" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-3.9</v>
+        <v>-3.2</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -7132,12 +7126,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 13/1 , LONG - 24 - 21/1 , ALT -  - 23/5</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 16 - 14/16 , SHORT - 16 - 13/4 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -7150,39 +7144,39 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (4g/-6/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-4/%60)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>69.44999695</v>
+        <v>132.1000061</v>
       </c>
       <c r="O50" s="8" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-1.3</v>
+        <v>-6</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -7196,51 +7190,116 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-LONG - 10 - 4/7 , LONG - 6 - 5/5 , LONG - 5 - 7/3</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+ALT -  - 42/5 , ALT -  - 25/6 , ALT -  - 18/5</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-6/%70)
+T - TP5/20G - %77 / 128 işlem - ADAY (1g/-6/%80)</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>2.67000008</v>
+      </c>
+      <c r="O51" s="8" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ASELS</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 9/1 , SHORT - 23 - 8/2 , LONG - 1 - 10/1</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="G52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/0/%80)</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-4/%60)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N51" s="7" t="n">
-        <v>102.40000153</v>
-      </c>
-      <c r="O51" s="8" t="n">
-        <v>46279</v>
+      <c r="N52" s="7" t="n">
+        <v>377</v>
+      </c>
+      <c r="O52" s="8" t="n">
+        <v>46280</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O51"/>
+  <autoFilter ref="A1:O52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -478,7 +478,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-3.7</v>
+        <v>-1.5</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -580,7 +580,8 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -602,7 +603,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (18g/?/%?)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (18g/-15/%38)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -616,10 +617,10 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>3.3499999</v>
+        <v>3.29999995</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -629,7 +630,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-6.5</v>
+        <v>-5.8</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -644,7 +645,7 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 17/4 , ALT -  - 24/12 , -</t>
+ALT -  - 16/3 , ALT -  - 24/12 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -666,11 +667,11 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (7g/-16/%40)
-X - TP2/10G - %98 / 46 işlem - ONAY (1g/-7/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-14/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (7g/-16/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (1g/-7/%88)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (7g/-15/%40)
+X - TP2/10G - %98 / 46 işlem - ONAY (1g/-6/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-13/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-15/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (1g/-6/%88)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -684,7 +685,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>13.27</v>
+        <v>13.37</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46281</v>
@@ -697,7 +698,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-6.3</v>
+        <v>-10</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -712,7 +713,7 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>BIS +1, PHL +2, CNDL 0, XU030 +1, TOPLAM 4, İZLE
-SHORT - 17 - 22/0 , ALT -  - 17/4 , -</t>
+ALT -  - 27/4 , ALT -  - 22/8 , -</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -734,7 +735,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-19/%40)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-22/%40)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -748,7 +749,7 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>15.57</v>
+        <v>14.96</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46281</v>
@@ -761,7 +762,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-7.6</v>
+        <v>-6.8</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -776,7 +777,7 @@
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 32/17 , ALT -  - 32/17 , -</t>
+ALT -  - 31/16 , ALT -  - 31/16 , -</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
@@ -800,7 +801,7 @@
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (7g/-16/%80)
 L - TP5/10G - %77 / 43 işlem - ADAY (8g/-14/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-16/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-15/%30)
 R - TP5/20G - %80 / 102 işlem - ADAY (7g/-16/%40)</t>
         </is>
       </c>
@@ -815,7 +816,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>251.5</v>
+        <v>253.75</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46281</v>
@@ -889,158 +890,160 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
+          <t>TUKAS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 22 - 18/3 , ALT -  - 20/2 , LONG - 34 - 9/1</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-7/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-5/%60)
+Z - TP5/20G - %75 / 71 işlem - ADAY (13g/-5/%50)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TSKB</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B8" s="3" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 LONG - 35 - 10/0 , LONG - 33 - 10/0 , LONG - 33 - 10/0</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-6/%67)
 H - TP5/10G - %70 / 20 işlem - ADAY (5g/-6/%88)
 H - TP5/20G - %85 / 20 işlem - ADAY (5g/-6/%100)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N7" s="7" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="O7" s="8" t="n">
+      <c r="N8" s="7" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="O8" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>MIATK</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B9" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-18/%82)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IZENR</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 21/3 , ALT -  - 21/3 , -</t>
-        </is>
-      </c>
       <c r="F9" s="6" t="n">
         <v>55</v>
       </c>
@@ -1048,34 +1051,33 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (10g/-14/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-27/%10)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-18/%82)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>6.12</v>
+        <v>31.22</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46281</v>
@@ -1084,11 +1086,11 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-4.2</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1102,8 +1104,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 24/10 , ALT -  - 19/8 , -</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+ALT -  - 25/6 , ALT -  - 25/6 , -</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1113,35 +1115,34 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (15g/-20/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-20/%15)
-Y - TP5/20G - %71 / 98 işlem - ADAY (14g/-20/%5)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (10g/-16/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-29/%10)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>2.71</v>
+        <v>5.96</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46281</v>
@@ -1150,11 +1151,11 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-3.9</v>
+        <v>-5.3</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1168,8 +1169,8 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 23/0 , ALT -  - 26/3 , -</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 25/11 , ALT -  - 20/9 , -</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -1186,28 +1187,28 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-20/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-17/%15)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-17/%55)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (15g/-21/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-21/%15)
+Y - TP5/20G - %71 / 98 işlem - ADAY (14g/-21/%5)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>53</v>
+        <v>2.68</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46281</v>
@@ -1216,11 +1217,11 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-4.5</v>
+        <v>-6</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1234,36 +1235,37 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 37/2 , ALT -  - 37/2 , ALT -  - 13/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 25/2 , ALT -  - 28/5 , -</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-8/%60)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-21/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-18/%15)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-18/%55)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1272,7 +1274,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>87.09999999999999</v>
+        <v>51.85</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46281</v>
@@ -1281,46 +1283,111 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 36/1 , ALT -  - 36/1 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-8/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%60)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>PSGYO</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B14" s="3" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-17/%40)
 I - TP5/10G - %61 / 109 işlem - ADAY (6g/-17/%50)
@@ -1329,82 +1396,18 @@
 R - TP5/20G - %80 / 102 işlem - ADAY (17g/-26/%15)</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="N14" s="7" t="n">
         <v>2.59</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 41/11 , ALT -  - 35/15 , ALT -  - 45/7</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-12/%20)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>34.16</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46281</v>
@@ -1413,95 +1416,92 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 40/10 , ALT -  - 34/14 , ALT -  - 44/6</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-11/%20)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>GRSEL</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B16" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-6/%65)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-6/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-6/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-13/%0)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>278.5</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 36/11 , ALT -  - 31/16 , ALT -  - 29/15</t>
-        </is>
-      </c>
       <c r="F16" s="6" t="n">
         <v>49</v>
       </c>
@@ -1509,100 +1509,102 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-4/%90)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-4/%65)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-4/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-11/%0)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>284.25</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 36/11 , ALT -  - 31/16 , ALT -  - 30/15</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I17" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-12/%50)
 I - TP5/20G - %82 / 67 işlem - ADAY (7g/-11/%75)
 R - TP5/10G - %60 / 138 işlem - ADAY (7g/-11/%0)</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N16" s="7" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>OYAKC</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 17/3 , ALT -  - 16/5 , ALT -  - 16/2</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
-U - TP5/20G - %74 / 74 işlem - ADAY (15g/-13/%27)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 77 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
       <c r="N17" s="7" t="n">
-        <v>19.97</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46281</v>
@@ -1615,7 +1617,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1629,8 +1631,8 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 14/3 , SHORT - 90 - 14/7 , ALT -  - 18/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 13/2 , SHORT - 90 - 14/7 , LONG - 10 - 17/0</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1666,7 +1668,7 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>77.3</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46281</v>
@@ -1675,11 +1677,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1693,38 +1695,36 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/1 , ALT -  - 12/2 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (5g/-6/%40)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-6/%60)
-R - TP2/10G - %84 / 119 işlem - ADAY (5g/-6/%40)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-6/%40)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-10/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-10/%50)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>0.96</v>
+        <v>48.18</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46281</v>
@@ -1742,11 +1742,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 7 - 9/1 , ALT -  - 11/1 , ALT -  - 12/1</t>
+ALT -  - 14/1 , ALT -  - 14/1 , ALT -  - 14/1</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1771,26 +1771,27 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/0/%90)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/0/%70)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-9/%0)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (5g/-5/%40)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-5/%75)
+R - TP2/10G - %84 / 119 işlem - ADAY (5g/-5/%45)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-5/%45)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1799,7 +1800,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>26</v>
+        <v>0.97</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46281</v>
@@ -1808,11 +1809,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-4.5</v>
+        <v>-3.7</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1826,35 +1827,37 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 11/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 7 - 10/1 , ALT -  - 12/1 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-1/%90)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-1/%70)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-9/%0)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -1863,7 +1866,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>20.38</v>
+        <v>25.78</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46281</v>
@@ -1872,11 +1875,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-4.5</v>
+        <v>-3.3</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1891,11 +1894,11 @@
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 22/8 , ALT -  - 31/7 , ALT -  - 32/13</t>
+SHORT - 13 - 10/0 , SHORT - 13 - 10/0 , SHORT - 13 - 10/0</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -1908,17 +1911,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-14/%45)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -1927,7 +1930,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>64.05</v>
+        <v>20.64</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46281</v>
@@ -1936,11 +1939,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1954,36 +1957,35 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 18/4 , ALT -  - 16/5 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-14/%80)
-S - TP5/20G - %82 / 22 işlem - ADAY (5g/-14/%90)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-14/%27)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -1992,7 +1994,7 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>32.18</v>
+        <v>19.82</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46281</v>
@@ -2001,11 +2003,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-2.3</v>
+        <v>-6</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2019,45 +2021,44 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 16/3 , SHORT - 68 - 17/1 , ALT -  - 15/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 23/9 , ALT -  - 32/8 , ALT -  - 34/14</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-2/%85)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-8/%5)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-15/%45)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>156.6</v>
+        <v>63.05</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>46281</v>
@@ -2066,11 +2067,11 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-7.8</v>
+        <v>3.3</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -2095,24 +2096,25 @@
         <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-17/%15)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-8/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (5g/-8/%90)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2121,7 +2123,7 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>7.01</v>
+        <v>34.64</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46281</v>
@@ -2130,11 +2132,11 @@
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-2</v>
+        <v>-2.7</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2148,8 +2150,8 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 28/5 , ALT -  - 28/5 , ALT -  - 30/11</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 16/3 , SHORT - 68 - 17/0 , ALT -  - 15/2</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
@@ -2159,33 +2161,34 @@
         <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-2/%85)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-8/%5)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>502.5</v>
+        <v>155.9</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46281</v>
@@ -2194,11 +2197,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.9</v>
+        <v>-2.1</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2213,7 +2216,7 @@
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 18/5 , SHORT - 87 - 32/3 , ALT -  - 23/9</t>
+LONG - 2 - 10/0 , SHORT - 24 - 9/1 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2235,7 +2238,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-9/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-6/%60)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2249,7 +2252,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>21.26</v>
+        <v>369.25</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>46281</v>
@@ -2258,11 +2261,11 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-3.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -2277,7 +2280,7 @@
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 13/0 , ALT -  - 13/0 , ALT -  - 20/9</t>
+-</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
@@ -2299,7 +2302,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-8/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-18/%15)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2313,7 +2316,7 @@
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>276.5</v>
+        <v>6.86</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>46281</v>
@@ -2322,382 +2325,382 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
+          <t>MGROS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 27/4 , ALT -  - 27/4 , ALT -  - 29/10</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-1/%100)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>507</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , SHORT - 87 - 29/5 , ALT -  - 20/6</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-7/%50)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 12 - 10/3 , ALT -  - 11/0 , ALT -  - 12/2</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-6/%20)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/0 , SHORT - 65 - 12/0 , ALT -  - 19/8</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-7/%50)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>278.25</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>TURSG</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="B33" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F33" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-6/%5)</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N29" s="7" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="O29" s="8" t="n">
+      <c r="N33" s="7" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="O33" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>AKSA</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="B34" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 ALT -  - 18/7 , ALT -  - 18/7 , ALT -  - 18/7</t>
         </is>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-7/%20)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N30" s="7" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 38/2 , ALT -  - 115/59 , ALT -  - 83/66</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-47/%0)</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 46/8 , ALT -  - 20/9 , ALT -  - 20/9</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-12/%30)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TABGD</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/?/%?)</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="n">
-        <v>225</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>HEKTS</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 52/12 , ALT -  - 33/13 , ALT -  - 26/11</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/-12/%55)
-T - TP5/20G - %77 / 128 işlem - ADAY (2g/-12/%70)</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N34" s="7" t="n">
-        <v>2.49</v>
+        <v>10.48</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46281</v>
@@ -2706,11 +2709,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-7.7</v>
+        <v>-4.7</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2724,45 +2727,44 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 74/57 , ALT -  - 38/2 , ALT -  - 22/11</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 35/0 , ALT -  - 109/55 , ALT -  - 79/62</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-30/%5)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-17/%0)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-46/%0)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>3.23</v>
+        <v>18.1</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46281</v>
@@ -2771,11 +2773,11 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-4.9</v>
+        <v>-3.7</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2790,43 +2792,43 @@
       <c r="E36" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 5 - 16/1 , SHORT - 2 - 10/7 , SHORT - 4 - 14/3</t>
+ALT -  - 44/6 , ALT -  - 19/7 , ALT -  - 19/7</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-18/%25)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-10/%30)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>615.5</v>
+        <v>2.62</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46281</v>
@@ -2835,46 +2837,368 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
+          <t>TABGD</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TRMET</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 17 - 19/12 , SHORT - 17 - 16/1 , ALT -  - 15/4</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-9/%25)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 52/12 , ALT -  - 33/14 , ALT -  - 26/12</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/-13/%55)
+T - TP5/20G - %77 / 128 işlem - ADAY (2g/-13/%70)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 69/53 , ALT -  - 38/2 , ALT -  - 19/8</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-28/%5)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-14/%0)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BRSAN</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 5 - 14/3 , SHORT - 2 - 8/8 , SHORT - 4 - 12/5</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-16/%25)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>627</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>KUYAS</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B42" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 ALT -  - 16/3 , ALT -  - 57/16 , ALT -  - 16/5</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F42" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G42" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I42" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-14/%91)
 Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-14/%75)
@@ -2884,600 +3208,276 @@
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N37" s="7" t="n">
+      <c r="N42" s="7" t="n">
         <v>62.7</v>
       </c>
-      <c r="O37" s="8" t="n">
+      <c r="O42" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>TRENJ</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="B43" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 6/4 , SHORT - 2 - 6/4 , ALT -  - 11/1</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
+SHORT - 2 - 7/3 , SHORT - 2 - 7/3 , ALT -  - 12/2</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="G38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="G43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>P-TP5/20G</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-8/%40)</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N38" s="7" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="O38" s="8" t="n">
+      <c r="N43" s="7" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="O43" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>EKGYO</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="B44" s="3" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
+ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="G39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="G44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>H-TP2/10G</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-10/%82)</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-11/%82)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N39" s="7" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="O39" s="8" t="n">
+      <c r="N44" s="7" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="O44" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>HALKB</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="B45" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 3 - 10/14 , SHORT - 3 - 9/19 , UST -  - 0/12</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="n">
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+SHORT - 3 - 7/16 , SHORT - 3 - 6/21 , UST -  - 3/14</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="G45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>K-TP5/10G</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (6g/-12/%73)</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (6g/-10/%73)</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N40" s="7" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="O40" s="8" t="n">
+      <c r="N45" s="7" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="O45" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SASA</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 22 - 20/2 , ALT -  - 21/3 , LONG - 34 - 10/1</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-8/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (13g/-6/%60)
-Z - TP5/20G - %75 / 71 işlem - ADAY (13g/-6/%50)</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N41" s="7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O41" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SASA</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 SHORT - 2 - 15/15 , SHORT - 2 - 15/9 , SHORT - 1 - 5/5</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F46" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="G42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="6" t="n">
+      <c r="G46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I46" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>X - TP5/20G - %93 / 43 işlem - ONAY (2g/-14/%92)
 X - TP5/10G - %82 / 44 işlem - ADAY (2g/-14/%79)
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N42" s="7" t="n">
+      <c r="N46" s="7" t="n">
         <v>2.52</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>KCHOL</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 18 - 9/7 , SHORT - 6 - 10/3 , SHORT - 6 - 8/8</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-7/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%60)</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="n">
-        <v>208.7</v>
-      </c>
-      <c r="O43" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AEFES</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 8 - 10/1 , LONG - 12 - 22/4 , LONG - 10 - 22/4</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-5/%75)</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="O44" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ENKAI</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-LONG - 17 - 34/1 , LONG - 22 - 13/0 , ALT -  - 11/1</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-8/%60)</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="n">
-        <v>82.95</v>
-      </c>
-      <c r="O45" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>TOASO</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 3 - 9/3 , SHORT - 3 - 9/3 , SHORT - 3 - 8/3</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-9/%55)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-9/%50)</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N46" s="7" t="n">
-        <v>271.5</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46281</v>
@@ -3486,11 +3486,11 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3504,36 +3504,36 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , ALT -  - 12/1 , ALT -  - 13/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 18 - 8/8 , SHORT - 6 - 9/4 , SHORT - 6 - 8/8</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-10/%55)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-10/%50)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-6/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%65)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>48.4</v>
+        <v>209.6</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46281</v>
@@ -3551,11 +3551,11 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-4.3</v>
+        <v>-2.7</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3569,8 +3569,8 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 13 - 10/2 , SHORT - 5 - 10/0 , SHORT - 5 - 10/0</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 8 - 9/1 , LONG - 12 - 21/5 , LONG - 10 - 22/4</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3580,228 +3580,228 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-4/%90)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ENKAI</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 17 - 32/2 , LONG - 22 - 11/1 , LONG - 21 - 10/1</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-7/%60)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 3 - 8/5 , LONG - 27 - 17/8 , SHORT - 3 - 6/4</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-8/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-8/%50)</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="O50" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ENJSA</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 13 - 11/2 , ALT -  - 11/0 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I51" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-8/%45)
 U - TP2/10G - %75 / 97 işlem - ADAY (5g/-9/%40)
 U - TP5/20G - %74 / 74 işlem - ADAY (13g/-9/%60)</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N48" s="7" t="n">
-        <v>108</v>
-      </c>
-      <c r="O48" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SOKM</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 1/8 , SHORT - 3 - 9/14 , SHORT - 3 - 8/3</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (3g/-8/%50)
-U - TP5/20G - %74 / 74 işlem - ADAY (5g/-7/%75)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="O49" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ASELS</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 12/2 , ALT -  - 11/0 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-8/%60)</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N50" s="7" t="n">
-        <v>361.25</v>
-      </c>
-      <c r="O50" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 12 - 12/1 , ALT -  - 13/3 , ALT -  - 15/4</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-8/%5)</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N51" s="7" t="n">
-        <v>94.8</v>
+        <v>107.3</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46281</v>
@@ -3810,11 +3810,11 @@
     <row r="52" ht="32" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-4.3</v>
+        <v>-2.7</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3829,34 +3829,35 @@
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 17 - 19/12 , SHORT - 17 - 16/1 , ALT -  - 15/4</t>
+SHORT - 1 - 0/9 , SHORT - 3 - 8/15 , SHORT - 3 - 7/3</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-9/%25)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (3g/-7/%50)
+U - TP5/20G - %74 / 74 işlem - ADAY (5g/-6/%75)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
@@ -3865,7 +3866,7 @@
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>126.4</v>
+        <v>56.75</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>46281</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-5.8</v>
+        <v>-5.4</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 16/3 , ALT -  - 24/12 , -</t>
+ALT -  - 16/3 , ALT -  - 23/12 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>13.37</v>
+        <v>13.43</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46281</v>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-6.8</v>
+        <v>-9.6</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 31/16 , ALT -  - 31/16 , -</t>
+ALT -  - 36/20 , ALT -  - 36/20 , -</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
@@ -799,10 +799,10 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (7g/-16/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (8g/-14/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-15/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (7g/-16/%40)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (7g/-18/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (8g/-17/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-18/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (7g/-18/%40)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>253.75</v>
+        <v>246.2</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46281</v>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 22 - 18/3 , ALT -  - 20/2 , LONG - 34 - 9/1</t>
+LONG - 22 - 21/1 , ALT -  - 22/4 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -931,9 +931,9 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-7/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (13g/-5/%60)
-Z - TP5/20G - %75 / 71 işlem - ADAY (13g/-5/%50)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-7/%60)
+Z - TP5/20G - %75 / 71 işlem - ADAY (13g/-7/%45)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46281</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-5.3</v>
+        <v>-7.4</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 35 - 10/0 , LONG - 33 - 10/0 , LONG - 33 - 10/0</t>
+ALT -  - 13/3 , ALT -  - 13/3 , ALT -  - 13/3</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -997,9 +997,9 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-6/%67)
-H - TP5/10G - %70 / 20 işlem - ADAY (5g/-6/%88)
-H - TP5/20G - %85 / 20 işlem - ADAY (5g/-6/%100)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-9/%67)
+H - TP5/10G - %70 / 20 işlem - ADAY (5g/-9/%88)
+H - TP5/20G - %85 / 20 işlem - ADAY (5g/-9/%100)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>10.63</v>
+        <v>10.4</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46281</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 25/6 , ALT -  - 25/6 , -</t>
+ALT -  - 25/7 , ALT -  - 25/7 , -</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (10g/-16/%75)
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (10g/-17/%75)
 Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-29/%10)</t>
         </is>
       </c>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>5.96</v>
+        <v>5.94</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46281</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-6</v>
+        <v>-6.9</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 25/2 , ALT -  - 28/5 , -</t>
+ALT -  - 26/3 , ALT -  - 30/6 , -</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1258,9 +1258,9 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-21/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-18/%15)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-18/%55)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-22/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-19/%15)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-19/%55)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>51.85</v>
+        <v>51.35</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46281</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-3.7</v>
+        <v>-5.1</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 36/1 , ALT -  - 36/1 , ALT -  - 12/1</t>
+ALT -  - 39/3 , ALT -  - 38/2 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1324,8 +1324,8 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-8/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%60)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-9/%60)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>87.84999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46281</v>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-4.4</v>
+        <v>-4.9</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 40/10 , ALT -  - 34/14 , ALT -  - 44/6</t>
+ALT -  - 41/11 , ALT -  - 35/15 , ALT -  - 45/7</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-11/%20)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-12/%20)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>34.36</v>
+        <v>34.18</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46281</v>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3</v>
+        <v>-3.6</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-4/%90)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-4/%65)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-4/%85)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-11/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-5/%85)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-5/%60)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-5/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-12/%0)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>284.25</v>
+        <v>282.5</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46281</v>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-5.8</v>
+        <v>-9.9</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 36/11 , ALT -  - 31/16 , ALT -  - 30/15</t>
+ALT -  - 43/17 , ALT -  - 38/22 , ALT -  - 36/21</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1588,9 +1588,9 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-12/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (7g/-11/%75)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-11/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-17/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-16/%75)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-16/%0)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>70.15000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46281</v>
@@ -1613,11 +1613,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.4</v>
+        <v>-4.5</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1631,8 +1631,8 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 13/2 , SHORT - 90 - 14/7 , LONG - 10 - 17/0</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 12/1 , LONG - 12 - 24/2 , LONG - 10 - 25/2</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-5/%70)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%65)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>77.65000000000001</v>
+        <v>18.12</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46281</v>
@@ -1677,11 +1677,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1696,35 +1696,34 @@
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/1 , ALT -  - 12/2 , ALT -  - 14/3</t>
+ALT -  - 15/4 , SHORT - 90 - 16/5 , ALT -  - 20/2</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-10/%55)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-10/%50)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%65)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1733,7 +1732,7 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>48.18</v>
+        <v>76.3</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46281</v>
@@ -1742,11 +1741,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-3</v>
+        <v>-5.1</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1760,8 +1759,8 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 14/1 , ALT -  - 14/1 , ALT -  - 14/1</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+ALT -  - 38/2 , ALT -  - 15/2 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1771,27 +1770,24 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (5g/-5/%40)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-5/%75)
-R - TP2/10G - %84 / 119 işlem - ADAY (5g/-5/%45)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-5/%45)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-10/%60)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1800,7 +1796,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>0.97</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46281</v>
@@ -1809,11 +1805,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-3.7</v>
+        <v>-6.2</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1827,37 +1823,36 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 7 - 10/1 , ALT -  - 12/1 , ALT -  - 13/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 17 - 19/2 , ALT -  - 15/4 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
         <v>47</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-1/%90)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/-1/%70)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-9/%0)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-12/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-12/%50)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -1866,7 +1861,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>25.78</v>
+        <v>47.32</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46281</v>
@@ -1875,11 +1870,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-3.3</v>
+        <v>-3</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1893,35 +1888,38 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 13 - 10/0 , SHORT - 13 - 10/0 , SHORT - 13 - 10/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 16/3 , ALT -  - 16/3 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (5g/-6/%40)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-6/%60)
+R - TP2/10G - %84 / 119 işlem - ADAY (5g/-6/%40)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-6/%40)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -1930,7 +1928,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>20.64</v>
+        <v>0.97</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46281</v>
@@ -1939,11 +1937,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-5.4</v>
+        <v>-5.8</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1957,35 +1955,37 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 18/4 , ALT -  - 16/5 , ALT -  - 16/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 13 - 12/0 , ALT -  - 12/2 , ALT -  - 12/2</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-14/%27)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-10/%45)
+U - TP2/10G - %75 / 97 işlem - ADAY (5g/-11/%40)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-10/%60)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>19.82</v>
+        <v>106.3</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46281</v>
@@ -2003,11 +2003,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-6</v>
+        <v>-4.8</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2021,35 +2021,37 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 23/9 , ALT -  - 32/8 , ALT -  - 34/14</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 11/1 , ALT -  - 14/3 , ALT -  - 14/4</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-15/%45)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-3/%75)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-3/%60)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-11/%0)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2058,7 +2060,7 @@
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>63.05</v>
+        <v>25.5</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>46281</v>
@@ -2067,1026 +2069,1024 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/1 , ALT -  - 11/1 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-8/%56)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 21/7 , ALT -  - 20/8 , ALT -  - 20/6</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-16/%27)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 27/13 , ALT -  - 37/12 , ALT -  - 38/18</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-17/%45)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>MAGEN</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="B28" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>S-TP5/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-12/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (5g/-12/%90)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 19/2 , ALT -  - 35/0 , ALT -  - 18/4</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-10/%0)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ASELS</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/4 , ALT -  - 13/2 , ALT -  - 16/5</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-10/%60)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DAPGM</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F31" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-8/%80)
-S - TP5/20G - %82 / 22 işlem - ADAY (5g/-8/%90)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-19/%15)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N25" s="7" t="n">
-        <v>34.64</v>
-      </c>
-      <c r="O25" s="8" t="n">
+      <c r="N31" s="7" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="O31" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MGROS</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 16/3 , SHORT - 68 - 17/0 , ALT -  - 15/2</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 31/7 , ALT -  - 31/7 , ALT -  - 33/13</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%85)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-8/%5)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>155.9</v>
-      </c>
-      <c r="O26" s="8" t="n">
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>496</v>
+      </c>
+      <c r="O32" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ASELS</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 17/4 , SHORT - 87 - 30/4 , ALT -  - 22/8</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-8/%50)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 12 - 11/1 , ALT -  - 13/2 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-7/%15)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 16/3 , ALT -  - 16/3 , ALT -  - 23/12</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-10/%50)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>271</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
         <v>-2.1</v>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 2 - 10/0 , SHORT - 24 - 9/1 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-6/%60)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>369.25</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DAPGM</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F36" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-18/%15)</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-6/%5)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N28" s="7" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="O28" s="8" t="n">
+      <c r="N36" s="7" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="O36" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MGROS</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AKSA</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 27/4 , ALT -  - 27/4 , ALT -  - 29/10</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>507</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>SARKY</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , SHORT - 87 - 29/5 , ALT -  - 20/6</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-7/%50)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 12 - 10/3 , ALT -  - 11/0 , ALT -  - 12/2</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-6/%20)</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , SHORT - 65 - 12/0 , ALT -  - 19/8</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-7/%50)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>278.25</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-6/%5)</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AKSA</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 ALT -  - 18/7 , ALT -  - 18/7 , ALT -  - 18/7</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F37" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-7/%20)</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N34" s="7" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="O34" s="8" t="n">
+      <c r="N37" s="7" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="O37" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>BSOKE</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="B38" s="3" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 35/0 , ALT -  - 109/55 , ALT -  - 79/62</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
+ALT -  - 40/3 , ALT -  - 117/60 , ALT -  - 85/67</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-46/%0)</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-47/%0)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N35" s="7" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="O35" s="8" t="n">
+      <c r="N38" s="7" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="O38" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>FENER</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="B39" s="3" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 44/6 , ALT -  - 19/7 , ALT -  - 19/7</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
+ALT -  - 47/8 , ALT -  - 21/9 , ALT -  - 21/9</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-10/%30)</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-12/%30)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N36" s="7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O36" s="8" t="n">
+      <c r="N39" s="7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O39" s="8" t="n">
         <v>46281</v>
       </c>
     </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>TABGD</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B40" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
 -</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F40" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%85)</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N37" s="7" t="n">
+      <c r="N40" s="7" t="n">
         <v>227.5</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TRMET</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 17 - 19/12 , SHORT - 17 - 16/1 , ALT -  - 15/4</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-9/%25)</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="O38" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>HEKTS</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>-9</v>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 52/12 , ALT -  - 33/14 , ALT -  - 26/12</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/-13/%55)
-T - TP5/20G - %77 / 128 işlem - ADAY (2g/-13/%70)</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="O39" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BTCIM</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 69/53 , ALT -  - 38/2 , ALT -  - 19/8</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-28/%5)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-14/%0)</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="n">
-        <v>3.32</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>46281</v>
@@ -3095,11 +3095,11 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-3.2</v>
+        <v>-5.5</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3113,44 +3113,44 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 5 - 14/3 , SHORT - 2 - 8/8 , SHORT - 4 - 12/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 17 - 21/11 , ALT -  - 18/0 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-16/%25)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-10/%25)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>627</v>
+        <v>124.9</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46281</v>
@@ -3159,46 +3159,240 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 56/15 , ALT -  - 37/16 , ALT -  - 29/15</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/-15/%55)
+T - TP5/20G - %77 / 128 işlem - ADAY (2g/-15/%70)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 71/54 , ALT -  - 36/1 , ALT -  - 20/9</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-29/%5)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-15/%0)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BRSAN</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 5 - 14/3 , SHORT - 2 - 7/9 , SHORT - 4 - 11/5</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-16/%25)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>635</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>KUYAS</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B45" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 ALT -  - 16/3 , ALT -  - 57/16 , ALT -  - 16/5</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F45" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G45" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H45" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I45" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-14/%91)
 Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-14/%75)
@@ -3208,210 +3402,18 @@
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N42" s="7" t="n">
+      <c r="N45" s="7" t="n">
         <v>62.7</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 7/3 , SHORT - 2 - 7/3 , ALT -  - 12/2</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-8/%40)</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="O43" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>EKGYO</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-11/%82)</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="O44" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>HALKB</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-SHORT - 3 - 7/16 , SHORT - 3 - 6/21 , UST -  - 3/14</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (6g/-10/%73)</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="n">
-        <v>45.48</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46281</v>
@@ -3420,257 +3422,256 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 2 - 7/3 , SHORT - 2 - 7/3 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-9/%40)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EKGYO</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 16/5 , ALT -  - 16/5 , ALT -  - 17/6</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-14/%82)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HALKB</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+SHORT - 3 - 6/17 , SHORT - 3 - 5/22 , UST -  - 4/15</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (6g/-8/%73)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>SASA</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B49" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 SHORT - 2 - 15/15 , SHORT - 2 - 15/9 , SHORT - 1 - 5/5</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F49" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="G46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="6" t="n">
+      <c r="G49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I49" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>X - TP5/20G - %93 / 43 işlem - ONAY (2g/-14/%92)
 X - TP5/10G - %82 / 44 işlem - ADAY (2g/-14/%79)
 Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N46" s="7" t="n">
+      <c r="N49" s="7" t="n">
         <v>2.52</v>
-      </c>
-      <c r="O46" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>KCHOL</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 18 - 8/8 , SHORT - 6 - 9/4 , SHORT - 6 - 8/8</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-6/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%65)</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="n">
-        <v>209.6</v>
-      </c>
-      <c r="O47" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AEFES</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 8 - 9/1 , LONG - 12 - 21/5 , LONG - 10 - 22/4</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-4/%90)</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="O48" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ENKAI</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-LONG - 17 - 32/2 , LONG - 22 - 11/1 , LONG - 21 - 10/1</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-7/%60)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="n">
-        <v>83.8</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46281</v>
@@ -3679,11 +3680,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-3.3</v>
+        <v>-5.8</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3698,35 +3699,35 @@
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 3 - 8/5 , LONG - 27 - 17/8 , SHORT - 3 - 6/4</t>
+SHORT - 18 - 10/6 , SHORT - 6 - 11/1 , SHORT - 6 - 10/6</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-8/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-8/%50)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-9/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-9/%60)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
@@ -3735,7 +3736,7 @@
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>275</v>
+        <v>206.2</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46281</v>
@@ -3744,11 +3745,11 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-4.9</v>
+        <v>-4.5</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3763,36 +3764,35 @@
       <c r="E51" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 13 - 11/2 , ALT -  - 11/0 , ALT -  - 11/0</t>
+SHORT - 3 - 10/3 , SHORT - 3 - 10/3 , SHORT - 3 - 8/2</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
         <v>14</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-8/%45)
-U - TP2/10G - %75 / 97 işlem - ADAY (5g/-9/%40)
-U - TP5/20G - %74 / 74 işlem - ADAY (13g/-9/%60)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-10/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-10/%50)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>107.3</v>
+        <v>271.5</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46281</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-2.7</v>
+        <v>-3.2</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 0/9 , SHORT - 3 - 8/15 , SHORT - 3 - 7/3</t>
+SHORT - 1 - 2/8 , SHORT - 3 - 9/14 , SHORT - 3 - 8/2</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
@@ -3851,8 +3851,8 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (3g/-7/%50)
-U - TP5/20G - %74 / 74 işlem - ADAY (5g/-6/%75)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (3g/-8/%50)
+U - TP5/20G - %74 / 74 işlem - ADAY (5g/-7/%75)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>56.75</v>
+        <v>56.45</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>46281</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -478,7 +478,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-1.5</v>
+        <v>-6</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (18g/-15/%38)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (18g/-19/%38)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>3.29999995</v>
+        <v>3.1500001</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46281</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-5.4</v>
+        <v>-4.4</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 16/3 , ALT -  - 23/12 , -</t>
+ALT -  - 15/2 , ALT -  - 22/10 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -667,11 +667,11 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (7g/-15/%40)
-X - TP2/10G - %98 / 46 işlem - ONAY (1g/-6/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-13/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (7g/-15/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (1g/-6/%88)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (7g/-14/%40)
+X - TP2/10G - %98 / 46 işlem - ONAY (1g/-4/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-12/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-14/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (1g/-4/%88)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>13.43</v>
+        <v>13.56999969</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46281</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>14.96</v>
+        <v>14.96000004</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46281</v>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-9.6</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>246.2</v>
+        <v>245.5</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46281</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>62.95</v>
+        <v>62.95000076</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46281</v>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>1.92</v>
+        <v>1.90999997</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46281</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-7.4</v>
+        <v>-6.9</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 13/3 , ALT -  - 13/3 , ALT -  - 13/3</t>
+ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -997,9 +997,9 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-9/%67)
-H - TP5/10G - %70 / 20 işlem - ADAY (5g/-9/%88)
-H - TP5/20G - %85 / 20 işlem - ADAY (5g/-9/%100)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-8/%67)
+H - TP5/10G - %70 / 20 işlem - ADAY (5g/-8/%88)
+H - TP5/20G - %85 / 20 işlem - ADAY (5g/-8/%100)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>10.4</v>
+        <v>10.44999981</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46281</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>31.22</v>
+        <v>31.21999931</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46281</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>5.94</v>
+        <v>5.94000006</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46281</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-5.3</v>
+        <v>-4.6</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 25/11 , ALT -  - 20/9 , -</t>
+ALT -  - 24/10 , ALT -  - 20/8 , -</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -1193,7 +1193,7 @@
       <c r="K11" s="5" t="inlineStr">
         <is>
           <t>M - TP5/20G - %89 / 55 işlem - ONAY (15g/-21/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-21/%15)
+Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-20/%15)
 Y - TP5/20G - %71 / 98 işlem - ADAY (14g/-21/%5)</t>
         </is>
       </c>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>2.68</v>
+        <v>2.70000005</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46281</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-6.9</v>
+        <v>-5.3</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 26/3 , ALT -  - 30/6 , -</t>
+ALT -  - 24/2 , ALT -  - 28/4 , -</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1258,9 +1258,9 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-22/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-19/%15)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-19/%55)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-21/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-18/%15)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-18/%55)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>51.35</v>
+        <v>52.25</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46281</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 39/3 , ALT -  - 38/2 , ALT -  - 14/3</t>
+ALT -  - 38/2 , ALT -  - 38/2 , ALT -  - 13/3</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>86.55</v>
+        <v>86.84999847</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46281</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>2.59</v>
+        <v>2.58999991</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46281</v>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-4.9</v>
+        <v>-4.6</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 41/11 , ALT -  - 35/15 , ALT -  - 45/7</t>
+ALT -  - 41/11 , ALT -  - 34/15 , ALT -  - 44/7</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-12/%20)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-11/%20)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>34.18</v>
+        <v>34.29999924</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46281</v>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3.6</v>
+        <v>-3.1</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-5/%85)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-5/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-5/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-12/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-4/%95)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-4/%65)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-4/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-11/%0)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>282.5</v>
+        <v>284</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46281</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>67.05</v>
+        <v>67.05000305</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46281</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-4.5</v>
+        <v>-4.4</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       <c r="E18" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 12/1 , LONG - 12 - 24/2 , LONG - 10 - 25/2</t>
+ALT -  - 11/1 , LONG - 12 - 23/3 , LONG - 10 - 24/3</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%65)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%70)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>18.12</v>
+        <v>18.13999939</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46281</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 15/4 , SHORT - 90 - 16/5 , ALT -  - 20/2</t>
+ALT -  - 15/4 , SHORT - 90 - 15/6 , ALT -  - 19/1</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%65)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%65)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>76.3</v>
+        <v>76.5</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46281</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-5.1</v>
+        <v>-4.5</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1759,8 +1759,8 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 38/2 , ALT -  - 15/2 , ALT -  - 14/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 36/1 , ALT -  - 14/1 , ALT -  - 12/2</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-10/%60)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-9/%60)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>81.40000000000001</v>
+        <v>81.94999695</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46281</v>
@@ -1824,7 +1824,7 @@
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 17 - 19/2 , ALT -  - 15/4 , ALT -  - 16/5</t>
+SHORT - 17 - 19/3 , ALT -  - 14/3 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>47.32</v>
+        <v>47.34000015</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46281</v>
@@ -1889,7 +1889,7 @@
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 16/3 , ALT -  - 16/3 , ALT -  - 16/3</t>
+ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>0.97</v>
+        <v>0.97000003</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46281</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-5.8</v>
+        <v>-4.9</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 13 - 12/0 , ALT -  - 12/2 , ALT -  - 12/2</t>
+SHORT - 13 - 11/2 , ALT -  - 11/0 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -1978,9 +1978,9 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-10/%45)
-U - TP2/10G - %75 / 97 işlem - ADAY (5g/-11/%40)
-U - TP5/20G - %74 / 74 işlem - ADAY (13g/-10/%60)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-9/%45)
+U - TP2/10G - %75 / 97 işlem - ADAY (5g/-10/%40)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-9/%60)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>106.3</v>
+        <v>107.30000305</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46281</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-4.8</v>
+        <v>-3.4</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 11/1 , ALT -  - 14/3 , ALT -  - 14/4</t>
+LONG - 7 - 9/1 , ALT -  - 12/1 , ALT -  - 12/2</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2044,9 +2044,9 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-3/%75)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/-3/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-11/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-1/%90)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-1/%70)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-9/%0)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>25.5</v>
+        <v>25.87999916</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>46281</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/1 , ALT -  - 11/1 , ALT -  - 11/1</t>
+ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>20.5</v>
+        <v>20.52000046</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46281</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-7.7</v>
+        <v>-7.4</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 21/7 , ALT -  - 20/8 , ALT -  - 20/6</t>
+ALT -  - 20/7 , ALT -  - 19/8 , ALT -  - 19/6</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>19.34</v>
+        <v>19.39999962</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46281</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-8.5</v>
+        <v>-10</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 27/13 , ALT -  - 37/12 , ALT -  - 38/18</t>
+ALT -  - 29/14 , ALT -  - 39/13 , ALT -  - 40/19</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-17/%45)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-19/%45)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>61.35</v>
+        <v>60.34999847</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>46281</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-1.7</v>
+        <v>0.2</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
 -</t>
         </is>
       </c>
@@ -2302,8 +2302,8 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-12/%80)
-S - TP5/20G - %82 / 22 işlem - ADAY (5g/-12/%90)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-10/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (5g/-10/%90)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>32.96</v>
+        <v>33.61999893</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>46281</v>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.2</v>
+        <v>-3.3</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       <c r="E29" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 19/2 , ALT -  - 35/0 , ALT -  - 18/4</t>
+ALT -  - 18/0 , ALT -  - 18/0 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -2367,8 +2367,8 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-10/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-9/%0)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>153.5</v>
+        <v>155</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>46281</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-5.6</v>
+        <v>-4.5</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       <c r="E30" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/4 , ALT -  - 13/2 , ALT -  - 16/5</t>
+ALT -  - 13/3 , ALT -  - 12/1 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-10/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-9/%60)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>355.75</v>
+        <v>360</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46281</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>6.84</v>
+        <v>6.84000015</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46281</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-3.3</v>
+        <v>-2.9</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       <c r="E32" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 31/7 , ALT -  - 31/7 , ALT -  - 33/13</t>
+ALT -  - 30/6 , ALT -  - 30/6 , ALT -  - 32/12</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-4/%75)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%75)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>46281</v>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-3.7</v>
+        <v>-2.8</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 17/4 , SHORT - 87 - 30/4 , ALT -  - 22/8</t>
+ALT -  - 16/3 , SHORT - 87 - 29/5 , ALT -  - 20/7</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-8/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-7/%50)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>21.54</v>
+        <v>21.73999977</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46281</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       <c r="E34" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 12 - 11/1 , ALT -  - 13/2 , ALT -  - 14/3</t>
+LONG - 12 - 11/2 , ALT -  - 12/1 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>95.55</v>
+        <v>95.75</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46281</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-5</v>
+        <v>-4.3</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
       <c r="E35" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 16/3 , ALT -  - 16/3 , ALT -  - 23/12</t>
+ALT -  - 14/2 , ALT -  - 14/2 , ALT -  - 22/10</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-10/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-9/%50)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46281</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-6/%5)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>5.93</v>
+        <v>5.98000002</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46281</v>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-3.4</v>
+        <v>-2.8</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
       <c r="E37" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 18/7 , ALT -  - 18/7 , ALT -  - 18/7</t>
+ALT -  - 17/6 , ALT -  - 17/6 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>10.55</v>
+        <v>10.60999966</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46281</v>
@@ -2922,7 +2922,7 @@
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 40/3 , ALT -  - 117/60 , ALT -  - 85/67</t>
+ALT -  - 39/3 , ALT -  - 116/59 , ALT -  - 84/67</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>17.65</v>
+        <v>17.65999985</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46281</v>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>2.58</v>
+        <v>2.57999992</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46281</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-1/%85)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-2/%75)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>227.5</v>
+        <v>226.8999939</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>46281</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 17 - 21/11 , ALT -  - 18/0 , ALT -  - 17/6</t>
+SHORT - 17 - 20/11 , SHORT - 17 - 17/0 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-10/%25)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-9/%25)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>124.9</v>
+        <v>125.09999847</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46281</v>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-9.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 56/15 , ALT -  - 37/16 , ALT -  - 29/15</t>
+ALT -  - 57/16 , ALT -  - 37/17 , ALT -  - 30/15</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>2.42</v>
+        <v>2.41000009</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46281</v>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-5.7</v>
+        <v>-4</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 71/54 , ALT -  - 36/1 , ALT -  - 20/9</t>
+ALT -  - 67/51 , ALT -  - 37/1 , ALT -  - 18/7</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -3265,8 +3265,8 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-29/%5)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-15/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-13/%0)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>3.3</v>
+        <v>3.3599999</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46281</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3307,8 +3307,8 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 5 - 14/3 , SHORT - 2 - 7/9 , SHORT - 4 - 11/5</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+SHORT - 5 - 13/4 , SHORT - 2 - 6/9 , SHORT - 4 - 11/6</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-16/%25)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-15/%25)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>635</v>
+        <v>637.5</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46281</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>62.7</v>
+        <v>62.70000076</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46281</v>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 7/3 , SHORT - 2 - 7/3 , ALT -  - 13/2</t>
+SHORT - 2 - 7/3 , SHORT - 2 - 7/3 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-9/%40)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-8/%40)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>98.65000000000001</v>
+        <v>99.05000305</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46281</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-9.1</v>
+        <v>-8.1</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       <c r="E47" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 16/5 , ALT -  - 16/5 , ALT -  - 17/6</t>
+ALT -  - 14/4 , ALT -  - 14/4 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-14/%82)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-13/%82)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>18</v>
+        <v>18.20000076</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46281</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="E48" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-SHORT - 3 - 6/17 , SHORT - 3 - 5/22 , UST -  - 4/15</t>
+SHORT - 3 - 4/18 , SHORT - 3 - 4/23 , UST -  - 5/16</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>47.3</v>
+        <v>46.77999878</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46281</v>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>2.52</v>
+        <v>2.51999998</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46281</v>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-5.8</v>
+        <v>-5.6</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 18 - 10/6 , SHORT - 6 - 11/1 , SHORT - 6 - 10/6</t>
+SHORT - 18 - 10/6 , SHORT - 6 - 11/2 , SHORT - 6 - 10/7</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3721,8 +3721,8 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-9/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-9/%60)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-8/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-8/%60)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>206.2</v>
+        <v>206.5</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46281</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-4.5</v>
+        <v>-4.2</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       <c r="E51" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 3 - 10/3 , SHORT - 3 - 10/3 , SHORT - 3 - 8/2</t>
+SHORT - 3 - 9/3 , SHORT - 3 - 9/3 , SHORT - 3 - 8/3</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
@@ -3786,8 +3786,8 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-10/%55)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-10/%50)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-9/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-9/%50)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>271.5</v>
+        <v>272.25</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46281</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 2/8 , SHORT - 3 - 9/14 , SHORT - 3 - 8/2</t>
+SHORT - 1 - 1/8 , SHORT - 3 - 9/14 , SHORT - 3 - 8/2</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>56.45</v>
+        <v>56.25</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>46281</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$45</definedName>
   </definedNames>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -478,7 +478,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -562,11 +562,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-6</v>
+        <v>0.5</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -580,57 +580,61 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 23 - 20/2 , ALT -  - 21/3 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>I-TP2/10G, Z-TP2/10G, I-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (18g/-19/%38)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
+Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-8/%75)
+I - TP5/20G - %82 / 67 işlem - ADAY (0g/0/%100)
+U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)
+Z - TP5/20G - %75 / 71 işlem - ADAY (14g/-7/%29)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, Z: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>3.1500001</v>
+        <v>1.92</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-4.4</v>
+        <v>-10</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -644,61 +648,62 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , ALT -  - 22/10 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 28/13 , ALT -  - 74/28 , ALT -  - 27/15</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (7g/-14/%40)
-X - TP2/10G - %98 / 46 işlem - ONAY (1g/-4/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-12/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (7g/-14/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (1g/-4/%88)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (4g/-22/%91)
+Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-22/%55)
+U - TP5/20G - %74 / 74 işlem - ADAY (6g/-22/%70)
+V - TP2/10G - %95 / 21 işlem - ADAY (6g/-22/%75)
+V - TP5/10G - %75 / 20 işlem - ADAY (7g/-21/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-22/%50)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>13.56999969</v>
+        <v>56.45</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-10</v>
+        <v>2.9</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -712,35 +717,39 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL +2, CNDL 0, XU030 +1, TOPLAM 4, İZLE
-ALT -  - 27/4 , ALT -  - 22/8 , -</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 1 - 10/2 , ALT -  - 17/6 , -</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-22/%40)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (8g/-11/%30)
+X - TP2/10G - %98 / 46 işlem - ONAY (2g/-2/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-9/%45)
+I - TP5/20G - %82 / 67 işlem - ADAY (8g/-11/%74)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/-2/%85)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -749,20 +758,20 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>14.96000004</v>
+        <v>13.96</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-9.800000000000001</v>
+        <v>-6</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -776,38 +785,34 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 36/20 , ALT -  - 36/20 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (7g/-18/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (8g/-17/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-18/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (7g/-18/%40)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (19g/?/%?)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -816,7 +821,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>245.5</v>
+        <v>3.1500001</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46281</v>
@@ -825,11 +830,11 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-9.9</v>
+        <v>-1.3</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -843,58 +848,57 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 31/16 , ALT -  - 44/13 , -</t>
+          <t>BIS -2, PHL +2, CNDL +1, XU030 -1, TOPLAM 0, ALMA
+ALT -  - 29/5 , ALT -  - 23/9 , -</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-14/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (3g/-14/%85)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-23/%25)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>62.95000076</v>
+        <v>14.76</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-4.5</v>
+        <v>3.9</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -908,59 +912,60 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 22 - 21/1 , ALT -  - 22/4 , ALT -  - 11/0</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 30/15 , ALT -  - 30/15 , -</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (13g/-7/%60)
-Z - TP5/20G - %75 / 71 işlem - ADAY (13g/-7/%45)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (8g/-15/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-14/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-15/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (8g/-15/%45)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>1.90999997</v>
+        <v>255</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-6.9</v>
+        <v>-1.9</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -974,12 +979,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
+          <t>BIS +2, PHL +2, CNDL +1, XU030 -1, TOPLAM 4, İZLE
+ALT -  - 20/2 , ALT -  - 19/8 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -992,19 +997,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-8/%67)
-H - TP5/10G - %70 / 20 işlem - ADAY (5g/-8/%88)
-H - TP5/20G - %85 / 20 işlem - ADAY (5g/-8/%100)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-22/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-22/%15)
+Y - TP5/20G - %71 / 98 işlem - ADAY (15g/-22/%5)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1013,20 +1018,20 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>10.44999981</v>
+        <v>2.65</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-10</v>
+        <v>-6.8</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1040,53 +1045,54 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 36/20 , ALT -  - 49/17 , -</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-18/%82)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-20/%88)
+L - TP5/10G - %77 / 43 işlem - ADAY (4g/-20/%70)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>31.21999931</v>
+        <v>58.7</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1104,8 +1110,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 25/7 , ALT -  - 25/7 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+-</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1115,47 +1121,46 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (10g/-17/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-29/%10)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-26/%73)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>5.94000006</v>
+        <v>28.1</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-4.6</v>
+        <v>-5.1</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1169,8 +1174,8 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 24/10 , ALT -  - 20/8 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 28/9 , ALT -  - 28/9 , -</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -1180,48 +1185,47 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (15g/-21/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-20/%15)
-Y - TP5/20G - %71 / 98 işlem - ADAY (14g/-21/%5)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (11g/-21/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-33/%10)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>2.70000005</v>
+        <v>5.64</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-5.3</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1235,37 +1239,39 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 24/2 , ALT -  - 28/4 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
         <v>55</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-21/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-18/%15)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-18/%55)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-25/%35)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-25/%45)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-25/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-25/%25)
+R - TP5/20G - %80 / 102 işlem - ADAY (18g/-33/%15)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1274,20 +1280,20 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>52.25</v>
+        <v>2.34</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-4.8</v>
+        <v>-5.2</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
@@ -1301,8 +1307,8 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 38/2 , ALT -  - 38/2 , ALT -  - 13/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+SHORT - 3 - 21/10 , SHORT - 3 - 21/5 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1312,25 +1318,26 @@
         <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-9/%60)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (3g/-19/%78)
+X - TP5/10G - %82 / 44 işlem - ADAY (3g/-19/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-19/%50)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1339,20 +1346,20 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>86.84999847</v>
+        <v>2.39</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-9.800000000000001</v>
+        <v>-1.6</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1366,39 +1373,37 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+ALT -  - 22/0 , ALT -  - 26/3 , -</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
         <v>52</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-17/%40)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-17/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-17/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-17/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (17g/-26/%15)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (14g/-22/%60)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-19/%0)
+R - TP5/20G - %80 / 102 işlem - ADAY (7g/-19/%40)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1407,20 +1412,20 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>2.58999991</v>
+        <v>51.4</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-4.6</v>
+        <v>2.4</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1434,35 +1439,36 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 41/11 , ALT -  - 34/15 , ALT -  - 44/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 34/1 , LONG - 1 - 33/2 , LONG - 1 - 10/0</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-11/%20)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-7/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-6/%65)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1471,20 +1477,20 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>34.29999924</v>
+        <v>88.95</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3.1</v>
+        <v>4</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1498,60 +1504,60 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 9/2 , LONG - 1 - 7/3 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>Y-TP2/10G, E-TP5/20G, Y-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-4/%95)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/-4/%65)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-4/%85)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-11/%0)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
+E - TP5/20G - %69 / 179 işlem - ADAY (4g/-5/%60)
+Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)
+Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Y: seçili strateji teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>284</v>
+        <v>374.25</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-9.9</v>
+        <v>3.4</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1565,37 +1571,35 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 43/17 , ALT -  - 38/22 , ALT -  - 36/21</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 1 - 7/3 , LONG - 13 - 19/7 , LONG - 11 - 19/6</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-17/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (7g/-16/%75)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-16/%0)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-3/%75)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1604,20 +1608,20 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>67.05000305</v>
+        <v>18.76</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-4.4</v>
+        <v>1.7</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1631,8 +1635,8 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/1 , LONG - 12 - 23/3 , LONG - 10 - 24/3</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+ALT -  - 12/2 , SHORT - 91 - 13/8 , LONG - 1 - 17/1</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1654,7 +1658,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%70)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-5/%75)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1668,20 +1672,20 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>18.13999939</v>
+        <v>77.8</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-1.9</v>
+        <v>1</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1695,8 +1699,8 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 15/4 , SHORT - 90 - 15/6 , ALT -  - 19/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 8 - 8/3 , LONG - 1 - 10/0 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1706,24 +1710,26 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%65)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (8g/0/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (8g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-8/%5)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1732,20 +1738,20 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>76.5</v>
+        <v>26.14</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-4.5</v>
+        <v>-0.8</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1759,57 +1765,59 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 36/1 , ALT -  - 14/1 , ALT -  - 12/2</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 42/16 , ALT -  - 37/21 , ALT -  - 35/20</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-9/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-17/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (8g/-16/%74)
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-16/%0)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>81.94999695</v>
+        <v>66.5</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-6.2</v>
+        <v>2.4</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -1823,48 +1831,47 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 17 - 19/3 , ALT -  - 14/3 , ALT -  - 16/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 32/2 , LONG - 1 - 10/3 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-12/%55)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-12/%50)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%60)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>47.34000015</v>
+        <v>83.95</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
@@ -1874,7 +1881,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1888,12 +1895,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+ALT -  - 14/1 , ALT -  - 14/1 , ALT -  - 14/1</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -1911,10 +1918,10 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (5g/-6/%40)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-6/%60)
-R - TP2/10G - %84 / 119 işlem - ADAY (5g/-6/%40)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-6/%40)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (6g/-6/%45)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-6/%50)
+R - TP2/10G - %84 / 119 işlem - ADAY (6g/-6/%35)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%30)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1924,24 +1931,24 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>0.97000003</v>
+        <v>0.97</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-4.9</v>
+        <v>3.1</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1955,37 +1962,35 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 13 - 11/2 , ALT -  - 11/0 , ALT -  - 11/0</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 24/10 , ALT -  - 33/9 , ALT -  - 35/15</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-9/%45)
-U - TP2/10G - %75 / 97 işlem - ADAY (5g/-10/%40)
-U - TP5/20G - %74 / 74 işlem - ADAY (13g/-9/%60)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (7g/-16/%35)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -1994,20 +1999,20 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>107.30000305</v>
+        <v>62.25</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-3.4</v>
+        <v>-1.2</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2021,37 +2026,36 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 7 - 9/1 , ALT -  - 12/1 , ALT -  - 12/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 58/17 , ALT -  - 38/18 , SHORT - 88 - 32/2</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-1/%90)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/-1/%70)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-9/%0)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/-16/%35)
+T - TP5/20G - %77 / 128 işlem - ADAY (3g/-16/%45)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2060,20 +2064,20 @@
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>25.87999916</v>
+        <v>2.38</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-3.8</v>
+        <v>-1.1</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
@@ -2087,35 +2091,36 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 11/0</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
+-</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-8/%56)</t>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (6g/-11/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (6g/-11/%90)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2124,20 +2129,20 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>20.52000046</v>
+        <v>33.26</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-7.4</v>
+        <v>1.5</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2151,12 +2156,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 20/7 , ALT -  - 19/8 , ALT -  - 19/6</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 9/1 , LONG - 1 - 9/1 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -2174,7 +2179,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-16/%27)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-7/%27)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2184,24 +2189,24 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>19.39999962</v>
+        <v>20.82</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10</v>
+        <v>-9.9</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2215,12 +2220,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 29/14 , ALT -  - 39/13 , ALT -  - 40/19</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>0</v>
@@ -2233,17 +2238,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-19/%45)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2252,20 +2257,20 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>60.34999847</v>
+        <v>6.16</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -2279,8 +2284,8 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 1 - 16/1 , LONG - 1 - 16/1 , ALT -  - 14/2</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
@@ -2290,25 +2295,24 @@
         <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-10/%80)
-S - TP5/20G - %82 / 22 işlem - ADAY (5g/-10/%90)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-2/%95)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
@@ -2317,20 +2321,20 @@
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>33.61999893</v>
+        <v>157</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.3</v>
+        <v>3.1</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2344,8 +2348,8 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 18/0 , ALT -  - 18/0 , ALT -  - 16/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 13 - 7/5 , LONG - 1 - 8/2 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -2355,47 +2359,46 @@
         <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-9/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-4/%35)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>155</v>
+        <v>98.75</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-4.5</v>
+        <v>-3.7</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -2409,12 +2412,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 13/3 , ALT -  - 12/1 , ALT -  - 14/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 39/3 , ALT -  - 122/64 , ALT -  - 89/71</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0</v>
@@ -2427,17 +2430,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-9/%60)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-49/%0)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -2446,20 +2449,20 @@
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>360</v>
+        <v>17.01</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-10</v>
+        <v>0.8</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2473,12 +2476,11 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>0</v>
@@ -2491,17 +2493,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-19/%15)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/?/%?)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -2510,7 +2512,7 @@
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>6.84000015</v>
+        <v>226.8999939</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46281</v>
@@ -2523,7 +2525,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2.9</v>
+        <v>2.5</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2537,12 +2539,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 30/6 , ALT -  - 30/6 , ALT -  - 32/12</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 26/3 , ALT -  - 26/3 , ALT -  - 27/9</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -2560,7 +2562,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%75)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/0/%95)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2570,14 +2572,14 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>498</v>
+        <v>510.5</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
@@ -2587,7 +2589,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-2.8</v>
+        <v>1.5</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -2601,12 +2603,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 16/3 , SHORT - 87 - 29/5 , ALT -  - 20/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 12/1 , SHORT - 88 - 26/7 , ALT -  - 17/4</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>0</v>
@@ -2624,7 +2626,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-7/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-6/%60)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2634,24 +2636,24 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>21.73999977</v>
+        <v>22.06</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-3.7</v>
+        <v>2</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2665,12 +2667,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 12 - 11/2 , ALT -  - 12/1 , ALT -  - 14/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 15/4 , ALT -  - 15/4 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>0</v>
@@ -2683,39 +2685,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-7/%15)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-4/%40)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>95.75</v>
+        <v>10.82</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-4.3</v>
+        <v>1.9</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2729,12 +2731,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 14/2 , ALT -  - 14/2 , ALT -  - 22/10</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 44/6 , ALT -  - 17/6 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>0</v>
@@ -2747,39 +2749,39 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-9/%50)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-10/%25)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>273</v>
+        <v>2.63</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-1.3</v>
+        <v>2.6</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2793,12 +2795,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+SHORT - 18 - 17/14 , SHORT - 18 - 13/4 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
@@ -2811,39 +2813,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (8g/-7/%25)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>5.98000002</v>
+        <v>128.4</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-2.8</v>
+        <v>0.5</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -2857,57 +2859,57 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 17/6 , ALT -  - 17/6 , ALT -  - 17/6</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+SHORT - 6 - 12/5 , SHORT - 3 - 6/10 , SHORT - 5 - 10/6</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (18g/-15/%25)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>10.60999966</v>
+        <v>640.5</v>
       </c>
       <c r="O37" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-7.1</v>
+        <v>2.6</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2921,57 +2923,57 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 39/3 , ALT -  - 116/59 , ALT -  - 84/67</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+SHORT - 3 - 4/6 , SHORT - 3 - 4/6 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-47/%0)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-6/%25)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>17.65999985</v>
+        <v>101.6</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-5.1</v>
+        <v>3.8</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2985,53 +2987,55 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 47/8 , ALT -  - 21/9 , ALT -  - 21/9</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
+LONG - 1 - 8/2 , LONG - 1 - 8/2 , LONG - 1 - 8/2</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-12/%30)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (6g/-5/%67)
+H - TP5/10G - %70 / 20 işlem - ADAY (6g/-5/%88)
+H - TP5/20G - %85 / 20 işlem - ADAY (6g/-5/%100)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>2.57999992</v>
+        <v>10.85</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
@@ -3049,57 +3053,60 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+SHORT - 14 - 10/3 , LONG - 1 - 10/1 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-2/%75)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-8/%40)
+U - TP2/10G - %75 / 97 işlem - ADAY (6g/-9/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (14g/-8/%56)
+Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>226.8999939</v>
+        <v>108.2</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-5.3</v>
+        <v>3.6</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3113,57 +3120,58 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 17 - 20/11 , SHORT - 17 - 17/0 , ALT -  - 16/5</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+SHORT - 19 - 6/10 , SHORT - 7 - 7/5 , SHORT - 7 - 6/10</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-9/%25)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (7g/-5/%80)
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-5/%70)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>125.09999847</v>
+        <v>213.9</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-9.699999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3177,58 +3185,60 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 57/16 , ALT -  - 37/17 , ALT -  - 30/15</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/-15/%55)
-T - TP5/20G - %77 / 128 işlem - ADAY (2g/-15/%70)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-4/%80)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-4/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-4/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-11/%0)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>2.41000009</v>
+        <v>285</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3242,58 +3252,58 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 67/51 , ALT -  - 37/1 , ALT -  - 18/7</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+SHORT - 4 - 5/7 , LONG - 28 - 14/11 , SHORT - 4 - 3/7</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-13/%0)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-6/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-6/%40)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>3.3599999</v>
+        <v>283.25</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-1.5</v>
+        <v>3.9</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3307,35 +3317,36 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-SHORT - 5 - 13/4 , SHORT - 2 - 6/9 , SHORT - 4 - 11/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 1 - 9/1 , LONG - 1 - 9/2 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-15/%25)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-8/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-8/%35)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -3344,20 +3355,20 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>637.5</v>
+        <v>49.18</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-10</v>
+        <v>1.3</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3371,62 +3382,58 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 16/3 , ALT -  - 57/16 , ALT -  - 16/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+UST -  - 0/10 , SHORT - 4 - 8/16 , SHORT - 4 - 6/4</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="I45" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-14/%91)
-Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-14/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (5g/-14/%75)
-V - TP2/10G - %95 / 21 işlem - ADAY (5g/-14/%80)
-V - TP5/10G - %75 / 20 işlem - ADAY (6g/-12/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (4g/-7/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (6g/-6/%80)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>62.70000076</v>
+        <v>57</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-4.4</v>
+        <v>1.6</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3440,35 +3447,35 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 7/3 , SHORT - 2 - 7/3 , ALT -  - 12/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 17/4 , ALT -  - 16/5 , ALT -  - 17/4</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-8/%40)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (16g/-15/%35)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -3477,20 +3484,20 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>99.05000305</v>
+        <v>19.71</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-8.1</v>
+        <v>-1.8</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3504,35 +3511,36 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 14/4 , ALT -  - 14/4 , ALT -  - 15/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 68/52 , ALT -  - 37/1 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>E-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-13/%82)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-29/%0)
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-15/%0)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -3541,20 +3549,20 @@
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>18.20000076</v>
+        <v>3.3</v>
       </c>
       <c r="O47" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3568,12 +3576,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-SHORT - 3 - 4/18 , SHORT - 3 - 4/23 , UST -  - 5/16</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 10/1 , LONG - 1 - 10/1 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>1</v>
@@ -3586,39 +3594,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (6g/-8/%73)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-9/%69)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>46.77999878</v>
+        <v>18.94</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-10</v>
+        <v>3.6</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3632,37 +3640,35 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 2 - 15/15 , SHORT - 2 - 15/9 , SHORT - 1 - 5/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 10/3 , LONG - 1 - 10/3 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (2g/-14/%92)
-X - TP5/10G - %82 / 44 işlem - ADAY (2g/-14/%79)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-6/%70)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -3671,20 +3677,20 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>2.51999998</v>
+        <v>282.75</v>
       </c>
       <c r="O49" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-5.6</v>
+        <v>5.4</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3698,58 +3704,57 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 18 - 10/6 , SHORT - 6 - 11/2 , SHORT - 6 - 10/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+UST -  - 1/22 , UST -  - 1/27 , UST -  - 9/20</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-8/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-8/%60)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-3/%71)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>206.5</v>
+        <v>49.32</v>
       </c>
       <c r="O50" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-4.2</v>
+        <v>6</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3763,117 +3768,51 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 3 - 9/3 , SHORT - 3 - 9/3 , SHORT - 3 - 8/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 32/4 , ALT -  - 27/8 , ALT -  - 36/0</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-9/%55)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-9/%50)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (17g/-6/%35)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>272.25</v>
+        <v>36.36</v>
       </c>
       <c r="O51" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>SOKM</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 1/8 , SHORT - 3 - 9/14 , SHORT - 3 - 8/2</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (3g/-8/%50)
-U - TP5/20G - %74 / 74 işlem - ADAY (5g/-7/%75)</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N52" s="7" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="O52" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O52"/>
+  <autoFilter ref="A1:O51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3984,11 +3923,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1</v>
+        <v>-6</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -4002,61 +3941,57 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 12/0 , ALT -  - 17/6 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (6g/-10/%40)
-X - TP2/10G - %98 / 46 işlem - ONAY (0g/0/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-10/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (18g/-19/%38)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>14.19999981</v>
+        <v>3.1500001</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-3.7</v>
+        <v>-4.4</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -4069,913 +4004,915 @@
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , ALT -  - 22/10 , -</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (7g/-14/%40)
+X - TP2/10G - %98 / 46 işlem - ONAY (1g/-4/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-12/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-14/%75)
+L - TP5/10G - %77 / 43 işlem - ADAY (1g/-4/%88)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>13.56999969</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL +2, CNDL 0, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 27/4 , ALT -  - 22/8 , -</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-22/%40)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>14.96000004</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 36/20 , ALT -  - 36/20 , -</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (7g/-18/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (8g/-17/%33)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-18/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (7g/-18/%40)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EUPWR</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 31/16 , ALT -  - 44/13 , -</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-14/%91)
+L - TP5/10G - %77 / 43 işlem - ADAY (3g/-14/%85)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>62.95000076</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TUKAS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 22 - 21/1 , ALT -  - 22/4 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-7/%60)
+Z - TP5/20G - %75 / 71 işlem - ADAY (13g/-7/%45)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>1.90999997</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (5g/-8/%67)
+H - TP5/10G - %70 / 20 işlem - ADAY (5g/-8/%88)
+H - TP5/20G - %85 / 20 işlem - ADAY (5g/-8/%100)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>10.44999981</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MIATK</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (4g/-18/%82)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>31.21999931</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+ALT -  - 25/7 , ALT -  - 25/7 , -</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (10g/-17/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (15g/-29/%10)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>5.94000006</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 24/10 , ALT -  - 20/8 , -</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (15g/-21/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (13g/-20/%15)
+Y - TP5/20G - %71 / 98 işlem - ADAY (14g/-21/%5)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>2.70000005</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 24/2 , ALT -  - 28/4 , -</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (13g/-21/%78)
+R - TP5/10G - %60 / 138 işlem - ADAY (6g/-18/%15)
+R - TP5/20G - %80 / 102 işlem - ADAY (6g/-18/%55)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 38/2 , ALT -  - 38/2 , ALT -  - 13/3</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (5g/-9/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-9/%60)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>86.84999847</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PSGYO</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-17/%40)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-17/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-17/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-17/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (17g/-26/%15)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>2.58999991</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 41/11 , ALT -  - 34/15 , ALT -  - 44/7</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (16g/-11/%20)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>34.29999924</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GRSEL</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>M-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (17g/-14/%50)</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="F16" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-4/%95)
+I - TP5/10G - %61 / 109 işlem - ADAY (6g/-4/%65)
+I - TP5/20G - %82 / 67 işlem - ADAY (6g/-4/%85)
+Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-11/%0)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N3" s="7" t="n">
-        <v>3.3499999</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 12 - 11/2 , SHORT - 12 - 10/2 , -</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-13/%50)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>16.62000084</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ASTOR</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 23/9 , ALT -  - 23/9 , -</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-10/%86)
-L - TP5/10G - %77 / 43 işlem - ADAY (7g/-8/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
-R - TP5/20G - %80 / 102 işlem - ADAY (6g/-10/%60)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>272.25</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MIATK</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (3g/-9/%90)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>34.68000031</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 20/6 , ALT -  - 16/5 , -</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (14g/-17/%60)
-Q - TP5/20G - %70 / 203 işlem - ADAY (12g/-17/%10)
-Y - TP5/20G - %71 / 98 işlem - ADAY (13g/-17/%5)</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>2.82999992</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EUPWR</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 21/8 , ALT -  - 33/9 , -</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-5/%91)
-L - TP5/10G - %77 / 43 işlem - ADAY (2g/-5/%83)</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>69.90000153</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IZENR</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 7 - 15/2 , LONG - 7 - 15/2 , -</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (9g/-7/%75)
-L - TP5/10G - %77 / 43 işlem - ADAY (9g/-7/%33)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-21/%15)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 83 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>6.5999999</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 34 - 5/5 , LONG - 32 - 5/5 , LONG - 32 - 5/5</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-1/%69)
-H - TP5/10G - %70 / 20 işlem - ADAY (4g/-1/%100)
-H - TP5/20G - %85 / 20 işlem - ADAY (4g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>11.22999954</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 72 - 21/1 , ALT -  - 24/1 , -</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (12g/-16/%78)
-R - TP5/10G - %60 / 138 işlem - ADAY (5g/-13/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (5g/-13/%60)</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>55.15000153</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 38/2</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (15g/-7/%35)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>35.93999863</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
-LONG - 6 - 6/4 , LONG - 6 - 6/4 , LONG - 3 - 9/1</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/+3/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (6g/+3/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)
-R - TP5/20G - %80 / 102 işlem - ADAY (19g/-6/%16)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 80 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>26.78000069</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 13/2 , SHORT - 89 - 13/7 , LONG - 9 - 17/0</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)
-I - TP5/20G - %82 / 67 işlem - ADAY (19g/-5/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-5/%15)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-5/%70)</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 82 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-8/%55)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-8/%60)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-8/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-8/%35)
-R - TP5/20G - %80 / 102 işlem - ADAY (16g/-18/%20)</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>2.86999989</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 28/5 , LONG - 8 - 32/3 , LONG - 8 - 9/2</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N16" s="7" t="n">
-        <v>91.19999695</v>
+        <v>284</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.7</v>
+        <v>-9.9</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -4988,967 +4925,966 @@
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 43/17 , ALT -  - 38/22 , ALT -  - 36/21</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-17/%50)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-16/%75)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-16/%0)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>67.05000305</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/1 , LONG - 12 - 23/3 , LONG - 10 - 24/3</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%70)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>18.13999939</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 15/4 , SHORT - 90 - 15/6 , ALT -  - 19/1</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-6/%65)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ENKAI</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 36/1 , ALT -  - 14/1 , ALT -  - 12/2</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-9/%60)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>81.94999695</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TRALT</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 17 - 19/3 , ALT -  - 14/3 , ALT -  - 16/5</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-12/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-12/%50)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>47.34000015</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GSRAY</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (5g/-6/%40)
+Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-6/%60)
+R - TP2/10G - %84 / 119 işlem - ADAY (5g/-6/%40)
+R - TP5/10G - %60 / 138 işlem - ADAY (5g/-6/%40)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>0.97000003</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ENJSA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 13 - 11/2 , ALT -  - 11/0 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-9/%45)
+U - TP2/10G - %75 / 97 işlem - ADAY (5g/-10/%40)
+U - TP5/20G - %74 / 74 işlem - ADAY (13g/-9/%60)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>107.30000305</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 7 - 9/1 , ALT -  - 12/1 , ALT -  - 12/2</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-1/%90)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-1/%70)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-9/%0)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>25.87999916</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-8/%56)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>20.52000046</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 20/7 , ALT -  - 19/8 , ALT -  - 19/6</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-16/%27)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>19.39999962</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 29/14 , ALT -  - 39/13 , ALT -  - 40/19</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (6g/-19/%45)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>60.34999847</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+-</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>S-TP5/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (5g/-10/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (5g/-10/%90)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>33.61999893</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 18/0 , ALT -  - 18/0 , ALT -  - 16/3</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-9/%0)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ASELS</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 13/3 , ALT -  - 12/1 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-9/%60)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DAPGM</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-1/%95)
-I - TP5/10G - %61 / 109 işlem - ADAY (5g/-1/%90)
-I - TP5/20G - %82 / 67 işlem - ADAY (5g/-1/%90)
-Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-9/%20)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="F31" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-19/%15)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N17" s="7" t="n">
-        <v>293</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 30/6 , ALT -  - 25/11 , ALT -  - 24/10</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-7/%55)
-I - TP5/20G - %82 / 67 işlem - ADAY (6g/-6/%85)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%25)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>74.44999695</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 67 - 14/3 , SHORT - 144 - 30/4 , LONG - 8 - 13/0</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-6/%25)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 78 hisse / 97 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>160.30000305</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DAPGM</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (14g/-10/%10)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>7.5999999</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SARKY</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , SHORT - 86 - 27/6 , ALT -  - 18/5</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-5/%75)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>22.36000061</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 11 - 7/5 , LONG - 7 - 8/2 , LONG - 6 - 10/1</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-3/%65)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>99.40000153</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 62 - 11/1 , SHORT - 64 - 11/2 , ALT -  - 17/6</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-5/%65)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>285.25</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (18g/-4/%25)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>6.05999994</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 34/1 , ALT -  - 102/50 , ALT -  - 74/57</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-43/%10)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TABGD</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (3g/-3/%85)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>225</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ECILC</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 17/4 , ALT -  - 25/3 , ALT -  - 27/8</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (5g/-10/%50)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>67.05000305</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (4g/-10/%78)
-S - TP5/20G - %82 / 22 işlem - ADAY (4g/-10/%89)</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>33.54000092</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>BTCIM</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 40/3 , LONG - 8 - 34/1 , ALT -  - 16/5</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (15g/-24/%15)
-R - TP5/10G - %60 / 138 işlem - ADAY (6g/-10/%15)</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 40/3 , ALT -  - 16/5 , ALT -  - 16/5</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-7/%50)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>2.72000003</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
-LONG - 13 - 20/11 , LONG - 13 - 20/11 , SHORT - 2 - 5/5</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-4/%100)
-Y - TP2/10G - %86 / 78 işlem - ONAY (1g/-4/%75)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-4/%70)
-V - TP2/10G - %95 / 21 işlem - ADAY (4g/-4/%88)
-V - TP5/10G - %75 / 20 işlem - ADAY (5g/-2/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N31" s="7" t="n">
-        <v>69.65000153</v>
+        <v>6.84000015</v>
       </c>
       <c r="O31" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-5.1</v>
+        <v>-2.9</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -5962,57 +5898,57 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 11/5 , SHORT - 1 - 5/11 , SHORT - 3 - 9/7</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 30/6 , ALT -  - 30/6 , ALT -  - 32/12</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (16g/-14/%40)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (1g/-3/%75)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>647.5</v>
+        <v>498</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -6026,57 +5962,57 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 1 - 2/8 , SHORT - 1 - 2/8 , SHORT - 12 - 8/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 16/3 , SHORT - 87 - 29/5 , ALT -  - 20/7</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (17g/-4/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-7/%50)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>103.59999847</v>
+        <v>21.73999977</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -6091,56 +6027,56 @@
       <c r="E34" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 2 - 5/5 , SHORT - 2 - 5/5 , SHORT - 4 - 6/4</t>
+LONG - 12 - 11/2 , ALT -  - 12/1 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (2g/-5/%85)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-7/%15)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>19.79999924</v>
+        <v>95.75</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-2.1</v>
+        <v>-4.3</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -6154,57 +6090,57 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 2 - 6/17 , SHORT - 2 - 5/22 , UST -  - 4/15</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 14/2 , ALT -  - 14/2 , ALT -  - 22/10</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-9/%73)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (4g/-9/%50)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>46.08000183</v>
+        <v>273</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-2</v>
+        <v>-1.3</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -6218,59 +6154,57 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 21 - 16/5 , LONG - 7 - 17/0 , LONG - 33 - 7/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (4g/-4/%78)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-3/%80)
-Z - TP5/20G - %75 / 71 işlem - ADAY (12g/-3/%50)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (19g/-5/%5)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>2</v>
+        <v>5.98000002</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-4.8</v>
+        <v>-2.8</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -6284,59 +6218,57 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 11/18 , LONG - 8 - 10/18 , UST -  - 5/14</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 17/6 , ALT -  - 17/6 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (1g/-5/%93)
-X - TP5/10G - %82 / 44 işlem - ADAY (1g/-5/%81)
-Y - TP5/10G - %61 / 71 işlem - ADAY (1g/-5/%70)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-6/%20)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>2.79999995</v>
+        <v>10.60999966</v>
       </c>
       <c r="O37" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-3</v>
+        <v>-7.1</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -6350,58 +6282,57 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-SHORT - 17 - 4/12 , LONG - 82 - 8/11 , SHORT - 5 - 3/12</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 39/3 , ALT -  - 116/59 , ALT -  - 84/67</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (5g/-3/%85)
-Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-3/%80)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (17g/-47/%0)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>218.80000305</v>
+        <v>17.65999985</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-3.9</v>
+        <v>-5.1</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -6415,12 +6346,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 18 - 29/5 , LONG - 21 - 10/2 , LONG - 20 - 8/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 47/8 , ALT -  - 21/9 , ALT -  - 21/9</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>0</v>
@@ -6433,39 +6364,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (4g/-5/%70)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-12/%30)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>85.80000305</v>
+        <v>2.57999992</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-4.6</v>
+        <v>0.8</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -6479,12 +6410,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-LONG - 32 - 10/3 , LONG - 40 - 11/2 , LONG - 77 - 15/6</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+-</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -6497,39 +6428,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (19g/-3/%13)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-2/%75)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>127.80000305</v>
+        <v>226.8999939</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>-5.3</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -6543,58 +6474,57 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-SHORT - 2 - 5/7 , LONG - 26 - 14/10 , SHORT - 2 - 3/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 17 - 20/11 , SHORT - 17 - 17/0 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-5/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-5/%65)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-9/%25)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>284.25</v>
+        <v>125.09999847</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -6608,60 +6538,58 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 11/0 , SHORT - 13 - 12/1 , SHORT - 13 - 12/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 57/16 , ALT -  - 37/17 , ALT -  - 30/15</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (4g/-3/%70)
-Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-3/%80)
-R - TP2/10G - %84 / 119 işlem - ADAY (4g/-3/%70)
-R - TP5/10G - %60 / 138 işlem - ADAY (4g/-3/%80)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/-15/%55)
+T - TP5/20G - %77 / 128 işlem - ADAY (2g/-15/%70)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>1</v>
+        <v>2.41000009</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-1.3</v>
+        <v>-4</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -6675,59 +6603,58 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 44 - 16/9 , SHORT - 4 - 6/4 , SHORT - 4 - 6/4</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 67/51 , ALT -  - 37/1 , ALT -  - 18/7</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>E-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (2g/-4/%55)
-U - TP2/10G - %75 / 97 işlem - ADAY (4g/-5/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (12g/-4/%80)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-13/%0)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>112.80000305</v>
+        <v>3.3599999</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -6741,36 +6668,35 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 2/12 , SHORT - 2 - 5/17 , SHORT - 2 - 4/6</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+SHORT - 5 - 13/4 , SHORT - 2 - 6/9 , SHORT - 4 - 11/6</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (2g/-5/%60)
-U - TP5/20G - %74 / 74 işlem - ADAY (4g/-3/%70)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (17g/-15/%25)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -6779,20 +6705,20 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>58.29999924</v>
+        <v>637.5</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-1.8</v>
+        <v>-10</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -6806,57 +6732,62 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 12 - 7/3 , SHORT - 12 - 7/3 , SHORT - 12 - 7/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 16/3 , ALT -  - 57/16 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (13g/-4/%60)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-14/%91)
+Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-14/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (5g/-14/%75)
+V - TP2/10G - %95 / 21 işlem - ADAY (5g/-14/%80)
+V - TP5/10G - %75 / 20 işlem - ADAY (6g/-12/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>21.34000015</v>
+        <v>62.70000076</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-3.7</v>
+        <v>-4.4</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -6870,57 +6801,57 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 7/3 , LONG - 11 - 18/7 , LONG - 9 - 19/7</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 2 - 7/3 , SHORT - 2 - 7/3 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (5g/-1/%80)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (18g/-8/%40)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>18.97999954</v>
+        <v>99.05000305</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-3.4</v>
+        <v>-8.1</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -6934,58 +6865,57 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 4 - 6/4 , LONG - 10 - 9/1 , SHORT - 12 - 9/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 14/4 , ALT -  - 14/4 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (2g/-6/%75)
-Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-6/%60)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (3g/-13/%82)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>50.45000076</v>
+        <v>18.20000076</v>
       </c>
       <c r="O47" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-3.8</v>
+        <v>1.5</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -6999,57 +6929,57 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 14 - 12/1 , ALT -  - 11/1 , SHORT - 12 - 11/2</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+SHORT - 3 - 4/18 , SHORT - 3 - 4/23 , UST -  - 5/16</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (6g/-8/%73)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>20.95999908</v>
+        <v>46.77999878</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-1.5</v>
+        <v>-10</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -7063,57 +6993,59 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 14/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 2 - 15/15 , SHORT - 2 - 15/9 , SHORT - 1 - 5/5</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-3/%60)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (2g/-14/%92)
+X - TP5/10G - %82 / 44 işlem - ADAY (2g/-14/%79)
+Y - TP5/10G - %61 / 71 işlem - ADAY (2g/-14/%60)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>10.92000008</v>
+        <v>2.51999998</v>
       </c>
       <c r="O49" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-3.2</v>
+        <v>-5.6</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -7127,35 +7059,36 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 16 - 14/16 , SHORT - 16 - 13/4 , ALT -  - 11/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 18 - 10/6 , SHORT - 6 - 11/2 , SHORT - 6 - 10/7</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-4/%60)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (6g/-8/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-8/%60)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
@@ -7164,20 +7097,20 @@
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>132.1000061</v>
+        <v>206.5</v>
       </c>
       <c r="O50" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-6</v>
+        <v>-4.2</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -7191,58 +7124,58 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-ALT -  - 42/5 , ALT -  - 25/6 , ALT -  - 18/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 3 - 9/3 , SHORT - 3 - 9/3 , SHORT - 3 - 8/3</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/-6/%70)
-T - TP5/20G - %77 / 128 işlem - ADAY (1g/-6/%80)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-9/%55)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-9/%50)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>2.67000008</v>
+        <v>272.25</v>
       </c>
       <c r="O51" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>1.2</v>
+        <v>-3.5</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -7256,47 +7189,48 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 9/1 , SHORT - 23 - 8/2 , LONG - 1 - 10/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 1 - 1/8 , SHORT - 3 - 9/14 , SHORT - 3 - 8/2</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-4/%60)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (3g/-8/%50)
+U - TP5/20G - %74 / 74 işlem - ADAY (5g/-7/%75)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N52" s="7" t="n">
-        <v>377</v>
+        <v>56.25</v>
       </c>
       <c r="O52" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
   </sheetData>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -478,7 +478,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -562,11 +562,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.5</v>
+        <v>-10</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -581,95 +581,27 @@
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 23 - 20/2 , ALT -  - 21/3 , LONG - 1 - 10/1</t>
+ALT -  - 28/13 , ALT -  - 74/28 , ALT -  - 27/15</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-TP2/10G, Z-TP2/10G, I-TP5/20G, U-TP5/20G, Z-TP5/20G</t>
+          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
-Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-8/%75)
-I - TP5/20G - %82 / 67 işlem - ADAY (0g/0/%100)
-U - TP5/20G - %74 / 74 işlem - ADAY (14g/-7/%56)
-Z - TP5/20G - %75 / 71 işlem - ADAY (14g/-7/%29)</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, Z: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 40 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 28/13 , ALT -  - 74/28 , ALT -  - 27/15</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, Y-TP2/10G, U-TP5/20G, V-TP2/10G, V-TP5/10G, Y-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (4g/-22/%91)
 Y - TP2/10G - %86 / 78 işlem - ONAY (3g/-22/%55)
@@ -679,9 +611,77 @@
 Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-22/%50)</t>
         </is>
       </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CVKMD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 1 - 10/3 , ALT -  - 17/6 , -</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (8g/-11/%30)
+X - TP2/10G - %98 / 46 işlem - ONAY (2g/-1/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-9/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (8g/-11/%74)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/-1/%85)</t>
+        </is>
+      </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, Y: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, V: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 32 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>56.45</v>
+        <v>14.06</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46282</v>
@@ -699,11 +699,11 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -717,48 +717,44 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 1 - 10/2 , ALT -  - 17/6 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+-</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-TP2/10G, X-TP2/10G, I-TP5/10G, I-TP5/20G, L-TP5/10G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (8g/-11/%30)
-X - TP2/10G - %98 / 46 işlem - ONAY (2g/-2/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/-9/%45)
-I - TP5/20G - %82 / 67 işlem - ADAY (8g/-11/%74)
-L - TP5/10G - %77 / 43 işlem - ADAY (2g/-2/%85)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (19g/-19/%38)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>13.96</v>
+        <v>3.1500001</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46282</v>
@@ -767,11 +763,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-6</v>
+        <v>-3.4</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -785,11 +781,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL +2, CNDL +1, XU030 -1, TOPLAM 0, ALMA
+ALT -  - 30/7 , ALT -  - 25/11 , -</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
@@ -802,39 +799,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (19g/?/%?)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-24/%25)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>3.1500001</v>
+        <v>14.45</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-1.3</v>
+        <v>2.6</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -848,8 +845,8 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL +1, XU030 -1, TOPLAM 0, ALMA
-ALT -  - 29/5 , ALT -  - 23/9 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 31/17 , ALT -  - 31/17 , -</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -859,24 +856,27 @@
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-23/%25)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (8g/-16/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-15/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-16/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (8g/-16/%45)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>14.76</v>
+        <v>252</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46282</v>
@@ -894,11 +894,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -913,37 +913,34 @@
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 30/15 , ALT -  - 30/15 , -</t>
+LONG - 1 - 10/0 , LONG - 1 - 10/0 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (8g/-15/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (9g/-14/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-15/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (8g/-15/%45)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-10/%69)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -952,7 +949,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>255</v>
+        <v>18.92</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46282</v>
@@ -965,7 +962,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-1.9</v>
+        <v>-4.4</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -979,8 +976,8 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL +1, XU030 -1, TOPLAM 4, İZLE
-ALT -  - 20/2 , ALT -  - 19/8 , -</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 -1, TOPLAM 3, İZLE
+ALT -  - 23/5 , ALT -  - 23/11 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -1002,9 +999,9 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-22/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-22/%15)
-Y - TP5/20G - %71 / 98 işlem - ADAY (15g/-22/%5)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-24/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-24/%15)
+Y - TP5/20G - %71 / 98 işlem - ADAY (15g/-24/%5)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1018,7 +1015,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46282</v>
@@ -1031,7 +1028,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-6.8</v>
+        <v>-9.9</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1046,7 +1043,7 @@
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 36/20 , ALT -  - 49/17 , -</t>
+ALT -  - 41/25 , ALT -  - 55/22 , -</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1068,8 +1065,8 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-20/%88)
-L - TP5/10G - %77 / 43 işlem - ADAY (4g/-20/%70)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-23/%88)
+L - TP5/10G - %77 / 43 işlem - ADAY (4g/-23/%70)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -1083,7 +1080,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>58.7</v>
+        <v>56.7</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46282</v>
@@ -1092,92 +1089,96 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
+          <t>GRSEL</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
+E - TP5/20G - %69 / 179 işlem - ADAY (7g/-5/%65)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-5/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-5/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-13/%0)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 70 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>279.75</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>MIATK</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
 -</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-26/%73)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IZENR</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 28/9 , ALT -  - 28/9 , -</t>
-        </is>
-      </c>
       <c r="F11" s="6" t="n">
         <v>55</v>
       </c>
@@ -1185,34 +1186,33 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (11g/-21/%75)
-Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-33/%10)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (5g/-26/%73)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>5.64</v>
+        <v>28.1</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46282</v>
@@ -1221,46 +1221,111 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 -1, TOPLAM 3, İZLE
+ALT -  - 35/15 , ALT -  - 35/15 , -</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (11g/-25/%75)
+Q - TP5/20G - %70 / 203 işlem - ADAY (16g/-36/%10)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>PSGYO</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="3" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F13" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-25/%35)
 I - TP5/10G - %61 / 109 işlem - ADAY (7g/-25/%45)
@@ -1269,84 +1334,18 @@
 R - TP5/20G - %80 / 102 işlem - ADAY (18g/-33/%15)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="N13" s="7" t="n">
         <v>2.34</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SASA</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-SHORT - 3 - 21/10 , SHORT - 3 - 21/5 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (3g/-19/%78)
-X - TP5/10G - %82 / 44 işlem - ADAY (3g/-19/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-19/%50)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>2.39</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46282</v>
@@ -1355,11 +1354,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1373,12 +1372,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-ALT -  - 22/0 , ALT -  - 26/3 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 23 - 22/0 , ALT -  - 23/5 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>1</v>
@@ -1391,19 +1390,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>Z-TP2/10G, U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (14g/-22/%60)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-19/%0)
-R - TP5/20G - %80 / 102 işlem - ADAY (7g/-19/%40)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-10/%75)
+U - TP5/20G - %74 / 74 işlem - ADAY (14g/-8/%56)
+Z - TP5/20G - %75 / 71 işlem - ADAY (14g/-8/%29)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ONAY Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1412,7 +1411,7 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>51.4</v>
+        <v>1.89</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46282</v>
@@ -1421,11 +1420,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1440,11 +1439,11 @@
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 34/1 , LONG - 1 - 33/2 , LONG - 1 - 10/0</t>
+ALT -  - 46/8 , ALT -  - 19/8 , ALT -  - 19/8</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1457,27 +1456,27 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Z-TP2/10G, Z-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-7/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-6/%65)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-12/%25)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>88.95</v>
+        <v>2.58</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46282</v>
@@ -1486,259 +1485,263 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 28/4 , ALT -  - 32/8 , -</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (14g/-25/%60)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-23/%0)
+R - TP5/20G - %80 / 102 işlem - ADAY (7g/-23/%40)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 65 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 41/15 , ALT -  - 36/20 , ALT -  - 34/19</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, L-TP5/10G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-16/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (8g/-15/%74)
+L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-15/%0)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 71 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 36/1 , ALT -  - 36/1 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Z-TP2/10G, Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-8/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-8/%55)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Z: seçili strateji teyidi; ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>ASELS</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 10/1 , LONG - 1 - 8/2 , LONG - 1 - 10/0</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 9/2 , LONG - 1 - 7/3 , LONG - 1 - 9/1</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Y-TP2/10G, E-TP5/20G, Y-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %69 / 179 işlem - ADAY (4g/-5/%60)
+E - TP5/20G - %69 / 179 işlem - ADAY (4g/-6/%50)
 Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)
 Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Y: seçili strateji teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N16" s="7" t="n">
-        <v>374.25</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AEFES</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 1 - 7/3 , LONG - 13 - 19/7 , LONG - 11 - 19/6</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-3/%75)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-ALT -  - 12/2 , SHORT - 91 - 13/8 , LONG - 1 - 17/1</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-5/%75)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-LONG - 8 - 8/3 , LONG - 1 - 10/0 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (8g/0/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (8g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-8/%5)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
       <c r="N19" s="7" t="n">
-        <v>26.14</v>
+        <v>369.5</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46282</v>
@@ -1747,11 +1750,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.8</v>
+        <v>2.1</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1765,46 +1768,44 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 42/16 , ALT -  - 37/21 , ALT -  - 35/20</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 1 - 9/2 , LONG - 13 - 20/5 , LONG - 11 - 21/5</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-17/%40)
-I - TP5/20G - %82 / 67 işlem - ADAY (8g/-16/%74)
-R - TP5/10G - %60 / 138 işlem - ADAY (8g/-16/%0)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-4/%75)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>66.5</v>
+        <v>18.53</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>46282</v>
@@ -1813,110 +1814,304 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 14/3 , SHORT - 91 - 14/7 , ALT -  - 18/0</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-6/%70)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 -1, TOPLAM -2, ALMA
+LONG - 8 - 9/2 , ALT -  - 11/1 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (8g/-1/%90)
+I - TP5/10G - %61 / 109 işlem - ADAY (8g/-1/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-9/%0)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-8/%27)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>ENKAI</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="B24" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
 LONG - 1 - 32/2 , LONG - 1 - 10/3 , LONG - 1 - 9/1</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F24" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%60)</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N21" s="7" t="n">
-        <v>83.95</v>
-      </c>
-      <c r="O21" s="8" t="n">
+      <c r="N24" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="O24" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>GSRAY</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-ALT -  - 14/1 , ALT -  - 14/1 , ALT -  - 14/1</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
+ALT -  - 16/3 , ALT -  - 16/3 , ALT -  - 16/3</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Q - TP2/10G - %82 / 103 işlem - ADAY (6g/-6/%45)
 Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-6/%50)
@@ -1924,723 +2119,533 @@
 R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%30)</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="N25" s="7" t="n">
         <v>0.97</v>
       </c>
-      <c r="O22" s="8" t="n">
+      <c r="O25" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>ECILC</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="B26" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
 ALT -  - 24/10 , ALT -  - 33/9 , ALT -  - 35/15</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F26" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>Y - TP5/20G - %71 / 98 işlem - ADAY (7g/-16/%35)</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N23" s="7" t="n">
-        <v>62.25</v>
-      </c>
-      <c r="O23" s="8" t="n">
+      <c r="N26" s="7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="O26" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>HEKTS</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="B27" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 60/18 , ALT -  - 40/19 , SHORT - 88 - 33/1</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/-17/%35)
+T - TP5/20G - %77 / 128 işlem - ADAY (3g/-17/%45)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 58/17 , ALT -  - 38/18 , SHORT - 88 - 32/2</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
+-</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I28" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/-16/%35)
-T - TP5/20G - %77 / 128 işlem - ADAY (3g/-16/%45)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>S-TP5/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (6g/-14/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (6g/-14/%90)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N24" s="7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O24" s="8" t="n">
+      <c r="N28" s="7" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O28" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DAPGM</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 13 - 9/4 , LONG - 1 - 10/1 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-5/%30)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 80/63 , ALT -  - 41/4 , ALT -  - 25/13</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-33/%0)
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-20/%0)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 48/9 , ALT -  - 137/75 , ALT -  - 102/82</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-52/%0)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TABGD</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
 -</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (6g/-11/%80)
-S - TP5/20G - %82 / 22 işlem - ADAY (6g/-11/%90)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="F33" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%95)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N25" s="7" t="n">
-        <v>33.26</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 9/1 , LONG - 1 - 9/1 , LONG - 1 - 9/1</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-7/%27)</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>20.82</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DAPGM</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-LONG - 1 - 16/1 , LONG - 1 - 16/1 , ALT -  - 14/2</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-2/%95)</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>157</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 13 - 7/5 , LONG - 1 - 8/2 , LONG - 1 - 9/1</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-4/%35)</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>98.75</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 39/3 , ALT -  - 122/64 , ALT -  - 89/71</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-49/%0)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>17.01</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TABGD</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/?/%?)</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="n">
-        <v>226.8999939</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MGROS</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 26/3 , ALT -  - 26/3 , ALT -  - 27/9</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/0/%95)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>510.5</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SARKY</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 12/1 , SHORT - 88 - 26/7 , ALT -  - 17/4</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-6/%60)</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N33" s="7" t="n">
-        <v>22.06</v>
+        <v>229.69999695</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46282</v>
@@ -2649,318 +2654,318 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
+          <t>TRMET</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+SHORT - 18 - 20/11 , SHORT - 18 - 15/2 , ALT -  - 15/4</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (8g/-9/%15)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 17/0 , LONG - 1 - 17/0 , ALT -  - 16/3</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-3/%85)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MGROS</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 26/3 , ALT -  - 26/3 , ALT -  - 28/9</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%95)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>508.5</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 14/1 , SHORT - 88 - 27/6 , ALT -  - 19/5</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-7/%60)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>AKSA</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="B38" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
 ALT -  - 15/4 , ALT -  - 15/4 , ALT -  - 15/4</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F38" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-4/%40)</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-4/%30)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N34" s="7" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="O34" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 44/6 , ALT -  - 17/6 , ALT -  - 17/6</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-10/%25)</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TRMET</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-SHORT - 18 - 17/14 , SHORT - 18 - 13/4 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (8g/-7/%25)</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="n">
-        <v>128.4</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BRSAN</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-SHORT - 6 - 12/5 , SHORT - 3 - 6/10 , SHORT - 5 - 10/6</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>X-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (18g/-15/%25)</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="n">
-        <v>640.5</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-SHORT - 3 - 4/6 , SHORT - 3 - 4/6 , LONG - 1 - 9/1</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-6/%25)</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N38" s="7" t="n">
-        <v>101.6</v>
+        <v>10.8</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46282</v>
@@ -2969,11 +2974,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>3.8</v>
+        <v>-1.2</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2987,37 +2992,35 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
-LONG - 1 - 8/2 , LONG - 1 - 8/2 , LONG - 1 - 8/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+SHORT - 6 - 14/3 , SHORT - 3 - 8/8 , SHORT - 5 - 12/5</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+          <t>X-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (6g/-5/%67)
-H - TP5/10G - %70 / 20 işlem - ADAY (6g/-5/%88)
-H - TP5/20G - %85 / 20 işlem - ADAY (6g/-5/%100)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (18g/-16/%25)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
@@ -3026,7 +3029,7 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>10.85</v>
+        <v>630</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46282</v>
@@ -3035,11 +3038,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3053,47 +3056,44 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-SHORT - 14 - 10/3 , LONG - 1 - 10/1 , LONG - 1 - 9/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+SHORT - 3 - 6/4 , SHORT - 3 - 6/4 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G, Y-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-8/%40)
-U - TP2/10G - %75 / 97 işlem - ADAY (6g/-9/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (14g/-8/%56)
-Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-8/%25)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 78 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>108.2</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>46282</v>
@@ -3102,11 +3102,11 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3120,36 +3120,37 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-SHORT - 19 - 6/10 , SHORT - 7 - 7/5 , SHORT - 7 - 6/10</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 1 - 9/1 , LONG - 1 - 9/1 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (7g/-5/%80)
-Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-5/%70)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (6g/-6/%67)
+H - TP5/10G - %70 / 20 işlem - ADAY (6g/-6/%88)
+H - TP5/20G - %85 / 20 işlem - ADAY (6g/-6/%100)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -3158,7 +3159,7 @@
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>213.9</v>
+        <v>10.73</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46282</v>
@@ -3167,11 +3168,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3185,47 +3186,44 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+SHORT - 4 - 3/19 , SHORT - 4 - 3/24 , UST -  - 6/16</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (7g/-4/%80)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/-4/%50)
-I - TP5/20G - %82 / 67 işlem - ADAY (7g/-4/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-11/%0)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-7/%57)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 77 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>285</v>
+        <v>47.5</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46282</v>
@@ -3234,11 +3232,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>4</v>
+        <v>-7.1</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3252,36 +3250,37 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-SHORT - 4 - 5/7 , LONG - 28 - 14/11 , SHORT - 4 - 3/7</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+SHORT - 3 - 23/9 , SHORT - 3 - 23/3 , ALT -  - 12/2</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-6/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-6/%40)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (3g/-20/%78)
+X - TP5/10G - %82 / 44 işlem - ADAY (3g/-20/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-20/%50)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3290,7 +3289,7 @@
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>283.25</v>
+        <v>2.34</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46282</v>
@@ -3299,11 +3298,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3317,36 +3316,36 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-LONG - 1 - 9/1 , LONG - 1 - 9/2 , ALT -  - 11/0</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+SHORT - 19 - 7/9 , SHORT - 7 - 8/4 , SHORT - 7 - 7/9</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-8/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-8/%35)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (7g/-6/%80)
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-6/%70)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -3355,7 +3354,7 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>49.18</v>
+        <v>211.4</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46282</v>
@@ -3364,11 +3363,11 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3382,36 +3381,36 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-UST -  - 0/10 , SHORT - 4 - 8/16 , SHORT - 4 - 6/4</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+SHORT - 4 - 7/5 , LONG - 28 - 16/9 , SHORT - 4 - 5/5</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (4g/-7/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (6g/-6/%80)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-7/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-7/%40)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -3420,7 +3419,7 @@
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>57</v>
+        <v>279.25</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46282</v>
@@ -3429,7 +3428,7 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -3447,35 +3446,36 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 17/4 , ALT -  - 16/5 , ALT -  - 17/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 12/1 , ALT -  - 11/0 , ALT -  - 13/3</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (16g/-15/%35)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-10/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-10/%35)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>19.71</v>
+        <v>48.1</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46282</v>
@@ -3493,11 +3493,11 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-1.8</v>
+        <v>-0.1</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3512,35 +3512,36 @@
       <c r="E47" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 68/52 , ALT -  - 37/1 , ALT -  - 17/6</t>
+SHORT - 14 - 11/1 , ALT -  - 11/1 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-29/%0)
-R - TP5/10G - %60 / 138 işlem - ADAY (8g/-15/%0)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
+U - TP2/10G - %75 / 97 işlem - ADAY (6g/-10/%30)
+U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -3549,7 +3550,7 @@
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>3.3</v>
+        <v>107.2</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46282</v>
@@ -3558,11 +3559,11 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3576,44 +3577,45 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 10/1 , LONG - 1 - 10/1 , ALT -  - 11/0</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+SHORT - 2 - 2/8 , SHORT - 4 - 9/14 , SHORT - 4 - 8/2</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-9/%69)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (4g/-9/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (6g/-7/%75)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>18.94</v>
+        <v>56.15</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46282</v>
@@ -3622,11 +3624,11 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3640,12 +3642,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 10/3 , LONG - 1 - 10/3 , ALT -  - 17/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+ALT -  - 18/5 , ALT -  - 16/5 , ALT -  - 17/4</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3658,26 +3660,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-6/%70)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (16g/-15/%35)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>282.75</v>
+        <v>19.68</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46282</v>
@@ -3686,11 +3688,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3705,43 +3707,43 @@
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-UST -  - 1/22 , UST -  - 1/27 , UST -  - 9/20</t>
+LONG - 1 - 11/2 , LONG - 1 - 11/2 , ALT -  - 18/7</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-3/%71)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-6/%55)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>49.32</v>
+        <v>281</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46282</v>
@@ -3754,7 +3756,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3769,11 +3771,11 @@
       <c r="E51" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 32/4 , ALT -  - 27/8 , ALT -  - 36/0</t>
+ALT -  - 31/3 , ALT -  - 25/7 , LONG - 1 - 35/0</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -3791,7 +3793,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (17g/-6/%35)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (17g/-5/%35)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3801,11 +3803,11 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>36.36</v>
+        <v>36.8</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46282</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 1 - 10/3 , ALT -  - 17/6 , -</t>
+LONG - 1 - 9/3 , ALT -  - 16/5 , -</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -672,11 +672,11 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (8g/-11/%30)
-X - TP2/10G - %98 / 46 işlem - ONAY (2g/-1/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/-9/%40)
-I - TP5/20G - %82 / 67 işlem - ADAY (8g/-11/%74)
-L - TP5/10G - %77 / 43 işlem - ADAY (2g/-1/%85)</t>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (8g/-10/%30)
+X - TP2/10G - %98 / 46 işlem - ONAY (2g/0/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-8/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (8g/-10/%74)
+L - TP5/10G - %77 / 43 işlem - ADAY (2g/0/%85)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>14.06</v>
+        <v>14.14</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46282</v>
@@ -699,126 +699,126 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
+          <t>BRSAN</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 13/4 , SHORT - 3 - 2/13 , SHORT - 5 - 7/9</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>X-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (18g/-12/%25)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>665</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>KONTR</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
 -</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>M-TP5/20G</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>M - TP5/20G - %89 / 55 işlem - ONAY (19g/-19/%38)</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N5" s="7" t="n">
         <v>3.1500001</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL +2, CNDL +1, XU030 -1, TOPLAM 0, ALMA
-ALT -  - 30/7 , ALT -  - 25/11 , -</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-24/%25)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>14.45</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>46282</v>
@@ -827,11 +827,11 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -845,8 +845,8 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 31/17 , ALT -  - 31/17 , -</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 30/6 , ALT -  - 24/10 , -</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -856,27 +856,24 @@
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (8g/-16/%80)
-L - TP5/10G - %77 / 43 işlem - ADAY (9g/-15/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-16/%30)
-R - TP5/20G - %80 / 102 işlem - ADAY (8g/-16/%45)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-24/%25)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -885,7 +882,7 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>252</v>
+        <v>14.68</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46282</v>
@@ -894,53 +891,56 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 29/14 , ALT -  - 29/14 , -</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 10/0 , LONG - 1 - 10/0 , ALT -  - 11/1</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>L-TP2/10G, L-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-10/%69)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (8g/-15/%80)
+L - TP5/10G - %77 / 43 işlem - ADAY (9g/-13/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-14/%30)
+R - TP5/20G - %80 / 102 işlem - ADAY (8g/-15/%45)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>18.92</v>
+        <v>257.25</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46282</v>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-4.4</v>
+        <v>-2.6</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL +2, CNDL 0, XU030 -1, TOPLAM 3, İZLE
-ALT -  - 23/5 , ALT -  - 23/11 , -</t>
+ALT -  - 22/4 , ALT -  - 21/10 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -999,9 +999,9 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-24/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-24/%15)
-Y - TP5/20G - %71 / 98 işlem - ADAY (15g/-24/%5)</t>
+          <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-23/%50)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-22/%15)
+Y - TP5/20G - %71 / 98 işlem - ADAY (15g/-23/%5)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46282</v>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-1.5</v>
+        <v>-2.6</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
       <c r="K10" s="5" t="inlineStr">
         <is>
           <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %69 / 179 işlem - ADAY (7g/-5/%65)
-I - TP5/10G - %61 / 109 işlem - ADAY (7g/-5/%40)
-I - TP5/20G - %82 / 67 işlem - ADAY (7g/-5/%80)
-Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-13/%0)</t>
+E - TP5/20G - %69 / 179 işlem - ADAY (7g/-7/%50)
+I - TP5/10G - %61 / 109 işlem - ADAY (7g/-7/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (7g/-7/%80)
+Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-14/%0)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>279.75</v>
+        <v>276.5</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46282</v>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 23 - 22/0 , ALT -  - 23/5 , ALT -  - 11/1</t>
+LONG - 23 - 21/1 , ALT -  - 22/4 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-10/%75)
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-9/%75)
 U - TP5/20G - %74 / 74 işlem - ADAY (14g/-8/%56)
 Z - TP5/20G - %75 / 71 işlem - ADAY (14g/-8/%29)</t>
         </is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46282</v>
@@ -1420,11 +1420,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1438,45 +1438,46 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 46/8 , ALT -  - 19/8 , ALT -  - 19/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+SHORT - 3 - 19/12 , SHORT - 3 - 19/7 , SHORT - 2 - 8/2</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-12/%25)</t>
+          <t>X - TP5/20G - %93 / 43 işlem - ONAY (3g/-18/%78)
+X - TP5/10G - %82 / 44 işlem - ADAY (3g/-18/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-18/%50)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46282</v>
@@ -1489,7 +1490,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
@@ -1504,7 +1505,7 @@
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 28/4 , ALT -  - 32/8 , -</t>
+ALT -  - 32/8 , ALT -  - 37/12 , -</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1526,9 +1527,9 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (14g/-25/%60)
-R - TP5/10G - %60 / 138 işlem - ADAY (7g/-23/%0)
-R - TP5/20G - %80 / 102 işlem - ADAY (7g/-23/%40)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (14g/-29/%60)
+R - TP5/10G - %60 / 138 işlem - ADAY (7g/-26/%0)
+R - TP5/20G - %80 / 102 işlem - ADAY (7g/-26/%40)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1542,7 +1543,7 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>49.12</v>
+        <v>47.04</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46282</v>
@@ -1555,7 +1556,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1570,7 +1571,7 @@
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 41/15 , ALT -  - 36/20 , ALT -  - 34/19</t>
+ALT -  - 38/13 , ALT -  - 33/18 , ALT -  - 31/16</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1592,10 +1593,10 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-16/%40)
-I - TP5/20G - %82 / 67 işlem - ADAY (8g/-15/%74)
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-14/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (8g/-13/%74)
 L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %60 / 138 işlem - ADAY (8g/-15/%0)</t>
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-13/%0)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1609,7 +1610,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>67.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46282</v>
@@ -1622,7 +1623,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1636,8 +1637,8 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 36/1 , ALT -  - 36/1 , ALT -  - 12/1</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 33/2 , LONG - 1 - 32/3 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1659,8 +1660,8 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-8/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-8/%55)</t>
+          <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-6/%75)
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-5/%70)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1674,7 +1675,7 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>87.8</v>
+        <v>89.95</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46282</v>
@@ -1683,11 +1684,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1701,47 +1702,46 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 10/1 , LONG - 1 - 8/2 , LONG - 1 - 10/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 8 - 7/4 , LONG - 1 - 9/1 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, E-TP5/20G, Y-TP5/10G, Y-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %69 / 179 işlem - ADAY (4g/-6/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)
-Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (8g/+1/%100)
+I - TP5/10G - %61 / 109 işlem - ADAY (8g/+1/%100)
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-7/%5)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Y: seçili strateji teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>369.5</v>
+        <v>26.44</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46282</v>
@@ -1750,11 +1750,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -1768,350 +1768,28 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 1 - 9/2 , LONG - 13 - 20/5 , LONG - 11 - 21/5</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-4/%75)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 14/3 , SHORT - 91 - 14/7 , ALT -  - 18/0</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-6/%70)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>77.05</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 -1, TOPLAM -2, ALMA
-LONG - 8 - 9/2 , ALT -  - 11/1 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (8g/-1/%90)
-I - TP5/10G - %61 / 109 işlem - ADAY (8g/-1/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-9/%0)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 84 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 11/0 , ALT -  - 11/0 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-8/%27)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ENKAI</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 32/2 , LONG - 1 - 10/3 , LONG - 1 - 9/1</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-7/%60)</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>84</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>GSRAY</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-ALT -  - 16/3 , ALT -  - 16/3 , ALT -  - 16/3</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Q - TP2/10G - %82 / 103 işlem - ADAY (6g/-6/%45)
 Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-6/%50)
@@ -2119,18 +1797,339 @@
 R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%30)</t>
         </is>
       </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>S-TP5/10G, S-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>S - TP5/10G - %78 / 23 işlem - ADAY (6g/-19/%80)
+S - TP5/20G - %82 / 22 işlem - ADAY (6g/-19/%90)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 9/2 , LONG - 1 - 9/2 , LONG - 1 - 9/2</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-6/%27)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DAPGM</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 1 - 16/2 , LONG - 1 - 16/2 , ALT -  - 14/1</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-2/%95)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 13 - 7/5 , LONG - 1 - 8/2 , LONG - 1 - 10/1</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-3/%35)</t>
+        </is>
+      </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>0.97</v>
+        <v>99.2</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46282</v>
@@ -2139,11 +2138,11 @@
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>3.7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
@@ -2157,35 +2156,36 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 24/10 , ALT -  - 33/9 , ALT -  - 35/15</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 81/64 , ALT -  - 42/5 , ALT -  - 25/13</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>E-TP5/20G, R-TP5/10G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (7g/-16/%35)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-34/%0)
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-21/%0)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>62.6</v>
+        <v>3.08</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46282</v>
@@ -2203,11 +2203,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.5</v>
+        <v>-10</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
@@ -2222,35 +2222,34 @@
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 60/18 , ALT -  - 40/19 , SHORT - 88 - 33/1</t>
+ALT -  - 48/9 , ALT -  - 137/75 , ALT -  - 102/82</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/-17/%35)
-T - TP5/20G - %77 / 128 işlem - ADAY (3g/-17/%45)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-52/%0)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2259,7 +2258,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>2.35</v>
+        <v>15.9</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>46282</v>
@@ -2268,11 +2267,11 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-5.1</v>
+        <v>1.2</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -2286,36 +2285,35 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+          <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
 -</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>S-TP5/10G, S-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>S - TP5/10G - %78 / 23 işlem - ADAY (6g/-14/%80)
-S - TP5/20G - %82 / 22 işlem - ADAY (6g/-14/%90)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%95)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
@@ -2324,7 +2322,7 @@
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>31.9</v>
+        <v>229.69999695</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>46282</v>
@@ -2333,11 +2331,11 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-9.9</v>
+        <v>1.2</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -2351,44 +2349,45 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 54/14 , ALT -  - 35/15 , SHORT - 88 - 29/5</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/-14/%35)
+T - TP5/20G - %77 / 128 işlem - ADAY (3g/-14/%45)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>6.16</v>
+        <v>2.44</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>46282</v>
@@ -2397,11 +2396,11 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
@@ -2415,12 +2414,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 13 - 9/4 , LONG - 1 - 10/1 , ALT -  - 11/1</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 10/2 , SHORT - 88 - 23/9 , ALT -  - 15/2</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0</v>
@@ -2438,7 +2437,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-5/%30)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-4/%65)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2448,11 +2447,11 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>97.59999999999999</v>
+        <v>22.58</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46282</v>
@@ -2461,11 +2460,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-8</v>
+        <v>4.4</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
@@ -2479,45 +2478,44 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 80/63 , ALT -  - 41/4 , ALT -  - 25/13</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-33/%0)
-R - TP5/10G - %60 / 138 işlem - ADAY (8g/-20/%0)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-2/%45)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>3.09</v>
+        <v>11.08</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>46282</v>
@@ -2526,11 +2524,11 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-10</v>
+        <v>1.9</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -2544,12 +2542,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 48/9 , ALT -  - 137/75 , ALT -  - 102/82</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 43/6 , ALT -  - 17/6 , ALT -  - 17/6</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -2567,7 +2565,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-52/%0)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-11/%25)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2577,11 +2575,11 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>15.9</v>
+        <v>2.63</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>46282</v>
@@ -2590,11 +2588,11 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -2608,12 +2606,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+SHORT - 18 - 15/15 , SHORT - 18 - 11/5 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>0</v>
@@ -2631,7 +2629,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%95)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (8g/-5/%35)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2641,11 +2639,11 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>229.69999695</v>
+        <v>130.8</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46282</v>
@@ -2654,11 +2652,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2672,44 +2670,44 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-SHORT - 18 - 20/11 , SHORT - 18 - 15/2 , ALT -  - 15/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+SHORT - 3 - 2/8 , SHORT - 3 - 2/8 , LONG - 1 - 7/3</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (8g/-9/%15)</t>
+          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-4/%25)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>125.7</v>
+        <v>103.9</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46282</v>
@@ -2718,11 +2716,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2737,43 +2735,43 @@
       <c r="E35" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 17/0 , LONG - 1 - 17/0 , ALT -  - 16/3</t>
+SHORT - 4 - 1/21 , SHORT - 4 - 0/26 , UST -  - 8/18</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>K-TP5/10G</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-3/%85)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-4/%71)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>155</v>
+        <v>48.66</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46282</v>
@@ -2782,11 +2780,11 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
@@ -2800,44 +2798,47 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 26/3 , ALT -  - 26/3 , ALT -  - 28/9</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 1 - 7/4 , LONG - 1 - 7/3 , LONG - 1 - 7/3</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-1/%95)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-5/%45)
+U - TP2/10G - %75 / 97 işlem - ADAY (6g/-6/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (14g/-6/%56)
+Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 78 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>508.5</v>
+        <v>111.6</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46282</v>
@@ -2846,11 +2847,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.1</v>
+        <v>5.2</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -2864,44 +2865,45 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 14/1 , SHORT - 88 - 27/6 , ALT -  - 19/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 1 - 8/2 , LONG - 1 - 8/2 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-7/%60)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-7/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-7/%40)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>21.76</v>
+        <v>49.78</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46282</v>
@@ -2910,11 +2912,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>SOKM</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2928,44 +2930,45 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 15/4 , ALT -  - 15/4 , ALT -  - 15/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+UST -  - 1/10 , SHORT - 4 - 7/16 , SHORT - 4 - 5/5</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-4/%30)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (4g/-6/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (6g/-4/%80)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>10.8</v>
+        <v>57.7</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46282</v>
@@ -2974,11 +2977,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-1.2</v>
+        <v>6.6</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2992,12 +2995,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-SHORT - 6 - 14/3 , SHORT - 3 - 8/8 , SHORT - 5 - 12/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 7/3 , LONG - 1 - 7/3 , LONG - 1 - 8/2</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1</v>
@@ -3010,26 +3013,26 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (18g/-16/%25)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-7/%69)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 24 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>630</v>
+        <v>19.41</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46282</v>
@@ -3038,11 +3041,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -3056,44 +3059,47 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-SHORT - 3 - 6/4 , SHORT - 3 - 6/4 , ALT -  - 11/1</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
+LONG - 1 - 4/6 , LONG - 1 - 4/6 , LONG - 1 - 4/6</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %89 / 45 işlem - ONAY (19g/-8/%25)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (6g/-1/%67)
+H - TP5/10G - %70 / 20 işlem - ADAY (6g/-1/%75)
+H - TP5/20G - %85 / 20 işlem - ADAY (6g/-1/%100)
+Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N40" s="7" t="n">
-        <v>99.65000000000001</v>
+        <v>11.25</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>46282</v>
@@ -3102,11 +3108,11 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -3120,46 +3126,46 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-LONG - 1 - 9/1 , LONG - 1 - 9/1 , LONG - 1 - 10/1</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+LONG - 1 - 4/6 , LONG - 84 - 8/12 , SHORT - 7 - 3/12</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+          <t>U-TP5/20G, Y-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (6g/-6/%67)
-H - TP5/10G - %70 / 20 işlem - ADAY (6g/-6/%88)
-H - TP5/20G - %85 / 20 işlem - ADAY (6g/-6/%100)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (7g/-2/%95)
+Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-2/%75)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>10.73</v>
+        <v>220.1</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46282</v>
@@ -3168,11 +3174,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3186,44 +3192,47 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-SHORT - 4 - 3/19 , SHORT - 4 - 3/24 , UST -  - 6/16</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 7/3 , LONG - 1 - 5/5 , LONG - 1 - 7/3</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>K-TP5/10G</t>
+          <t>Y-TP2/10G, E-TP5/20G, Y-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-7/%57)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
+E - TP5/20G - %69 / 179 işlem - ADAY (4g/-3/%80)
+Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)
+Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Y: seçili strateji teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 75 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>47.5</v>
+        <v>381</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46282</v>
@@ -3232,11 +3241,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-7.1</v>
+        <v>9.4</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3250,46 +3259,44 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-SHORT - 3 - 23/9 , SHORT - 3 - 23/3 , ALT -  - 12/2</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+ALT -  - 29/1 , ALT -  - 23/5 , LONG - 1 - 32/2</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X-TP5/20G, X-TP5/10G, Y-TP5/10G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>X - TP5/20G - %93 / 43 işlem - ONAY (3g/-20/%78)
-X - TP5/10G - %82 / 44 işlem - ADAY (3g/-20/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (3g/-20/%50)</t>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (17g/-3/%35)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY X: seçili strateji teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 30 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>2.34</v>
+        <v>37.54</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46282</v>
@@ -3298,11 +3305,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3317,44 +3324,43 @@
       <c r="E44" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-SHORT - 19 - 7/9 , SHORT - 7 - 8/4 , SHORT - 7 - 7/9</t>
+LONG - 1 - 5/5 , LONG - 13 - 17/8 , LONG - 11 - 17/8</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>U-TP5/20G, Z-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (7g/-6/%80)
-Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-6/%70)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-1/%75)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>211.4</v>
+        <v>19.11</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46282</v>
@@ -3363,11 +3369,11 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3382,44 +3388,43 @@
       <c r="E45" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-SHORT - 4 - 7/5 , LONG - 28 - 16/9 , SHORT - 4 - 5/5</t>
+LONG - 1 - 9/1 , SHORT - 91 - 9/10 , LONG - 1 - 13/4</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-7/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-7/%40)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-2/%75)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>279.25</v>
+        <v>80.45</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46282</v>
@@ -3428,11 +3433,11 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3446,45 +3451,44 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 12/1 , ALT -  - 11/0 , ALT -  - 13/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 29/5 , LONG - 1 - 7/5 , LONG - 1 - 7/3</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-10/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-10/%35)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-4/%75)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>48.1</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46282</v>
@@ -3493,11 +3497,11 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-0.1</v>
+        <v>5.4</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -3511,46 +3515,44 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-SHORT - 14 - 11/1 , ALT -  - 11/1 , ALT -  - 11/0</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+ALT -  - 14/1 , ALT -  - 12/2 , ALT -  - 13/0</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-9/%45)
-U - TP2/10G - %75 / 97 işlem - ADAY (6g/-10/%30)
-U - TP5/20G - %74 / 74 işlem - ADAY (14g/-9/%56)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (16g/-12/%35)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>107.2</v>
+        <v>20.44</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46282</v>
@@ -3559,11 +3561,11 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOKM</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-0.2</v>
+        <v>5.2</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3577,45 +3579,45 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-SHORT - 2 - 2/8 , SHORT - 4 - 9/14 , SHORT - 4 - 8/2</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+SHORT - 4 - 4/8 , LONG - 28 - 13/11 , SHORT - 4 - 2/7</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (4g/-9/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (6g/-7/%75)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-5/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-5/%45)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>56.15</v>
+        <v>286.5</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46282</v>
@@ -3624,11 +3626,11 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3642,12 +3644,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-ALT -  - 18/5 , ALT -  - 16/5 , ALT -  - 17/4</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+ALT -  - 21/7 , ALT -  - 30/6 , ALT -  - 31/12</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3660,26 +3662,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (16g/-15/%35)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (7g/-14/%35)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>19.68</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46282</v>
@@ -3688,11 +3690,11 @@
     <row r="50" ht="32" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3707,11 +3709,11 @@
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 11/2 , LONG - 1 - 11/2 , ALT -  - 18/7</t>
+ALT -  - 22/0 , ALT -  - 22/0 , ALT -  - 24/6</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -3729,7 +3731,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-6/%55)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -3739,11 +3741,11 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>281</v>
+        <v>526</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46282</v>
@@ -3752,11 +3754,11 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3771,7 +3773,7 @@
       <c r="E51" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 31/3 , ALT -  - 25/7 , LONG - 1 - 35/0</t>
+LONG - 1 - 8/5 , LONG - 1 - 8/5 , ALT -  - 15/4</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
@@ -3788,17 +3790,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (17g/-5/%35)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (5g/-3/%75)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
@@ -3807,7 +3809,7 @@
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>36.8</v>
+        <v>288.75</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46282</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>56.45</v>
+        <v>56.45000076</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46282</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>14.14</v>
+        <v>14.14999962</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46282</v>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 13/4 , SHORT - 3 - 2/13 , SHORT - 5 - 7/9</t>
+LONG - 1 - 12/4 , SHORT - 3 - 2/13 , SHORT - 5 - 6/10</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>46282</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>14.68</v>
+        <v>14.68000031</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>46282</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 29/14 , ALT -  - 29/14 , -</t>
+ALT -  - 30/15 , ALT -  - 30/15 , -</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -934,7 +934,7 @@
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (8g/-15/%80)
 L - TP5/10G - %77 / 43 işlem - ADAY (9g/-13/%30)
-Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-14/%30)
+Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-15/%30)
 R - TP5/20G - %80 / 102 işlem - ADAY (8g/-15/%45)</t>
         </is>
       </c>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>257.25</v>
+        <v>255.5</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46282</v>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-2.6</v>
+        <v>-3.3</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL +2, CNDL 0, XU030 -1, TOPLAM 3, İZLE
-ALT -  - 22/4 , ALT -  - 21/10 , -</t>
+ALT -  - 22/4 , ALT -  - 22/10 , -</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -1000,7 +1000,7 @@
       <c r="K8" s="5" t="inlineStr">
         <is>
           <t>M - TP5/20G - %89 / 55 işlem - ONAY (16g/-23/%50)
-Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-22/%15)
+Q - TP5/20G - %70 / 203 işlem - ADAY (14g/-23/%15)
 Y - TP5/20G - %71 / 98 işlem - ADAY (15g/-23/%5)</t>
         </is>
       </c>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>2.63</v>
+        <v>2.6099999</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46282</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>56.7</v>
+        <v>56.70000076</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>46282</v>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="N10" s="7" t="n">
-        <v>276.5</v>
+        <v>276</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>46282</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>28.1</v>
+        <v>28.10000038</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>46282</v>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="N12" s="7" t="n">
-        <v>5.35</v>
+        <v>5.3499999</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>46282</v>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>2.34</v>
+        <v>2.33999991</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>46282</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>1.9</v>
+        <v>1.89999998</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46282</v>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-SHORT - 3 - 19/12 , SHORT - 3 - 19/7 , SHORT - 2 - 8/2</t>
+SHORT - 3 - 20/12 , SHORT - 3 - 20/6 , SHORT - 2 - 9/1</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>2.43</v>
+        <v>2.42000008</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46282</v>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>47.04</v>
+        <v>47.04000092</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46282</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 38/13 , ALT -  - 33/18 , ALT -  - 31/16</t>
+ALT -  - 39/14 , ALT -  - 34/19 , ALT -  - 32/17</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1593,10 +1593,10 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-14/%40)
-I - TP5/20G - %82 / 67 işlem - ADAY (8g/-13/%74)
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (6g/-15/%40)
+I - TP5/20G - %82 / 67 işlem - ADAY (8g/-14/%74)
 L - TP5/10G - %77 / 43 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %60 / 138 işlem - ADAY (8g/-13/%0)</t>
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-14/%0)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46282</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       <c r="E18" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 33/2 , LONG - 1 - 32/3 , LONG - 1 - 9/1</t>
+LONG - 1 - 33/2 , LONG - 1 - 32/2 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1661,7 +1661,7 @@
       <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Z - TP2/10G - %88 / 43 işlem - ONAY (6g/-6/%75)
-Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-5/%70)</t>
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-6/%70)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>89.95</v>
+        <v>89.75</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>46282</v>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-LONG - 8 - 7/4 , LONG - 1 - 9/1 , LONG - 1 - 10/1</t>
+LONG - 8 - 7/3 , LONG - 1 - 10/1 , LONG - 1 - 10/0</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1727,7 +1727,7 @@
         <is>
           <t>E - TP5/20G - %69 / 179 işlem - ADAY (8g/+1/%100)
 I - TP5/10G - %61 / 109 işlem - ADAY (8g/+1/%100)
-Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-7/%5)</t>
+Q - TP5/20G - %70 / 203 işlem - ADAY (19g/-8/%5)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>26.44</v>
+        <v>26.31999969</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>46282</v>
@@ -1750,46 +1750,110 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
+          <t>ENKAI</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 30/4 , LONG - 1 - 8/4 , LONG - 1 - 7/3</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Z-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-5/%70)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>GSRAY</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
 ALT -  - 15/2 , ALT -  - 15/2 , ALT -  - 15/2</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F21" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Q - TP2/10G - %82 / 103 işlem - ADAY (6g/-6/%45)
 Q - TP5/20G - %70 / 203 işlem - ADAY (6g/-6/%50)
@@ -1797,147 +1861,83 @@
 R - TP5/10G - %60 / 138 işlem - ADAY (6g/-6/%30)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N20" s="7" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O20" s="8" t="n">
+      <c r="N21" s="7" t="n">
+        <v>0.97000003</v>
+      </c>
+      <c r="O21" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>MAGEN</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F22" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>S-TP5/10G, S-TP5/20G</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>S - TP5/10G - %78 / 23 işlem - ADAY (6g/-19/%80)
 S - TP5/20G - %82 / 22 işlem - ADAY (6g/-19/%90)</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>ADAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 22 hisse / 22 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N21" s="7" t="n">
-        <v>30.26</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 9/2 , LONG - 1 - 9/2 , LONG - 1 - 9/2</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-6/%27)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N22" s="7" t="n">
-        <v>20.94</v>
+        <v>30.26000023</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46282</v>
@@ -1946,92 +1946,92 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 9/1 , LONG - 1 - 9/1 , LONG - 1 - 9/1</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (15g/-7/%27)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>20.86000061</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>DAPGM</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B24" s="3" t="n">
         <v>-9.9</v>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-LONG - 1 - 16/2 , LONG - 1 - 16/2 , ALT -  - 14/1</t>
-        </is>
-      </c>
       <c r="F24" s="6" t="n">
         <v>42</v>
       </c>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-2/%95)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (16g/-27/%5)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>157.5</v>
+        <v>6.15999985</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>46282</v>
@@ -2074,92 +2074,92 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
+          <t>DOAS</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 1 - 16/1 , LONG - 1 - 16/1 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (2g/-2/%95)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>156.8999939</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>TCELL</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B26" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
 LONG - 13 - 7/5 , LONG - 1 - 8/2 , LONG - 1 - 10/1</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-3/%35)</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BTCIM</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-ALT -  - 81/64 , ALT -  - 42/5 , ALT -  - 25/13</t>
-        </is>
-      </c>
       <c r="F26" s="6" t="n">
         <v>42</v>
       </c>
@@ -2167,25 +2167,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>E-TP5/20G, R-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-34/%0)
-R - TP5/10G - %60 / 138 işlem - ADAY (8g/-21/%0)</t>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-3/%35)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
@@ -2194,7 +2193,7 @@
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>3.08</v>
+        <v>99.15000153</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46282</v>
@@ -2203,255 +2202,256 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+ALT -  - 79/62 , ALT -  - 41/4 , ALT -  - 24/12</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (17g/-33/%0)
+R - TP5/10G - %60 / 138 işlem - ADAY (8g/-20/%0)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 84 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>3.1099999</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>BSOKE</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B28" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
 ALT -  - 48/9 , ALT -  - 137/75 , ALT -  - 102/82</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F28" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-52/%0)</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N27" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="O27" s="8" t="n">
+      <c r="N28" s="7" t="n">
+        <v>15.89999962</v>
+      </c>
+      <c r="O28" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>TABGD</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="B29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
 -</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F29" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/-1/%95)</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (5g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N28" s="7" t="n">
-        <v>229.69999695</v>
-      </c>
-      <c r="O28" s="8" t="n">
+      <c r="N29" s="7" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="O29" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>HEKTS</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="B30" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 54/14 , ALT -  - 35/15 , SHORT - 88 - 29/5</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
+ALT -  - 55/14 , ALT -  - 35/15 , SHORT - 88 - 29/4</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I30" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/-14/%35)
 T - TP5/20G - %77 / 128 işlem - ADAY (3g/-14/%45)</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N29" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>SARKY</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 10/2 , SHORT - 88 - 23/9 , ALT -  - 15/2</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-4/%65)</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N30" s="7" t="n">
-        <v>22.58</v>
+        <v>2.43000007</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46282</v>
@@ -2460,156 +2460,156 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
+LONG - 1 - 11/2 , SHORT - 88 - 23/9 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 179 işlem - ADAY (3g/-4/%70)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 91 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>AKSA</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="B32" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
 ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 12/1</t>
         </is>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F32" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-2/%45)</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (18g/-1/%45)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N31" s="7" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="O31" s="8" t="n">
+      <c r="N32" s="7" t="n">
+        <v>11.11999989</v>
+      </c>
+      <c r="O32" s="8" t="n">
         <v>46282</v>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>FENER</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B33" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
 ALT -  - 43/6 , ALT -  - 17/6 , ALT -  - 17/6</t>
         </is>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-11/%25)</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TRMET</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-SHORT - 18 - 15/15 , SHORT - 18 - 11/5 , ALT -  - 11/0</t>
-        </is>
-      </c>
       <c r="F33" s="6" t="n">
         <v>38</v>
       </c>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (8g/-5/%35)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (7g/-10/%25)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>130.8</v>
+        <v>2.63000011</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46282</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>103.9</v>
+        <v>103.80000305</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46282</v>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       <c r="E35" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-SHORT - 4 - 1/21 , SHORT - 4 - 0/26 , UST -  - 8/18</t>
+SHORT - 4 - 2/20 , SHORT - 4 - 2/25 , UST -  - 7/17</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-4/%71)</t>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-6/%71)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>48.66</v>
+        <v>47.79999924</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46282</v>
@@ -2780,121 +2780,120 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
+          <t>TRALT</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+LONG - 1 - 8/2 , LONG - 1 - 8/2 , LONG - 1 - 10/0</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-8/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-8/%40)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>49.56000137</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>ENJSA</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="B37" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 1 - 7/4 , LONG - 1 - 7/3 , LONG - 1 - 7/3</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G, Y-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
+LONG - 1 - 6/4 , LONG - 1 - 7/3 , LONG - 1 - 7/4</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G, U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Q - TP5/20G - %70 / 203 işlem - ADAY (4g/-5/%45)
 U - TP2/10G - %75 / 97 işlem - ADAY (6g/-6/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (14g/-6/%56)
-Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 78 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TRALT</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-LONG - 1 - 8/2 , LONG - 1 - 8/2 , LONG - 1 - 10/1</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-7/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-7/%40)</t>
+U - TP5/20G - %74 / 74 işlem - ADAY (14g/-5/%56)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 81 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -2903,7 +2902,7 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>49.78</v>
+        <v>111.5</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46282</v>
@@ -2916,7 +2915,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -2931,7 +2930,7 @@
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 -1, TOPLAM -1, ALMA
-UST -  - 1/10 , SHORT - 4 - 7/16 , SHORT - 4 - 5/5</t>
+UST -  - 0/10 , SHORT - 4 - 8/15 , SHORT - 4 - 6/4</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2953,8 +2952,8 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %75 / 97 işlem - ADAY (4g/-6/%35)
-U - TP5/20G - %74 / 74 işlem - ADAY (6g/-4/%80)</t>
+          <t>U - TP2/10G - %75 / 97 işlem - ADAY (4g/-7/%35)
+U - TP5/20G - %74 / 74 işlem - ADAY (6g/-5/%80)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2968,7 +2967,7 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>57.7</v>
+        <v>57.15000153</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46282</v>
@@ -2981,7 +2980,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -2996,7 +2995,7 @@
       <c r="E39" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 7/3 , LONG - 1 - 7/3 , LONG - 1 - 8/2</t>
+LONG - 1 - 8/2 , LONG - 1 - 8/2 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -3018,7 +3017,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-7/%69)</t>
+          <t>H - TP2/10G - %92 / 51 işlem - ONAY (4g/-8/%69)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -3032,7 +3031,7 @@
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>19.41</v>
+        <v>19.23999977</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>46282</v>
@@ -3041,46 +3040,110 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
+LONG - 1 - 31/3 , ALT -  - 22/4 , LONG - 1 - 31/3</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 102 işlem - ADAY (17g/-2/%35)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>37.72000122</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>TSKB</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="B41" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL +1, XU030 -1, TOPLAM 0, ALMA
-LONG - 1 - 4/6 , LONG - 1 - 4/6 , LONG - 1 - 4/6</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="6" t="n">
+LONG - 1 - 5/5 , LONG - 1 - 5/5 , LONG - 1 - 5/5</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I41" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>H-TP2/10G, H-TP5/10G, H-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %92 / 51 işlem - ONAY (6g/-1/%67)
 H - TP5/10G - %70 / 20 işlem - ADAY (6g/-1/%75)
@@ -3088,84 +3151,18 @@
 Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N40" s="7" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>KCHOL</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-LONG - 1 - 4/6 , LONG - 84 - 8/12 , SHORT - 7 - 3/12</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>U-TP5/20G, Y-TP5/20G, Z-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (7g/-2/%95)
-Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)
-Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N41" s="7" t="n">
-        <v>220.1</v>
+        <v>11.22000027</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>46282</v>
@@ -3178,7 +3175,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -3193,7 +3190,7 @@
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL +1, XU030 -1, TOPLAM -2, ALMA
-LONG - 1 - 7/3 , LONG - 1 - 5/5 , LONG - 1 - 7/3</t>
+LONG - 1 - 7/3 , LONG - 1 - 6/4 , LONG - 1 - 8/3</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -3216,7 +3213,7 @@
       <c r="K42" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %86 / 78 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %69 / 179 işlem - ADAY (4g/-3/%80)
+E - TP5/20G - %69 / 179 işlem - ADAY (4g/-4/%80)
 Y - TP5/10G - %61 / 71 işlem - ADAY (0g/0/%100)
 Y - TP5/20G - %71 / 98 işlem - ADAY (0g/0/%100)</t>
         </is>
@@ -3232,7 +3229,7 @@
         </is>
       </c>
       <c r="N42" s="7" t="n">
-        <v>381</v>
+        <v>379.75</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>46282</v>
@@ -3241,11 +3238,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -3259,8 +3256,8 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 29/1 , ALT -  - 23/5 , LONG - 1 - 32/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
+LONG - 1 - 6/4 , LONG - 13 - 17/8 , LONG - 11 - 18/8</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -3277,26 +3274,26 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>Z-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 102 işlem - ADAY (17g/-3/%35)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-1/%75)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>37.54</v>
+        <v>19.07999992</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46282</v>
@@ -3305,11 +3302,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3323,8 +3320,8 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1, TOPLAM 1, ALMA
-LONG - 1 - 5/5 , LONG - 13 - 17/8 , LONG - 11 - 17/8</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+LONG - 1 - 9/1 , SHORT - 91 - 9/10 , LONG - 1 - 13/4</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -3346,7 +3343,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-1/%75)</t>
+          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-2/%75)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3360,7 +3357,7 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>19.11</v>
+        <v>80.40000153</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46282</v>
@@ -3369,11 +3366,11 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -3388,7 +3385,7 @@
       <c r="E45" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-LONG - 1 - 9/1 , SHORT - 91 - 9/10 , LONG - 1 - 13/4</t>
+SHORT - 19 - 4/12 , LONG - 84 - 9/11 , SHORT - 7 - 4/12</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -3398,33 +3395,34 @@
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>U-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-2/%75)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (7g/-3/%95)
+Z - TP5/20G - %75 / 71 işlem - ADAY (7g/-3/%75)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>80.45</v>
+        <v>218.69999695</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>46282</v>
@@ -3433,11 +3431,11 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -3451,8 +3449,8 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-LONG - 1 - 29/5 , LONG - 1 - 7/5 , LONG - 1 - 7/3</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
+ALT -  - 14/1 , ALT -  - 12/2 , ALT -  - 13/0</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
@@ -3469,26 +3467,26 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Z-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Z - TP5/20G - %75 / 71 işlem - ADAY (6g/-4/%75)</t>
+          <t>U - TP5/20G - %74 / 74 işlem - ADAY (16g/-12/%35)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>ADAY Z: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N46" s="7" t="n">
-        <v>86.40000000000001</v>
+        <v>20.42000008</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>46282</v>
@@ -3497,7 +3495,7 @@
     <row r="47" ht="32" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
@@ -3516,34 +3514,35 @@
       <c r="E47" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-ALT -  - 14/1 , ALT -  - 12/2 , ALT -  - 13/0</t>
+SHORT - 4 - 4/8 , LONG - 28 - 13/12 , SHORT - 4 - 2/8</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 74 işlem - ADAY (16g/-12/%35)</t>
+          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-4/%50)
+Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-4/%50)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -3552,7 +3551,7 @@
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>20.44</v>
+        <v>287</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>46282</v>
@@ -3561,11 +3560,11 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -3580,44 +3579,43 @@
       <c r="E48" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-SHORT - 4 - 4/8 , LONG - 28 - 13/11 , SHORT - 4 - 2/7</t>
+ALT -  - 20/7 , ALT -  - 29/6 , ALT -  - 31/12</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Y-TP2/10G, Y-TP5/10G</t>
+          <t>Y-TP5/20G</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Y - TP2/10G - %86 / 78 işlem - ONAY (4g/-5/%50)
-Y - TP5/10G - %61 / 71 işlem - ADAY (4g/-5/%45)</t>
+          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (7g/-13/%35)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>286.5</v>
+        <v>64.30000305</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46282</v>
@@ -3626,11 +3624,11 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -3644,8 +3642,8 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 -1, TOPLAM 2, ALMA
-ALT -  - 21/7 , ALT -  - 30/6 , ALT -  - 31/12</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 -1, TOPLAM -1, ALMA
+SHORT - 18 - 14/16 , SHORT - 18 - 10/6 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3662,26 +3660,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Y-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Y - TP5/20G - %71 / 98 işlem - ADAY (7g/-14/%35)</t>
+          <t>Q - TP5/20G - %70 / 203 işlem - ADAY (8g/-4/%55)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 65 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 86 hisse / 103 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>64.15000000000001</v>
+        <v>132</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46282</v>
@@ -3694,7 +3692,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -3709,7 +3707,7 @@
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 -1, TOPLAM -3, ALMA
-ALT -  - 22/0 , ALT -  - 22/0 , ALT -  - 24/6</t>
+ALT -  - 23/0 , ALT -  - 23/0 , ALT -  - 24/6</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3745,7 +3743,7 @@
         </is>
       </c>
       <c r="N50" s="7" t="n">
-        <v>526</v>
+        <v>524.5</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>46282</v>
@@ -3758,7 +3756,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -3809,7 +3807,7 @@
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>288.75</v>
+        <v>289.25</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>46282</v>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -476,7 +476,7 @@
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="N2" s="7" t="n">
-        <v>45.78</v>
+        <v>45.77999878</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>46286</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>4.34</v>
+        <v>4.34000015</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>46286</v>
@@ -695,11 +695,11 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>OTKAR</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.4</v>
+        <v>-0.9</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -712,248 +712,241 @@
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-ALT -  - 40/14 , ALT -  - 35/19 , ALT -  - 32/17</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %69 / 183 işlem - ADAY (8g/-16/%25)
-I - TP5/20G - %81 / 75 işlem - ADAY (10g/-15/%70)
-R - TP5/10G - %62 / 144 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 73 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EKGYO</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 3 - 8/2 , LONG - 3 - 8/2 , LONG - 3 - 9/1</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %91 / 55 işlem - ONAY (6g/-8/%67)</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ULKER</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , ALT -  - 47/9 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP2/10G, Q-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %69 / 183 işlem - ADAY (0g/0/%100)
-I - TP5/10G - %61 / 109 işlem - ADAY (0g/0/%100)
-I - TP5/20G - %81 / 75 işlem - ADAY (0g/0/%100)
-Q - TP2/10G - %82 / 106 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %69 / 205 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %62 / 144 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 7 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 69 hisse / 72 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OTKAR</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
 LONG - 3 - 10/0 , LONG - 3 - 10/0 , ALT -  - 11/0</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>I-TP2/10G, I-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
 I - TP5/20G - %81 / 75 işlem - ADAY (0g/0/%100)
 Y - TP5/20G - %72 / 99 işlem - ADAY (2g/-1/%90)</t>
         </is>
       </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>302</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ISMEN</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+LONG - 3 - 10/2 , LONG - 3 - 10/2 , LONG - 17 - 13/3</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, I-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
+I - TP5/20G - %81 / 75 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 63 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>33.65999985</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EKGYO</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 3 - 8/2 , LONG - 3 - 8/2 , LONG - 3 - 9/1</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, Y-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %91 / 55 işlem - ONAY (6g/-8/%67)
+Y - TP5/20G - %72 / 99 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY Y: seçili strateji teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>19.20000076</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MIATK</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-40/%57)</t>
+        </is>
+      </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Y: seçili strateji teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>302</v>
+        <v>22.78000069</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>46286</v>
@@ -962,7 +955,7 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -970,55 +963,56 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-LONG - 3 - 10/2 , LONG - 3 - 10/2 , LONG - 17 - 13/3</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 1 - 17/0 , SHORT - 148 - 34/1 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/20G</t>
+          <t>I-TP2/10G, E-TP5/20G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
           <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
+E - TP5/20G - %69 / 183 işlem - ADAY (4g/-4/%80)
 I - TP5/20G - %81 / 75 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 63 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 64 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N8" s="7" t="n">
-        <v>33.66</v>
+        <v>154.5</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>46286</v>
@@ -1027,11 +1021,11 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1044,226 +1038,161 @@
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>K-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/10G - %85 / 40 işlem - ONAY (7g/-40/%57)</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 32 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>22.78</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DOAS</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 1 - 17/0 , SHORT - 148 - 34/1 , ALT -  - 16/3</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %69 / 183 işlem - ADAY (4g/-4/%80)
-I - TP5/20G - %81 / 75 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %62 / 144 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 68 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>154.5</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>BIS 0, PHL +2, CNDL +1, XU030 +1, TOPLAM 4, İZLE
 ALT -  - 28/0 , ALT -  - 28/16 , -</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>M-TP5/20G, Q-TP5/20G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>M - TP5/20G - %88 / 56 işlem - ONAY (18g/-30/%33)
 Q - TP5/20G - %69 / 205 işlem - ADAY (16g/-30/%10)
 Y - TP5/20G - %72 / 99 işlem - ADAY (17g/-30/%0)</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 85 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N11" s="7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O11" s="8" t="n">
+      <c r="N9" s="7" t="n">
+        <v>2.38000011</v>
+      </c>
+      <c r="O9" s="8" t="n">
         <v>46286</v>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 3 - 8/2 , LONG - 3 - 8/2 , LONG - 3 - 9/2</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
+I - TP5/20G - %81 / 75 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %69 / 205 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 75 hisse / 73 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>107.40000153</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>KLRHO</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>-10</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL -2, CNDL 0, XU030 +1, TOPLAM -3, ALMA
-ALT -  - 45/19 , ALT -  - 55/27 , -</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
+ALT -  - 45/18 , ALT -  - 55/27 , -</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>L-TP5/20G, L-TP5/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-42/%60)
 L - TP5/10G - %79 / 61 işlem - ADAY (9g/-40/%17)
@@ -1271,66 +1200,66 @@
 R - TP5/20G - %80 / 106 işlem - ADAY (9g/-40/%35)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 64 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N12" s="7" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="O12" s="8" t="n">
+      <c r="N11" s="7" t="n">
+        <v>38.11999893</v>
+      </c>
+      <c r="O11" s="8" t="n">
         <v>46286</v>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>GRSEL</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I12" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>I-TP2/10G, E-TP5/20G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
 E - TP5/20G - %69 / 183 işlem - ADAY (9g/-10/%25)
@@ -1338,84 +1267,152 @@
 I - TP5/20G - %81 / 75 işlem - ADAY (9g/-10/%75)</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="N12" s="7" t="n">
         <v>267.75</v>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="O12" s="8" t="n">
         <v>46286</v>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>CVKMD</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B13" s="3" t="n">
         <v>-3</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL +1, XU030 +1, TOPLAM 2, ALMA
 ALT -  - 24/10 , ALT -  - 22/10 , -</t>
         </is>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F13" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6" t="n">
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>X-TP2/10G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>X - TP2/10G - %98 / 48 işlem - ONAY (4g/-6/%100)
 I - TP5/10G - %61 / 109 işlem - ADAY (9g/-14/%20)
 I - TP5/20G - %81 / 75 işlem - ADAY (10g/-16/%70)</t>
         </is>
       </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>ONAY X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>13.30000019</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SARKY</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+LONG - 3 - 9/3 , SHORT - 90 - 23/9 , ALT -  - 15/2</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 183 işlem - ADAY (5g/-5/%70)
+Q - TP2/10G - %82 / 106 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %69 / 205 işlem - ADAY (0g/0/%100)
+R - TP2/10G - %84 / 122 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %62 / 144 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>ONAY X: seçili strateji teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 4 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 86 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
       <c r="N14" s="7" t="n">
-        <v>13.3</v>
+        <v>22.18000031</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>46286</v>
@@ -1480,7 +1477,7 @@
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>129.7</v>
+        <v>129.69999695</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>46286</v>
@@ -1545,7 +1542,7 @@
         </is>
       </c>
       <c r="N16" s="7" t="n">
-        <v>86.90000000000001</v>
+        <v>86.90000153</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>46286</v>
@@ -1554,11 +1551,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1572,8 +1569,8 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-LONG - 3 - 9/3 , SHORT - 90 - 23/9 , ALT -  - 15/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 14/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1583,26 +1580,25 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP2/10G, Q-TP5/20G</t>
+          <t>E-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %69 / 183 işlem - ADAY (5g/-5/%70)
-Q - TP2/10G - %82 / 106 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %69 / 205 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %69 / 183 işlem - ADAY (0g/0/%100)
+U - TP5/20G - %75 / 76 işlem - ADAY (17g/-11/%13)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 93 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 80 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1611,7 +1607,7 @@
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>22.18</v>
+        <v>19.84000015</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>46286</v>
@@ -1620,11 +1616,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-1.8</v>
+        <v>-9</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -1638,225 +1634,158 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 14/3 , ALT -  - 14/3 , ALT -  - 14/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, U-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 183 işlem - ADAY (0g/0/%100)
-U - TP5/20G - %75 / 76 işlem - ADAY (17g/-11/%13)</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 80 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 10 - 5/5 , LONG - 3 - 7/3 , LONG - 3 - 8/3</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %69 / 183 işlem - ADAY (10g/+3/%100)
-T - TP5/10G - %65 / 141 işlem - ADAY (0g/0/%100)
-T - TP5/20G - %79 / 135 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 71 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>26.98</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-9</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %69 / 183 işlem - ADAY (9g/-35/%25)
 I - TP5/10G - %61 / 109 işlem - ADAY (9g/-35/%15)
 I - TP5/20G - %81 / 75 işlem - ADAY (9g/-35/%70)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
-      <c r="N20" s="7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="O20" s="8" t="n">
+      <c r="N18" s="7" t="n">
+        <v>2.02999997</v>
+      </c>
+      <c r="O18" s="8" t="n">
         <v>46286</v>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ENERY</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+UST -  - 7/20 , UST -  - 3/18 , -</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 61 işlem - ADAY (1g/-8/%75)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>11.84000015</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>GSRAY</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B20" s="3" t="n">
         <v>-3.2</v>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 22/8 , ALT -  - 22/8 , ALT -  - 22/8</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
+ALT -  - 22/8 , ALT -  - 22/8 , ALT -  - 21/8</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H20" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I20" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Q - TP2/10G - %82 / 106 işlem - ADAY (8g/-12/%20)
 Q - TP5/20G - %69 / 205 işlem - ADAY (8g/-12/%15)
@@ -1864,18 +1793,83 @@
 R - TP5/10G - %62 / 144 işlem - ADAY (8g/-12/%0)</t>
         </is>
       </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 83 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>0.91000003</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 65/22 , ALT -  - 43/22 , ALT -  - 35/20</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %65 / 141 işlem - ADAY (5g/-20/%15)
+T - TP5/20G - %79 / 135 işlem - ADAY (5g/-20/%40)</t>
+        </is>
+      </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 83 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>0.91</v>
+        <v>2.26999998</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>46286</v>
@@ -1884,11 +1878,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-3</v>
+        <v>-0.4</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
@@ -1903,35 +1897,34 @@
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 65/22 , ALT -  - 43/22 , ALT -  - 35/20</t>
+ALT -  - 47/9 , ALT -  - 16/5 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 141 işlem - ADAY (5g/-20/%15)
-T - TP5/20G - %79 / 135 işlem - ADAY (5g/-20/%40)</t>
+          <t>Q - TP5/20G - %69 / 205 işlem - ADAY (9g/-12/%15)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 72 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 87 hisse / 108 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -1940,7 +1933,7 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>2.27</v>
+        <v>2.57999992</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>46286</v>
@@ -1949,11 +1942,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
@@ -1968,7 +1961,7 @@
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 47/9 , ALT -  - 16/5 , ALT -  - 16/5</t>
+-</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -1990,7 +1983,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 205 işlem - ADAY (9g/-12/%15)</t>
+          <t>Q - TP5/20G - %69 / 205 işlem - ADAY (7g/-2/%80)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2004,7 +1997,7 @@
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>2.58</v>
+        <v>226.3999939</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>46286</v>
@@ -2013,11 +2006,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
@@ -2031,7 +2024,8 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 10 - 5/5 , LONG - 3 - 7/3 , LONG - 3 - 8/3</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2048,17 +2042,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 205 işlem - ADAY (7g/?/%?)</t>
+          <t>E - TP5/20G - %69 / 183 işlem - ADAY (10g/+3/%100)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 87 hisse / 108 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 70 hisse / 94 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2067,10 +2061,10 @@
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>230</v>
+        <v>26.97999954</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
@@ -2131,7 +2125,7 @@
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>5.16</v>
+        <v>5.15999985</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>46286</v>
@@ -2196,7 +2190,7 @@
         </is>
       </c>
       <c r="N26" s="7" t="n">
-        <v>24.52</v>
+        <v>24.52000046</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>46286</v>
@@ -2260,7 +2254,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>57.4</v>
+        <v>57.40000153</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>46286</v>
@@ -2287,7 +2281,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 LONG - 37 - 6/6 , LONG - 37 - 6/6 , LONG - 15 - 7/5</t>
         </is>
       </c>
@@ -2324,7 +2318,7 @@
         </is>
       </c>
       <c r="N28" s="7" t="n">
-        <v>151.2</v>
+        <v>151.19999695</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>46286</v>
@@ -2388,7 +2382,7 @@
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>2.62</v>
+        <v>2.61999989</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>46286</v>
@@ -2452,7 +2446,7 @@
         </is>
       </c>
       <c r="N30" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>99.90000153</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>46286</v>
@@ -2543,7 +2537,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
 UST -  - 2/11 , SHORT - 6 - 5/17 , SHORT - 6 - 4/6</t>
         </is>
       </c>
@@ -2581,7 +2575,7 @@
         </is>
       </c>
       <c r="N32" s="7" t="n">
-        <v>58.6</v>
+        <v>58.59999847</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>46286</v>
@@ -2590,11 +2584,11 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
@@ -2608,8 +2602,8 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 13/1 , ALT -  - 12/1 , ALT -  - 13/0</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+SHORT - 16 - 9/3 , LONG - 3 - 9/1 , LONG - 3 - 9/1</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2619,26 +2613,29 @@
         <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>I-TP2/10G, Q-TP5/20G, U-TP5/20G</t>
+          <t>Y-TP2/10G, Q-TP5/20G, R-TP5/10G, U-TP5/20G, Y-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %86 / 128 işlem - ONAY (0g/0/%100)
-Q - TP5/20G - %69 / 205 işlem - ADAY (0g/0/%100)
-U - TP5/20G - %75 / 76 işlem - ADAY (18g/-12/%6)</t>
+          <t>Y - TP2/10G - %87 / 82 işlem - ONAY (0g/0/%100)
+Q - TP5/20G - %69 / 205 işlem - ADAY (6g/-7/%45)
+R - TP5/10G - %62 / 144 işlem - ADAY (0g/0/%100)
+U - TP5/20G - %75 / 76 işlem - ADAY (16g/-8/%35)
+Y - TP5/10G - %62 / 74 işlem - ADAY (0g/0/%100)
+Y - TP5/20G - %72 / 99 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 74 hisse / 75 giriş gününe yayılıyor</t>
+          <t>ONAY Y: seçili strateji teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi; Bugün 4 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 79 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -2647,7 +2644,7 @@
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>20.36</v>
+        <v>109</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>46286</v>
@@ -2711,7 +2708,7 @@
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>47.24</v>
+        <v>47.24000168</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>46286</v>
@@ -2778,7 +2775,7 @@
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>10.85</v>
+        <v>10.85000038</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>46286</v>
@@ -2805,7 +2802,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 LONG - 3 - 8/8 , LONG - 3 - 6/6 , LONG - 81 - 10/10</t>
         </is>
       </c>
@@ -2845,7 +2842,7 @@
         </is>
       </c>
       <c r="N36" s="7" t="n">
-        <v>133.1</v>
+        <v>133.1000061</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>46286</v>
@@ -2911,7 +2908,7 @@
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>2.31</v>
+        <v>2.30999994</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>46286</v>
@@ -2939,7 +2936,7 @@
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 3 - 3/6 , LONG - 86 - 7/12 , SHORT - 9 - 2/13</t>
+LONG - 3 - 3/7 , LONG - 86 - 7/12 , SHORT - 9 - 2/13</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2976,7 +2973,7 @@
         </is>
       </c>
       <c r="N38" s="7" t="n">
-        <v>222.3</v>
+        <v>222.30000305</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>46286</v>
@@ -2985,11 +2982,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -3003,93 +3000,159 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL +1, XU030 +1, TOPLAM 3, İZLE
-SHORT - 6 - 3/8 , LONG - 30 - 11/12 , SHORT - 6 - 2/8</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 40/14 , ALT -  - 35/19 , ALT -  - 32/17</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
         <v>16</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, R-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %69 / 183 işlem - ADAY (8g/-16/%25)
+I - TP5/20G - %81 / 75 işlem - ADAY (10g/-15/%70)
+R - TP5/10G - %62 / 144 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 65 hisse / 77 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>67.19999695</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 6 - 3/8 , LONG - 30 - 11/12 , SHORT - 6 - 2/8</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Y-TP2/10G, Y-TP5/10G</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %87 / 82 işlem - ONAY (6g/-3/%35)
 Y - TP5/10G - %62 / 74 işlem - ADAY (6g/-3/%55)</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 39 hisse / 65 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="N40" s="7" t="n">
         <v>290</v>
       </c>
-      <c r="O39" s="8" t="n">
+      <c r="O40" s="8" t="n">
         <v>46286</v>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>ASELS</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B41" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 LONG - 3 - 7/3 , LONG - 3 - 5/5 , LONG - 3 - 8/3</t>
         </is>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F41" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="6" t="n">
+      <c r="G41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I41" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Y-TP2/10G, E-TP5/20G, Y-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %87 / 82 işlem - ONAY (2g/0/%85)
 E - TP5/20G - %69 / 183 işlem - ADAY (6g/-4/%90)
@@ -3097,66 +3160,66 @@
 Y - TP5/20G - %72 / 99 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 77 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N41" s="7" t="n">
         <v>378</v>
       </c>
-      <c r="O40" s="8" t="n">
+      <c r="O41" s="8" t="n">
         <v>46286</v>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>TRALT</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B42" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 LONG - 3 - 4/6 , LONG - 3 - 4/6 , LONG - 3 - 7/4</t>
         </is>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F42" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="6" t="n">
+      <c r="G42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Y-TP2/10G, R-TP5/10G, Y-TP5/10G, Y-TP5/20G</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %87 / 82 işlem - ONAY (6g/-5/%35)
 R - TP5/10G - %62 / 144 işlem - ADAY (1g/+2/%100)
@@ -3164,66 +3227,66 @@
 Y - TP5/20G - %72 / 99 işlem - ADAY (1g/+2/%100)</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi, Y: seçili strateji teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 70 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
-      <c r="N41" s="7" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="O41" s="8" t="n">
+      <c r="N42" s="7" t="n">
+        <v>51.15000153</v>
+      </c>
+      <c r="O42" s="8" t="n">
         <v>46286</v>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>TUKAS</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
 LONG - 1 - 13/7 , LONG - 1 - 14/3 , LONG - 1 - 3/6</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F43" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G43" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H43" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I43" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Y-TP2/10G, Z-TP2/10G, U-TP5/20G, Y-TP5/10G, Y-TP5/20G, Z-TP5/20G</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Y - TP2/10G - %87 / 82 işlem - ONAY (0g/0/%100)
 Z - TP2/10G - %88 / 43 işlem - ONAY (8g/-3/%75)
@@ -3233,83 +3296,18 @@
 Z - TP5/20G - %80 / 40 işlem - ADAY (16g/-2/%13)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>ONAY Y: seçili strateji teyidi, Z: seçili strateji teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi, Y: seçili strateji teyidi, Z: seçili strateji teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
-      <c r="N42" s="7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>46286</v>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ENJSA</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-SHORT - 16 - 9/3 , LONG - 3 - 9/1 , LONG - 3 - 9/1</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %69 / 205 işlem - ADAY (6g/-7/%45)
-U - TP5/20G - %75 / 76 işlem - ADAY (16g/-8/%35)</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 77 hisse / 91 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
       <c r="N43" s="7" t="n">
-        <v>109</v>
+        <v>2.01999998</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>46286</v>
@@ -3318,11 +3316,11 @@
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-7.9</v>
+        <v>0.8</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -3336,12 +3334,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-UST -  - 7/20 , UST -  - 3/18 , -</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 13/1 , ALT -  - 12/1 , ALT -  - 13/0</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -3354,17 +3352,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>L-TP5/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 61 işlem - ADAY (1g/-8/%75)</t>
+          <t>U - TP5/20G - %75 / 76 işlem - ADAY (18g/-12/%6)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -3373,7 +3371,7 @@
         </is>
       </c>
       <c r="N44" s="7" t="n">
-        <v>11.84</v>
+        <v>20.36000061</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>46286</v>
@@ -3400,7 +3398,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 LONG - 3 - 6/6 , LONG - 3 - 6/6 , ALT -  - 13/2</t>
         </is>
       </c>
@@ -3464,7 +3462,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 LONG - 2 - 19/3 , LONG - 2 - 19/3 , ALT -  - 21/3</t>
         </is>
       </c>
@@ -3629,7 +3627,7 @@
         </is>
       </c>
       <c r="N48" s="7" t="n">
-        <v>36.58</v>
+        <v>36.58000183</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>46286</v>
@@ -3656,7 +3654,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 ALT -  - 29/1 , ALT -  - 23/5 , LONG - 1 - 6/4</t>
         </is>
       </c>
@@ -3693,7 +3691,7 @@
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>37.4</v>
+        <v>37.40000153</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>46286</v>
@@ -3720,7 +3718,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 ALT -  - 26/11 , ALT -  - 26/11 , -</t>
         </is>
       </c>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$O$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OZET'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OZET'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -89,6 +96,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText